--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E663518-DF6D-4800-92F7-3D3C4E45B3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA472E5-F5BC-4354-93BD-382B95B20467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="StakeHolder" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="155">
   <si>
     <t>품질 속성</t>
   </si>
@@ -784,49 +784,67 @@
     <t>1순위</t>
   </si>
   <si>
-    <t>[전체 파이프라인에 대해서 (비격리 fps − 격리 fps) ÷ 비격리 fps ≤ 10%]</t>
-  </si>
-  <si>
-    <t>[도메인간 dma-buf버퍼 전달시 memcpy 호출 횟수 = 0회]</t>
-  </si>
-  <si>
     <t>2순위</t>
   </si>
   <si>
-    <t>[(격리 메모리 − 비격리 메모리) ≤ 256MB, (격리 전력 − 비격리 전력) ÷ 비격리 전력 ≤ 5%]</t>
-  </si>
-  <si>
     <t>3순위</t>
   </si>
   <si>
     <t>확장성 (Workload 수용)</t>
   </si>
   <si>
-    <t>[Workload 추가 전후 git diff에서 Framework 코어 디렉터리 변경 라인 수 = 0 LoC]</t>
-  </si>
-  <si>
-    <t>[Secure OS 교체 전후 git diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
-  </si>
-  <si>
     <t>가용성 (pVM 장애 격리)</t>
   </si>
   <si>
-    <t>[(Workload 서비스 재개 시각) − (장애 주입 시각) ≤ 3초]</t>
-  </si>
-  <si>
     <t>시험 용이성 (격리 검증)</t>
   </si>
   <si>
-    <t>[(전체 공격 벡터 항목 − 미커버 항목) ÷ 전체 항목 = 100%]</t>
-  </si>
-  <si>
     <t>보안 (HW 접근 격리)</t>
   </si>
   <si>
     <t>Camera/AI HW 사용 주체 전환 시 배타적 접근이 항상 보장된다.</t>
   </si>
   <si>
-    <t>[S2MPU 권한 상태 로그에서 두 주체의 권한 중첩 구간 = 없음 (위반 횟수 = 0)]</t>
+    <t>[S2MPU 권한 상태 로그에서 두 주체의 권한 중첩 구간 없음 (위반 횟수 = 0)]</t>
+  </si>
+  <si>
+    <t>[전체 파이프라인에 대해서 (비격리 fps - 격리 fps) / 비격리 fps &lt;= 10%]</t>
+  </si>
+  <si>
+    <t>[Workload 추가 전후 diff에서 Framework 코어 디렉터리 변경 라인 수 = 0 LoC]</t>
+  </si>
+  <si>
+    <t>4순위</t>
+  </si>
+  <si>
+    <t>[도메인 간 dma-buf 버퍼 전달 시 memcpy 호출 횟수 = 0회]</t>
+  </si>
+  <si>
+    <t>5순위</t>
+  </si>
+  <si>
+    <t>[(Workload 서비스 재개 시각) - (장애 주입 시각) &lt;= 3초]</t>
+  </si>
+  <si>
+    <t>6순위</t>
+  </si>
+  <si>
+    <t>[(격리 메모리 - 비격리 메모리) &lt;= 256MB, (격리 전력 - 비격리 전력) / 비격리 전력 &lt;= 5%]</t>
+  </si>
+  <si>
+    <t>7순위</t>
+  </si>
+  <si>
+    <t>[(전체 공격 벡터 항목 - 미커버 항목) / 전체 항목 = 100%]</t>
+  </si>
+  <si>
+    <t>8순위</t>
+  </si>
+  <si>
+    <t>[Secure OS 교체 전후 diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
+  </si>
+  <si>
+    <t>9순위</t>
   </si>
 </sst>
 </file>
@@ -1989,10 +2007,10 @@
         <v>11</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>4</v>
@@ -2001,14 +2019,14 @@
         <v>4</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -2019,29 +2037,29 @@
         <v>12</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>5</v>
+      <c r="E6" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="8" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
@@ -2049,29 +2067,29 @@
         <v>13</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>5</v>
+        <v>123</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+        <v>143</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
@@ -2079,29 +2097,29 @@
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>4</v>
+      <c r="E10" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="8" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="11"/>
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
@@ -2109,10 +2127,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>5</v>
@@ -2121,14 +2139,14 @@
         <v>5</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -2139,10 +2157,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>5</v>
@@ -2151,14 +2169,14 @@
         <v>5</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="8" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
@@ -2169,7 +2187,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>126</v>
@@ -2181,14 +2199,14 @@
         <v>5</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -2199,78 +2217,78 @@
         <v>18</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>4</v>
+        <v>124</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+        <v>153</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
       <c r="F19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA472E5-F5BC-4354-93BD-382B95B20467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB366698-D1FA-422F-96FE-01E8A8B5427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="StakeHolder" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="UC (정제)" sheetId="2" r:id="rId3"/>
     <sheet name="FR" sheetId="4" r:id="rId4"/>
     <sheet name="CONST" sheetId="5" r:id="rId5"/>
-    <sheet name="QA" sheetId="6" r:id="rId6"/>
+    <sheet name="UtilityTree" sheetId="7" r:id="rId6"/>
+    <sheet name="QA" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="260">
   <si>
     <t>품질 속성</t>
   </si>
@@ -845,13 +846,578 @@
   </si>
   <si>
     <t>9순위</t>
+  </si>
+  <si>
+    <t>QA-C ID</t>
+  </si>
+  <si>
+    <t>QA-M ID</t>
+  </si>
+  <si>
+    <t>응답 측정치</t>
+  </si>
+  <si>
+    <t>측정 방법</t>
+  </si>
+  <si>
+    <t>수치 설정 근거</t>
+  </si>
+  <si>
+    <t>근거 유형 / 확보 방법</t>
+  </si>
+  <si>
+    <t>QA-C-01</t>
+  </si>
+  <si>
+    <t>QA-M-01</t>
+  </si>
+  <si>
+    <t>공격 벡터 차단율 100%</t>
+  </si>
+  <si>
+    <t>보안 속성은 부분 달성이 무의미하며, 식별된 공격 전부 차단이 합격 기준</t>
+  </si>
+  <si>
+    <t>QA-M-02</t>
+  </si>
+  <si>
+    <t>격리 메모리 노출 0건</t>
+  </si>
+  <si>
+    <t>공격 실행 중 pVM 소유 메모리에서 실제로 읽힌 바이트와 노출 이벤트 수를 계측</t>
+  </si>
+  <si>
+    <t>단 1건의 노출로 기밀성 침해가 성립하므로 목표값은 0건이어야 함</t>
+  </si>
+  <si>
+    <t>QA-C-02</t>
+  </si>
+  <si>
+    <t>QA-M-03</t>
+  </si>
+  <si>
+    <t>30fps 유지</t>
+  </si>
+  <si>
+    <t>파이프라인 출구에서 초당 처리 프레임 수를 카운트하고 이동 평균으로 지속 유지 여부를 판정</t>
+  </si>
+  <si>
+    <t>30fps는 카메라/영상 산업의 표준 기본 프레임율이며 레퍼런스 시나리오의 센서 출력 규격</t>
+  </si>
+  <si>
+    <t>QA-M-04</t>
+  </si>
+  <si>
+    <t>E2E 지연 100ms 이하</t>
+  </si>
+  <si>
+    <t>센서 timestamp와 판단 결과 산출 시각의 차이를 프레임별 계측하고 p99로 평가</t>
+  </si>
+  <si>
+    <t>HCI 기준에서 0.1초는 즉각 반응으로 인지되는 상한</t>
+  </si>
+  <si>
+    <t>QA-M-05</t>
+  </si>
+  <si>
+    <t>비격리 대비 성능 저하 10% 이내</t>
+  </si>
+  <si>
+    <t>KVM 계열 가상화의 I/O 경로 오버헤드가 문헌상 통상 5~15%로 보고되는 범위에서 상한 설정</t>
+  </si>
+  <si>
+    <t>QA-C-03</t>
+  </si>
+  <si>
+    <t>QA-M-06</t>
+  </si>
+  <si>
+    <t>프레임 전달 복사 횟수 0회</t>
+  </si>
+  <si>
+    <t>dma-buf 등 버퍼 전달 경로에서 코드 경로와 trace로 복사 횟수를 확인</t>
+  </si>
+  <si>
+    <t>zero-copy 주장을 만족하려면 프레임 데이터 복사가 없어야 함</t>
+  </si>
+  <si>
+    <t>QA-M-07</t>
+  </si>
+  <si>
+    <t>도메인 간 프레임당 전달 지연 5ms 이하</t>
+  </si>
+  <si>
+    <t>송신 도메인 기록 완료 시각과 수신 도메인 접근 가능 시각의 차이를 계측</t>
+  </si>
+  <si>
+    <t>30fps 프레임 예산 33.3ms 중 약 15%를 전달 단계에 배분한 값</t>
+  </si>
+  <si>
+    <t>QA-C-04</t>
+  </si>
+  <si>
+    <t>QA-M-08</t>
+  </si>
+  <si>
+    <t>기존 프레임율 유지, Drop 0%</t>
+  </si>
+  <si>
+    <t>Host 일반 촬영과 보안 파이프라인을 동시 실행하며 양측의 프레임 drop 수를 카운트</t>
+  </si>
+  <si>
+    <t>프레임 drop은 사용자 체감 기능 실패와 실시간성 위반으로 이어지므로 0%가 기능 성립 조건</t>
+  </si>
+  <si>
+    <t>QA-M-09</t>
+  </si>
+  <si>
+    <t>사용 주체 전환 1ms 이하</t>
+  </si>
+  <si>
+    <t>사용 완료 확인, 잔류 데이터 소거, S2MPU 재설정, 재바인딩 구간의 소요 시간을 계측</t>
+  </si>
+  <si>
+    <t>33.3ms 프레임 간격의 약 3%로, 전환이 프레임 스케줄에 영향을 주지 않도록 배분</t>
+  </si>
+  <si>
+    <t>QA-C-05</t>
+  </si>
+  <si>
+    <t>QA-M-10</t>
+  </si>
+  <si>
+    <t>추가 메모리 256MB 이하</t>
+  </si>
+  <si>
+    <t>Framework+pVM 2개 상시 운용 상태와 비격리 구성의 시스템 메모리 사용량 차이를 계측</t>
+  </si>
+  <si>
+    <t>AVF Microdroid pVM이 통상 128~256MB급으로 운용되는 공개 구성 사례를 기준으로 추정</t>
+  </si>
+  <si>
+    <t>QA-M-11</t>
+  </si>
+  <si>
+    <t>전력 증가 5% 이내</t>
+  </si>
+  <si>
+    <t>전력 계측 장비 또는 PMIC 텔레메트리로 통상 운용 평균 소비 전력을 비교</t>
+  </si>
+  <si>
+    <t>현재 객관적 근거가 부족하므로 제품 배터리 가동시간 요구에서 역산해야 함</t>
+  </si>
+  <si>
+    <t>QA-C-06</t>
+  </si>
+  <si>
+    <t>QA-M-12</t>
+  </si>
+  <si>
+    <t>Framework 코어 수정 0 LoC</t>
+  </si>
+  <si>
+    <t>신규 Workload 추가 전후 git diff에서 Framework 코어 모듈 변경 라인 수를 카운트</t>
+  </si>
+  <si>
+    <t>플러그인 아키텍처의 개방-폐쇄 원칙상 코어 무수정이 목표 조건</t>
+  </si>
+  <si>
+    <t>QA-C-07</t>
+  </si>
+  <si>
+    <t>QA-M-13</t>
+  </si>
+  <si>
+    <t>Secure OS 외 모듈 수정 파일 0개</t>
+  </si>
+  <si>
+    <t>Secure OS 교체 작업 diff에서 Secure OS 패키지 외부 변경 파일 수를 카운트</t>
+  </si>
+  <si>
+    <t>인터페이스 추상화 목표의 정의상 Secure OS 외부 변경이 없어야 함</t>
+  </si>
+  <si>
+    <t>QA-C-08</t>
+  </si>
+  <si>
+    <t>QA-M-14</t>
+  </si>
+  <si>
+    <t>Host/타 pVM 다운타임 0</t>
+  </si>
+  <si>
+    <t>pVM 강제 kill, 게스트 커널 panic 등 장애 주입 중 Host 서비스와 타 pVM 응답 중단 시간을 계측</t>
+  </si>
+  <si>
+    <t>격리 구조의 정의상 장애 비전파가 성립해야 함</t>
+  </si>
+  <si>
+    <t>불변 조건</t>
+  </si>
+  <si>
+    <t>QA-M-15</t>
+  </si>
+  <si>
+    <t>장애 pVM 재시작 3초 이내</t>
+  </si>
+  <si>
+    <t>장애 검출 시각부터 pVM 재시작 완료와 Workload 서비스 재개 시각까지 계측</t>
+  </si>
+  <si>
+    <t>AVF pVM(Microdroid) 부팅이 초 단위로 보고되는 점에 기반한 초기 목표</t>
+  </si>
+  <si>
+    <t>QA-C-09</t>
+  </si>
+  <si>
+    <t>QA-M-16</t>
+  </si>
+  <si>
+    <t>자동화 시험 커버리지 100%</t>
+  </si>
+  <si>
+    <t>시험되지 않은 격리 주장 항목이 있으면 검증 완료 주장이 성립하지 않음</t>
+  </si>
+  <si>
+    <t>QA-M-17</t>
+  </si>
+  <si>
+    <t>회귀 반복 실행 가능</t>
+  </si>
+  <si>
+    <t>CI에서 동일 공격/격리 테스트가 반복 실행 가능한지 확인</t>
+  </si>
+  <si>
+    <t>격리 보장은 반복 가능한 회귀 검증 체계가 있어야 유지 가능</t>
+  </si>
+  <si>
+    <r>
+      <t>표준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 타겟 카메라 센서 데이터시트로 확정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>문헌 + 가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 로봇 제조사의 인지-행동 루프 요구 지연으로 보정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. PoC 실측 뒤 제조사 협의로 보정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 타겟 보드에서 dma-buf 전달 경로 검증</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>산술 도출 + 가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. memcpy/dma-buf 마이크로벤치마크로 검증</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 순간 부하의 예외 허용 여부는 제조사와 협의</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>산술 도출 + 가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 전환 시퀀스 마이크로벤치마크로 보정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>유사 시스템 참조 + 가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 타겟 SoC 메모리 예산표로 확정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. PoC 전력 프로파일링으로 보정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 코어 경계를 설계 단계에서 명시</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 후보 Secure OS의 GP TEE API 준수 여부를 사전 확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>가정치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. PoC 부팅 시간과 서비스 허용 중단 시간으로 확정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. GP TEE PP 공격 목록을 기준으로 커버리지 분모 확보</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. CI 실행 로그와 테스트 결과로 확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중요도</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난이도</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host 루트 권한 침해 테스트 도구로 공격 벡터를 전 항목 실행하고, 차단된 항목 비율을 산출</t>
+  </si>
+  <si>
+    <t>동일 HW에서 비격리 pipeline과 격리 구성의 fps/지연을 비교</t>
+  </si>
+  <si>
+    <t>격리 요구사항별 공격 벡터와 자동화 테스트의 매핑표를 작성하고 미커버 항목 수를 카운트</t>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 공격 벡터는 GP TEE PP 공격 목록과 Android VRP의 pKVM Boundary Defeat 사례를 기준으로 구성 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>99_security_qa_metrics.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 참조)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>불변 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>. 공격 벡터의 완전성을 GP TEE PP 기준으로 보강</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secure OS ENC/DEC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명령</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전송</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -907,6 +1473,40 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -916,7 +1516,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -939,13 +1539,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -956,9 +1585,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -982,6 +1608,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -997,6 +1650,59 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>83819</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="image-0" descr="uml diagram">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CB921F1-E588-C1EB-BA96-2DFA92D3BA54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="754380" y="10424160"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1305,101 +2011,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1419,189 +2125,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1682,7 +2388,7 @@
       <c r="B6" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1780,7 +2486,7 @@
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1797,7 +2503,7 @@
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1814,7 +2520,7 @@
       <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1831,7 +2537,7 @@
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1848,7 +2554,7 @@
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1865,8 +2571,8 @@
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>42</v>
+      <c r="B7" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>112</v>
@@ -1911,7 +2617,7 @@
       <c r="A2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -1925,7 +2631,7 @@
       <c r="A3" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1942,6 +2648,431 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3144ED8-EE6E-425D-A2F2-C1B2877442CC}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="2" width="9.8984375" customWidth="1"/>
+    <col min="3" max="3" width="17.796875" customWidth="1"/>
+    <col min="4" max="6" width="43.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:8" s="13" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" spans="1:8" s="13" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8" s="11" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:8" s="12" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:8" s="12" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+    </row>
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" spans="1:8" s="14" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A17" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -1973,322 +3104,322 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>136</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="8" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="8" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="8" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="8" t="s">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -1574,7 +1574,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1599,22 +1599,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
@@ -1629,11 +1617,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2658,412 +2655,412 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="14" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:8" s="8" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="15" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="15" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-    </row>
-    <row r="5" spans="1:8" s="13" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A5" s="15" t="s">
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="1:8" s="13" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="15" t="s">
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:8" s="11" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A7" s="15" t="s">
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="1:8" s="8" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="1:8" s="12" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="15" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" s="9" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A9" s="15" t="s">
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A9" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="1:8" s="12" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="15" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:8" s="9" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="15" t="s">
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="15" t="s">
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="15" t="s">
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" s="8" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" s="14" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="15" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" s="10" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A15" s="15" t="s">
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A15" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="15" t="s">
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A17" s="15" t="s">
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
+      <c r="A17" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" s="12" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="15" t="s">
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3104,322 +3101,322 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="17" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="16" t="s">
         <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="17" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="17" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>136</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="17" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="16" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="17" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="16" t="s">
         <v>137</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="17" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="17" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="17" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="17" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB366698-D1FA-422F-96FE-01E8A8B5427A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C090301-F910-405A-87EA-D23C50E5F340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="StakeHolder" sheetId="3" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="UC (정제)" sheetId="2" r:id="rId3"/>
     <sheet name="FR" sheetId="4" r:id="rId4"/>
     <sheet name="CONST" sheetId="5" r:id="rId5"/>
-    <sheet name="UtilityTree" sheetId="7" r:id="rId6"/>
-    <sheet name="QA" sheetId="6" r:id="rId7"/>
+    <sheet name="QA" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
   <si>
     <t>품질 속성</t>
   </si>
@@ -782,15 +782,6 @@
     <t>[침해 테스트 시험에서 pVM 소유 메모리로부터 읽힌 바이트 수 = 0건]</t>
   </si>
   <si>
-    <t>1순위</t>
-  </si>
-  <si>
-    <t>2순위</t>
-  </si>
-  <si>
-    <t>3순위</t>
-  </si>
-  <si>
     <t>확장성 (Workload 수용)</t>
   </si>
   <si>
@@ -815,567 +806,19 @@
     <t>[Workload 추가 전후 diff에서 Framework 코어 디렉터리 변경 라인 수 = 0 LoC]</t>
   </si>
   <si>
-    <t>4순위</t>
-  </si>
-  <si>
     <t>[도메인 간 dma-buf 버퍼 전달 시 memcpy 호출 횟수 = 0회]</t>
   </si>
   <si>
-    <t>5순위</t>
-  </si>
-  <si>
     <t>[(Workload 서비스 재개 시각) - (장애 주입 시각) &lt;= 3초]</t>
   </si>
   <si>
-    <t>6순위</t>
-  </si>
-  <si>
     <t>[(격리 메모리 - 비격리 메모리) &lt;= 256MB, (격리 전력 - 비격리 전력) / 비격리 전력 &lt;= 5%]</t>
   </si>
   <si>
-    <t>7순위</t>
-  </si>
-  <si>
     <t>[(전체 공격 벡터 항목 - 미커버 항목) / 전체 항목 = 100%]</t>
   </si>
   <si>
-    <t>8순위</t>
-  </si>
-  <si>
     <t>[Secure OS 교체 전후 diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
-  </si>
-  <si>
-    <t>9순위</t>
-  </si>
-  <si>
-    <t>QA-C ID</t>
-  </si>
-  <si>
-    <t>QA-M ID</t>
-  </si>
-  <si>
-    <t>응답 측정치</t>
-  </si>
-  <si>
-    <t>측정 방법</t>
-  </si>
-  <si>
-    <t>수치 설정 근거</t>
-  </si>
-  <si>
-    <t>근거 유형 / 확보 방법</t>
-  </si>
-  <si>
-    <t>QA-C-01</t>
-  </si>
-  <si>
-    <t>QA-M-01</t>
-  </si>
-  <si>
-    <t>공격 벡터 차단율 100%</t>
-  </si>
-  <si>
-    <t>보안 속성은 부분 달성이 무의미하며, 식별된 공격 전부 차단이 합격 기준</t>
-  </si>
-  <si>
-    <t>QA-M-02</t>
-  </si>
-  <si>
-    <t>격리 메모리 노출 0건</t>
-  </si>
-  <si>
-    <t>공격 실행 중 pVM 소유 메모리에서 실제로 읽힌 바이트와 노출 이벤트 수를 계측</t>
-  </si>
-  <si>
-    <t>단 1건의 노출로 기밀성 침해가 성립하므로 목표값은 0건이어야 함</t>
-  </si>
-  <si>
-    <t>QA-C-02</t>
-  </si>
-  <si>
-    <t>QA-M-03</t>
-  </si>
-  <si>
-    <t>30fps 유지</t>
-  </si>
-  <si>
-    <t>파이프라인 출구에서 초당 처리 프레임 수를 카운트하고 이동 평균으로 지속 유지 여부를 판정</t>
-  </si>
-  <si>
-    <t>30fps는 카메라/영상 산업의 표준 기본 프레임율이며 레퍼런스 시나리오의 센서 출력 규격</t>
-  </si>
-  <si>
-    <t>QA-M-04</t>
-  </si>
-  <si>
-    <t>E2E 지연 100ms 이하</t>
-  </si>
-  <si>
-    <t>센서 timestamp와 판단 결과 산출 시각의 차이를 프레임별 계측하고 p99로 평가</t>
-  </si>
-  <si>
-    <t>HCI 기준에서 0.1초는 즉각 반응으로 인지되는 상한</t>
-  </si>
-  <si>
-    <t>QA-M-05</t>
-  </si>
-  <si>
-    <t>비격리 대비 성능 저하 10% 이내</t>
-  </si>
-  <si>
-    <t>KVM 계열 가상화의 I/O 경로 오버헤드가 문헌상 통상 5~15%로 보고되는 범위에서 상한 설정</t>
-  </si>
-  <si>
-    <t>QA-C-03</t>
-  </si>
-  <si>
-    <t>QA-M-06</t>
-  </si>
-  <si>
-    <t>프레임 전달 복사 횟수 0회</t>
-  </si>
-  <si>
-    <t>dma-buf 등 버퍼 전달 경로에서 코드 경로와 trace로 복사 횟수를 확인</t>
-  </si>
-  <si>
-    <t>zero-copy 주장을 만족하려면 프레임 데이터 복사가 없어야 함</t>
-  </si>
-  <si>
-    <t>QA-M-07</t>
-  </si>
-  <si>
-    <t>도메인 간 프레임당 전달 지연 5ms 이하</t>
-  </si>
-  <si>
-    <t>송신 도메인 기록 완료 시각과 수신 도메인 접근 가능 시각의 차이를 계측</t>
-  </si>
-  <si>
-    <t>30fps 프레임 예산 33.3ms 중 약 15%를 전달 단계에 배분한 값</t>
-  </si>
-  <si>
-    <t>QA-C-04</t>
-  </si>
-  <si>
-    <t>QA-M-08</t>
-  </si>
-  <si>
-    <t>기존 프레임율 유지, Drop 0%</t>
-  </si>
-  <si>
-    <t>Host 일반 촬영과 보안 파이프라인을 동시 실행하며 양측의 프레임 drop 수를 카운트</t>
-  </si>
-  <si>
-    <t>프레임 drop은 사용자 체감 기능 실패와 실시간성 위반으로 이어지므로 0%가 기능 성립 조건</t>
-  </si>
-  <si>
-    <t>QA-M-09</t>
-  </si>
-  <si>
-    <t>사용 주체 전환 1ms 이하</t>
-  </si>
-  <si>
-    <t>사용 완료 확인, 잔류 데이터 소거, S2MPU 재설정, 재바인딩 구간의 소요 시간을 계측</t>
-  </si>
-  <si>
-    <t>33.3ms 프레임 간격의 약 3%로, 전환이 프레임 스케줄에 영향을 주지 않도록 배분</t>
-  </si>
-  <si>
-    <t>QA-C-05</t>
-  </si>
-  <si>
-    <t>QA-M-10</t>
-  </si>
-  <si>
-    <t>추가 메모리 256MB 이하</t>
-  </si>
-  <si>
-    <t>Framework+pVM 2개 상시 운용 상태와 비격리 구성의 시스템 메모리 사용량 차이를 계측</t>
-  </si>
-  <si>
-    <t>AVF Microdroid pVM이 통상 128~256MB급으로 운용되는 공개 구성 사례를 기준으로 추정</t>
-  </si>
-  <si>
-    <t>QA-M-11</t>
-  </si>
-  <si>
-    <t>전력 증가 5% 이내</t>
-  </si>
-  <si>
-    <t>전력 계측 장비 또는 PMIC 텔레메트리로 통상 운용 평균 소비 전력을 비교</t>
-  </si>
-  <si>
-    <t>현재 객관적 근거가 부족하므로 제품 배터리 가동시간 요구에서 역산해야 함</t>
-  </si>
-  <si>
-    <t>QA-C-06</t>
-  </si>
-  <si>
-    <t>QA-M-12</t>
-  </si>
-  <si>
-    <t>Framework 코어 수정 0 LoC</t>
-  </si>
-  <si>
-    <t>신규 Workload 추가 전후 git diff에서 Framework 코어 모듈 변경 라인 수를 카운트</t>
-  </si>
-  <si>
-    <t>플러그인 아키텍처의 개방-폐쇄 원칙상 코어 무수정이 목표 조건</t>
-  </si>
-  <si>
-    <t>QA-C-07</t>
-  </si>
-  <si>
-    <t>QA-M-13</t>
-  </si>
-  <si>
-    <t>Secure OS 외 모듈 수정 파일 0개</t>
-  </si>
-  <si>
-    <t>Secure OS 교체 작업 diff에서 Secure OS 패키지 외부 변경 파일 수를 카운트</t>
-  </si>
-  <si>
-    <t>인터페이스 추상화 목표의 정의상 Secure OS 외부 변경이 없어야 함</t>
-  </si>
-  <si>
-    <t>QA-C-08</t>
-  </si>
-  <si>
-    <t>QA-M-14</t>
-  </si>
-  <si>
-    <t>Host/타 pVM 다운타임 0</t>
-  </si>
-  <si>
-    <t>pVM 강제 kill, 게스트 커널 panic 등 장애 주입 중 Host 서비스와 타 pVM 응답 중단 시간을 계측</t>
-  </si>
-  <si>
-    <t>격리 구조의 정의상 장애 비전파가 성립해야 함</t>
-  </si>
-  <si>
-    <t>불변 조건</t>
-  </si>
-  <si>
-    <t>QA-M-15</t>
-  </si>
-  <si>
-    <t>장애 pVM 재시작 3초 이내</t>
-  </si>
-  <si>
-    <t>장애 검출 시각부터 pVM 재시작 완료와 Workload 서비스 재개 시각까지 계측</t>
-  </si>
-  <si>
-    <t>AVF pVM(Microdroid) 부팅이 초 단위로 보고되는 점에 기반한 초기 목표</t>
-  </si>
-  <si>
-    <t>QA-C-09</t>
-  </si>
-  <si>
-    <t>QA-M-16</t>
-  </si>
-  <si>
-    <t>자동화 시험 커버리지 100%</t>
-  </si>
-  <si>
-    <t>시험되지 않은 격리 주장 항목이 있으면 검증 완료 주장이 성립하지 않음</t>
-  </si>
-  <si>
-    <t>QA-M-17</t>
-  </si>
-  <si>
-    <t>회귀 반복 실행 가능</t>
-  </si>
-  <si>
-    <t>CI에서 동일 공격/격리 테스트가 반복 실행 가능한지 확인</t>
-  </si>
-  <si>
-    <t>격리 보장은 반복 가능한 회귀 검증 체계가 있어야 유지 가능</t>
-  </si>
-  <si>
-    <r>
-      <t>표준</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 타겟 카메라 센서 데이터시트로 확정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>문헌 + 가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 로봇 제조사의 인지-행동 루프 요구 지연으로 보정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. PoC 실측 뒤 제조사 협의로 보정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 타겟 보드에서 dma-buf 전달 경로 검증</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>산술 도출 + 가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. memcpy/dma-buf 마이크로벤치마크로 검증</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 순간 부하의 예외 허용 여부는 제조사와 협의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>산술 도출 + 가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 전환 시퀀스 마이크로벤치마크로 보정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>유사 시스템 참조 + 가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 타겟 SoC 메모리 예산표로 확정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. PoC 전력 프로파일링으로 보정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 코어 경계를 설계 단계에서 명시</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 후보 Secure OS의 GP TEE API 준수 여부를 사전 확인</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>가정치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. PoC 부팅 시간과 서비스 허용 중단 시간으로 확정</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. GP TEE PP 공격 목록을 기준으로 커버리지 분모 확보</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. CI 실행 로그와 테스트 결과로 확인</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>중요도</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>난이도</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Host 루트 권한 침해 테스트 도구로 공격 벡터를 전 항목 실행하고, 차단된 항목 비율을 산출</t>
-  </si>
-  <si>
-    <t>동일 HW에서 비격리 pipeline과 격리 구성의 fps/지연을 비교</t>
-  </si>
-  <si>
-    <t>격리 요구사항별 공격 벡터와 자동화 테스트의 매핑표를 작성하고 미커버 항목 수를 카운트</t>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 공격 벡터는 GP TEE PP 공격 목록과 Android VRP의 pKVM Boundary Defeat 사례를 기준으로 구성 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>99_security_qa_metrics.md</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> 참조)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>불변 조건</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>. 공격 벡터의 완전성을 GP TEE PP 기준으로 보강</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1417,7 +860,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1473,40 +916,6 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFA31515"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1516,7 +925,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1539,42 +948,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1598,30 +978,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1647,59 +1003,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>83819</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1025" name="image-0" descr="uml diagram">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CB921F1-E588-C1EB-BA96-2DFA92D3BA54}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="754380" y="10424160"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2569,7 +1872,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>112</v>
@@ -2645,431 +1948,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3144ED8-EE6E-425D-A2F2-C1B2877442CC}">
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="2" width="9.8984375" customWidth="1"/>
-    <col min="3" max="3" width="17.796875" customWidth="1"/>
-    <col min="4" max="6" width="43.19921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A4" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="1:8" ht="40.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A5" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="1:8" s="8" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A7" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" s="9" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A9" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="1:8" s="9" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" spans="1:8" s="8" customFormat="1" ht="61.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="1:8" s="10" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A15" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" ht="61.2" x14ac:dyDescent="0.4">
-      <c r="A17" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="1:8" s="9" customFormat="1" ht="41.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -3101,274 +1979,274 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>133</v>
+      <c r="F2" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="17"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>139</v>
+      <c r="B4" s="8" t="s">
+        <v>136</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>134</v>
+      <c r="F4" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="17"/>
+        <v>138</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>135</v>
+      <c r="F6" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="17"/>
+        <v>139</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>136</v>
+      <c r="B8" s="8" t="s">
+        <v>133</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>144</v>
+      <c r="F8" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>146</v>
+      <c r="F10" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+        <v>141</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>137</v>
+      <c r="B12" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>148</v>
+      <c r="F12" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+        <v>142</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>150</v>
+      <c r="F14" s="9">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+        <v>143</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>138</v>
+      <c r="B16" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>152</v>
+      <c r="F16" s="9">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
+        <v>144</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>154</v>
+      <c r="F18" s="9">
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -3421,4 +2299,68 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="23.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,18 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C090301-F910-405A-87EA-D23C50E5F340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC62146-2593-496D-AE16-26FEA58B69B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
-    <sheet name="StakeHolder" sheetId="3" r:id="rId1"/>
-    <sheet name="VOS" sheetId="1" r:id="rId2"/>
-    <sheet name="UC (정제)" sheetId="2" r:id="rId3"/>
-    <sheet name="FR" sheetId="4" r:id="rId4"/>
-    <sheet name="CONST" sheetId="5" r:id="rId5"/>
-    <sheet name="QA" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
+    <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
+    <sheet name="StakeHolder" sheetId="3" r:id="rId2"/>
+    <sheet name="VOS" sheetId="1" r:id="rId3"/>
+    <sheet name="UC (정제)" sheetId="2" r:id="rId4"/>
+    <sheet name="FR" sheetId="4" r:id="rId5"/>
+    <sheet name="CONST" sheetId="5" r:id="rId6"/>
+    <sheet name="QA" sheetId="6" r:id="rId7"/>
+    <sheet name="Matrix" sheetId="8" r:id="rId8"/>
+    <sheet name="pKVM interfacer" sheetId="10" r:id="rId9"/>
+    <sheet name="Scenario Steps" sheetId="11" r:id="rId10"/>
+    <sheet name="Sheet3" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="207">
   <si>
     <t>품질 속성</t>
   </si>
@@ -306,9 +310,6 @@
     <t>신규 보안 시나리오를 Framework 수정 없이 수용해야 한다.</t>
   </si>
   <si>
-    <t>2026-10-30까지 제한된 인력으로 E2E 데모를 완료해야 한다.</t>
-  </si>
-  <si>
     <t>Secure Camera와 Secure AI 도메인은 독립적으로 동시 운용되어야 한다.</t>
   </si>
   <si>
@@ -390,9 +391,6 @@
     <t>Android 스택에 의존하지 않고 Linux에서 네이티브로 동작한다.</t>
   </si>
   <si>
-    <t>CONST-02</t>
-  </si>
-  <si>
     <t>pKVM 커널 전제</t>
   </si>
   <si>
@@ -417,9 +415,6 @@
     <t>Secure OS/Framework 버전이 변경될 때 정의된 인터페이스만으로 대응하고 재이식하지 않는다.</t>
   </si>
   <si>
-    <t>pVM이 비정상 종료/오동작해도 Host/다른 pVM/로봇 기본 동작은 유지된다.</t>
-  </si>
-  <si>
     <t>격리 검증이 필요할 때 Host 침해를 모사한 시험으로 객관적으로 검증할 수 있다.</t>
   </si>
   <si>
@@ -772,67 +767,100 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>CONST-01</t>
+    <t>우선순위</t>
+  </si>
+  <si>
+    <t>[침해 테스트 시험에서 pVM 소유 메모리로부터 읽힌 바이트 수 = 0건]</t>
+  </si>
+  <si>
+    <t>확장성 (Workload 수용)</t>
+  </si>
+  <si>
+    <t>시험 용이성 (격리 검증)</t>
+  </si>
+  <si>
+    <t>보안 (HW 접근 격리)</t>
+  </si>
+  <si>
+    <t>Camera/AI HW 사용 주체 전환 시 배타적 접근이 항상 보장된다.</t>
+  </si>
+  <si>
+    <t>[S2MPU 권한 상태 로그에서 두 주체의 권한 중첩 구간 없음 (위반 횟수 = 0)]</t>
+  </si>
+  <si>
+    <t>[전체 파이프라인에 대해서 (비격리 fps - 격리 fps) / 비격리 fps &lt;= 10%]</t>
+  </si>
+  <si>
+    <t>[도메인 간 dma-buf 버퍼 전달 시 memcpy 호출 횟수 = 0회]</t>
+  </si>
+  <si>
+    <t>[(격리 메모리 - 비격리 메모리) &lt;= 256MB, (격리 전력 - 비격리 전력) / 비격리 전력 &lt;= 5%]</t>
+  </si>
+  <si>
+    <t>[(전체 공격 벡터 항목 - 미커버 항목) / 전체 항목 = 100%]</t>
+  </si>
+  <si>
+    <t>[Secure OS 교체 전후 diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secure OS ENC/DEC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명령</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전송</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>우선순위</t>
-  </si>
-  <si>
-    <t>[침해 테스트 시험에서 pVM 소유 메모리로부터 읽힌 바이트 수 = 0건]</t>
-  </si>
-  <si>
-    <t>확장성 (Workload 수용)</t>
-  </si>
-  <si>
-    <t>가용성 (pVM 장애 격리)</t>
-  </si>
-  <si>
-    <t>시험 용이성 (격리 검증)</t>
-  </si>
-  <si>
-    <t>보안 (HW 접근 격리)</t>
-  </si>
-  <si>
-    <t>Camera/AI HW 사용 주체 전환 시 배타적 접근이 항상 보장된다.</t>
-  </si>
-  <si>
-    <t>[S2MPU 권한 상태 로그에서 두 주체의 권한 중첩 구간 없음 (위반 횟수 = 0)]</t>
-  </si>
-  <si>
-    <t>[전체 파이프라인에 대해서 (비격리 fps - 격리 fps) / 비격리 fps &lt;= 10%]</t>
-  </si>
-  <si>
-    <t>[Workload 추가 전후 diff에서 Framework 코어 디렉터리 변경 라인 수 = 0 LoC]</t>
-  </si>
-  <si>
-    <t>[도메인 간 dma-buf 버퍼 전달 시 memcpy 호출 횟수 = 0회]</t>
-  </si>
-  <si>
-    <t>[(Workload 서비스 재개 시각) - (장애 주입 시각) &lt;= 3초]</t>
-  </si>
-  <si>
-    <t>[(격리 메모리 - 비격리 메모리) &lt;= 256MB, (격리 전력 - 비격리 전력) / 비격리 전력 &lt;= 5%]</t>
-  </si>
-  <si>
-    <t>[(전체 공격 벡터 항목 - 미커버 항목) / 전체 항목 = 100%]</t>
-  </si>
-  <si>
-    <t>[Secure OS 교체 전후 diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Secure OS ENC/DEC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>명령</t>
+    <t>O</t>
+  </si>
+  <si>
+    <t>CS-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS-02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QA-07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
     </r>
     <r>
       <rPr>
@@ -851,7 +879,1483 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>전송</t>
+      <t>도출되었지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중요 품질속성 아님</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QA-08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도출되었지만 중요 품질속성 아님</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>년도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사고사례</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>영향</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkada 보안카메라 해킹 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>295만 달러 합의금 발생</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>iRobot Roomba / Scale AI 학습 이미지 유출</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>iRobot은 Scale AI와 관계를 종료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ecovacs Deebot X2 로봇 청소기 해킹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라/스피커 무단 원격 제어로 가정 내부 영상 노출</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>국내 IP카메라 12만대 해킹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>가정내 영상 무단 접근 / 유출</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>규격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준수</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">GlobalPlatform </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>규격을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준수해야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한다.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VOS-12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS-03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문서화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요구는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설계에서 제외</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관련</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사항으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조 설계에서 제외</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA-06</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2026-12-31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제한된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인력으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> E2E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데모를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완료해야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가용성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (pVM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장애</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>격리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KVM_ 인터페이스 기준 pKVM 주요 기능 및 동작 비교</t>
+  </si>
+  <si>
+    <t>KVM_ 인터페이스 (ioctl)</t>
+  </si>
+  <si>
+    <t>일반 KVM에서의 동작</t>
+  </si>
+  <si>
+    <t>pKVM (Protected KVM)의 핵심 기능 및 활동</t>
+  </si>
+  <si>
+    <t>KVM_CREATE_VM</t>
+  </si>
+  <si>
+    <t>일반적인 가상 머신(VM) 인스턴스를 생성하고 제어 구조체를 초기화함.</t>
+  </si>
+  <si>
+    <r>
+      <t>KVM_VM_TYPE_ARM_PROTECTED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 플래그를 확인하여, 해당 VM을 **보호 대상(pVM)**으로 지정하고 호스트 커널의 접근 권한 박탈을 준비함.</t>
+    </r>
+  </si>
+  <si>
+    <t>KVM_SET_USER_MEMORY_REGION</t>
+  </si>
+  <si>
+    <t>게스트의 가상 메모리(IPA) 영역을 호스트의 물리 메모리(SPA)와 매핑함.</t>
+  </si>
+  <si>
+    <t>할당된 게스트 메모리 영역을 **호스트 커널의 Stage-2 페이지 테이블에서 완전히 제거(Unmap)**하고, 소유권을 하이퍼바이저 격리 영역으로 이전(Donation)함.</t>
+  </si>
+  <si>
+    <t>KVM_CREATE_VCPU</t>
+  </si>
+  <si>
+    <t>가상 CPU를 생성하고 레지스터 상태를 초기화함.</t>
+  </si>
+  <si>
+    <t>보호된 가상 CPU를 생성하며, 호스트 커널(EL1)이 게스트의 CPU 레지스터 상태를 임의로 읽거나 쓰지 못하도록 하이퍼바이저(EL2) 내부 전용 구조체에 격리함.</t>
+  </si>
+  <si>
+    <t>KVM_RUN</t>
+  </si>
+  <si>
+    <t>게스트 OS 코드를 실행하며, I/O 등이 발생하면 호스트로 제어권을 넘김.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">콘텍스트 스위칭 시 호스트 레지스터를 완벽히 지우고 게스트를 실행함. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>민감한 트랩(Trap)은 호스트로 넘기지 않고 EL2에서 직접 처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>하여 정보 유출을 차단함.</t>
+    </r>
+  </si>
+  <si>
+    <t>가상 인터럽트 컨트롤러 등 가상 하드웨어 디바이스를 생성함.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">호스트가 인터럽트 설정을 조작하여 격리 벽을 허무는 것을 막기 위해, 호스트의 명령을 EL2에서 가로채(Trap) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>섀도 구조체(Shadow Structures)로 안전하게 에뮬레이션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>함.</t>
+    </r>
+  </si>
+  <si>
+    <t>vCPU의 특정 레지스터 값을 직접 설정하거나 읽어옴.</t>
+  </si>
+  <si>
+    <t>부팅 시점 외에는 호스트 커널이 pVM vCPU의 핵심 시스템 레지스터를 직접 수정하거나 엿보는 동작을 거부하고 제어권을 방어함.</t>
+  </si>
+  <si>
+    <r>
+      <t>KVM_SET_ONE_REG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> KVM_GET_ONE_REG</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KVM_CREATE_DEVICE (e.g., vGIC, vITS)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>단계</t>
+  </si>
+  <si>
+    <t>요청/동작</t>
+  </si>
+  <si>
+    <t>Host Application이 파이프라인 시작 요청</t>
+  </si>
+  <si>
+    <t>요청 권한 및 정책 확인</t>
+  </si>
+  <si>
+    <t>Workload 이미지 검증</t>
+  </si>
+  <si>
+    <t>pVM 생성 및 자원 할당</t>
+  </si>
+  <si>
+    <t>Workload 탑재 및 실행</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI HW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추론 수행</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Camera HW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캡쳐 수행</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Camera </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>암호화 저장</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Camera </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프레임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전달</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>암호화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t>Host Application</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>으로 결과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전달</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장애 처리 혹은 파이프라인 종료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RPC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채널</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구성</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[Host/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> VM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비정상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동작</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비정상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동작</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)]</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Workload </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> diff</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Framework </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = 0 LoC]</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>pVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비정상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오동작해도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Host/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pVM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동작은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유지된다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -860,7 +2364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -916,16 +2420,70 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA31515"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -948,13 +2506,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -979,6 +2565,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -987,6 +2594,45 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1301,16 +2947,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA4CBF-2B00-47DE-B890-6C9CADE53CC2}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="2" max="3" width="22.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10">
+        <v>2021</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FC3EE2-E578-4F70-869F-9EBF67B87D76}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="5.09765625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" s="29" customFormat="1">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="28"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="28">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="28">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="28">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="28">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="28">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="28">
+        <v>13</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="16.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>46</v>
       </c>
@@ -1321,7 +3188,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
         <v>54</v>
       </c>
@@ -1332,7 +3199,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
         <v>55</v>
       </c>
@@ -1343,7 +3210,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1354,7 +3221,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
         <v>66</v>
       </c>
@@ -1365,7 +3232,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
         <v>57</v>
       </c>
@@ -1376,7 +3243,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
         <v>48</v>
       </c>
@@ -1387,7 +3254,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
@@ -1398,7 +3265,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
         <v>52</v>
       </c>
@@ -1407,208 +3274,6 @@
       </c>
       <c r="C9" s="5" t="s">
         <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.19921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1618,135 +3283,200 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="26.8984375" customWidth="1"/>
-    <col min="3" max="3" width="69" customWidth="1"/>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1755,9 +3485,146 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="69" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
@@ -1765,7 +3632,7 @@
     <col min="5" max="5" width="6.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1782,15 +3649,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -1799,7 +3666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1807,7 +3674,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -1816,7 +3683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
@@ -1824,7 +3691,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>33</v>
@@ -1833,15 +3700,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>36</v>
@@ -1850,15 +3717,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>39</v>
@@ -1867,78 +3734,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="14.296875" customWidth="1"/>
-    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1948,9 +3758,80 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="2" max="2" width="14.296875" customWidth="1"/>
+    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="99.8984375" customWidth="1"/>
@@ -1958,7 +3839,7 @@
     <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1975,278 +3856,278 @@
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="C4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="16">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="16"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D10" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="E10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="7" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -2301,62 +4182,539 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" customWidth="1"/>
+    <col min="2" max="16" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
+    <row r="1" spans="1:16">
+      <c r="A1" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="12"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="12"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B14:P14"/>
+    <mergeCell ref="B15:P15"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="B7:P7"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="25.796875" customWidth="1"/>
+    <col min="2" max="2" width="64.09765625" customWidth="1"/>
+    <col min="3" max="3" width="40.8984375" customWidth="1"/>
+    <col min="4" max="4" width="25.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1"/>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A4" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="42" thickBot="1">
+      <c r="A5" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="42" thickBot="1">
+      <c r="A6" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="42" thickBot="1">
+      <c r="A7" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="42" thickBot="1">
+      <c r="A8" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="27.6">
+      <c r="A9" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC62146-2593-496D-AE16-26FEA58B69B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC03124-1655-445D-9133-5684159717FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="11" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,9 @@
     <sheet name="Matrix" sheetId="8" r:id="rId8"/>
     <sheet name="pKVM interfacer" sheetId="10" r:id="rId9"/>
     <sheet name="Scenario Steps" sheetId="11" r:id="rId10"/>
-    <sheet name="Sheet3" sheetId="12" r:id="rId11"/>
+    <sheet name="ContextView" sheetId="12" r:id="rId11"/>
+    <sheet name="DP" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="248">
   <si>
     <t>품질 속성</t>
   </si>
@@ -2358,13 +2360,730 @@
       <t>.</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host Application</t>
+  </si>
+  <si>
+    <t>Normal Camera Application</t>
+  </si>
+  <si>
+    <t>pKVM(EL2 Hypervisor)</t>
+  </si>
+  <si>
+    <t>Camera HW Driver</t>
+  </si>
+  <si>
+    <t>AI HW Driver</t>
+  </si>
+  <si>
+    <t>S2MPU/DMA HW Driver</t>
+  </si>
+  <si>
+    <t>Secure OS(TEE)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pVM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생성/운용 및 Workload 탑재/실행을 요청하는 주체</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Workload</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Camera Workload</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">추론시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">가속을 사용하기 위한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kernel Driver</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Camera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">영상을 획득하기 위한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kernel Driver</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>접근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>격리를 제어하는 Driver</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ENC/DEC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환경</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>pVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탑재되어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Secure Camera</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영상 획득을 담당</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>pVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">탑재되어 Secure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추론을 담당</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secure Camera </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">사용과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>충돌될</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Camera </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주체</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pVM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생성과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CPU/Memroy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자원 제어를 담당</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외부</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="3"/>
+      </rPr>
+      <t>Module</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>역할</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DP1</t>
+  </si>
+  <si>
+    <t>기밀성, 확장성, 가용성을 위한 pVM 관리 골격 설계</t>
+  </si>
+  <si>
+    <t>DP2</t>
+  </si>
+  <si>
+    <t>무결성 보장을 위한 보안 Workload 실행 방식 설계</t>
+  </si>
+  <si>
+    <t>DP3</t>
+  </si>
+  <si>
+    <t>성능(통신 오버헤드)을 위한 zero-copy 보안 채널 구조 설계</t>
+  </si>
+  <si>
+    <t>DP4</t>
+  </si>
+  <si>
+    <t>성능(실시간 처리) 및 자원 효율을 위한 HW IP 중재 구조 설계</t>
+  </si>
+  <si>
+    <t>DP5</t>
+  </si>
+  <si>
+    <t>GP API Backward Compatibility를 위한 TrustZone 연동 구조 설계</t>
+  </si>
+  <si>
+    <t>DP6</t>
+  </si>
+  <si>
+    <t>보안(기밀성)을 위한 Secure Storage 구조 설계</t>
+  </si>
+  <si>
+    <t>제목</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>관련 Driver</t>
+  </si>
+  <si>
+    <t>FR-01, FR-02, FR-05, QA-01, QA-04, QA-06, CS-01, CS-02</t>
+  </si>
+  <si>
+    <t>FR-01, FR-05, QA-01, QA-04, CS-01, CS-02</t>
+  </si>
+  <si>
+    <t>FR-03, FR-04, QA-01, QA-02, QA-03, QA-05, CS-01, CS-02</t>
+  </si>
+  <si>
+    <t>FR-03, QA-01, QA-02, QA-03, CS-01, CS-02</t>
+  </si>
+  <si>
+    <t>FR-06, QA-01, QA-03, QA-05, CS-03</t>
+  </si>
+  <si>
+    <t>FR-06, QA-01, QA-03, CS-03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2468,8 +3187,71 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2482,8 +3264,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2534,13 +3322,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD6D6D6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD6D6D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2580,26 +3383,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -2633,6 +3418,42 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2949,9 +3770,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA4CBF-2B00-47DE-B890-6C9CADE53CC2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="22.59765625" customWidth="1"/>
+    <col min="2" max="3" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3018,9 +3839,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FC3EE2-E578-4F70-869F-9EBF67B87D76}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="5.09765625" style="27" customWidth="1"/>
+    <col min="1" max="1" width="5.125" style="21" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
@@ -3034,14 +3855,14 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" s="29" customFormat="1">
-      <c r="A2" s="28">
+    <row r="2" spans="1:3" s="23" customFormat="1">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="28"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3">
@@ -3053,7 +3874,7 @@
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="28">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3071,7 +3892,7 @@
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="28">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3089,7 +3910,7 @@
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="28">
+      <c r="A8" s="22">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -3107,7 +3928,7 @@
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="28">
+      <c r="A10" s="22">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -3125,7 +3946,7 @@
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="28">
+      <c r="A12" s="22">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -3143,10 +3964,10 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="28">
+      <c r="A14" s="22">
         <v>13</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="24" t="s">
         <v>202</v>
       </c>
       <c r="C14" s="3"/>
@@ -3159,8 +3980,206 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="74.625" customWidth="1"/>
+    <col min="3" max="3" width="57.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="31"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="32"/>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="32"/>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="32"/>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="32"/>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="32"/>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="32"/>
+    </row>
+    <row r="8" spans="1:3" ht="18" thickBot="1">
+      <c r="A8" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="32"/>
+    </row>
+    <row r="9" spans="1:3" ht="18" thickBot="1">
+      <c r="A9" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="32"/>
+    </row>
+    <row r="10" spans="1:3" ht="18" thickBot="1">
+      <c r="A10" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="32"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E651437D-FAC7-4432-A76A-B730DB461C13}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3170,11 +4189,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3285,10 +4304,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.19921875" customWidth="1"/>
+    <col min="3" max="3" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3487,9 +4506,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3624,12 +4643,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3649,7 +4668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="21">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -3683,7 +4702,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="21">
       <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
@@ -3700,7 +4719,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="21">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -3734,7 +4753,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="21">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -3760,9 +4779,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="14.296875" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3831,12 +4850,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="99.8984375" customWidth="1"/>
-    <col min="4" max="5" width="5.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.875" customWidth="1"/>
+    <col min="4" max="5" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3860,322 +4879,322 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="25" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="16"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="25" t="s">
         <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="27">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="16"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="27">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="16"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="25" t="s">
         <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="27">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="27">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
       <c r="C11" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="28" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="25" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="25" t="s">
         <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="27">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="27">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4185,9 +5204,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
   <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" customWidth="1"/>
+    <col min="1" max="1" width="7.375" customWidth="1"/>
     <col min="2" max="16" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4319,23 +5338,23 @@
       <c r="A5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
@@ -4365,23 +5384,23 @@
       <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
@@ -4525,45 +5544,45 @@
       <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
@@ -4594,22 +5613,22 @@
       <c r="B17" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
       <c r="M17" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4626,94 +5645,94 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="25.796875" customWidth="1"/>
-    <col min="2" max="2" width="64.09765625" customWidth="1"/>
-    <col min="3" max="3" width="40.8984375" customWidth="1"/>
-    <col min="4" max="4" width="25.796875" customWidth="1"/>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="64.125" customWidth="1"/>
+    <col min="3" max="3" width="40.875" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:3" ht="17.25">
+      <c r="A1" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1"/>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="21" t="s">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
+    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A3" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.2" thickBot="1">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A4" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="17" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="42" thickBot="1">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:3" ht="43.5" thickBot="1">
+      <c r="A5" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="17" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="42" thickBot="1">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:3" ht="43.5" thickBot="1">
+      <c r="A6" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="17" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="42" thickBot="1">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:3" ht="45" thickBot="1">
+      <c r="A7" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="17" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="42" thickBot="1">
-      <c r="A8" s="25" t="s">
+    <row r="8" spans="1:3" ht="45" thickBot="1">
+      <c r="A8" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="27.6">
-      <c r="A9" s="25" t="s">
+    <row r="9" spans="1:3" ht="28.5">
+      <c r="A9" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="20" t="s">
         <v>185</v>
       </c>
     </row>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC03124-1655-445D-9133-5684159717FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F3D21C-41EC-4FC6-BD3C-F118385EFAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="11" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="12" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -25,8 +25,12 @@
     <sheet name="Scenario Steps" sheetId="11" r:id="rId10"/>
     <sheet name="ContextView" sheetId="12" r:id="rId11"/>
     <sheet name="DP" sheetId="13" r:id="rId12"/>
-    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
+    <sheet name="New DP" sheetId="14" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="15" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'New DP'!$A$1:$E$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="330">
   <si>
     <t>품질 속성</t>
   </si>
@@ -3077,13 +3081,478 @@
   </si>
   <si>
     <t>FR-06, QA-01, QA-03, CS-03</t>
+  </si>
+  <si>
+    <t>Decision Point</t>
+  </si>
+  <si>
+    <t>주요 품질속성</t>
+  </si>
+  <si>
+    <t>DP-A1</t>
+  </si>
+  <si>
+    <t>pVM 관리 골격(제어 평면) 구조</t>
+  </si>
+  <si>
+    <t>기밀성, 확장성, 가용성</t>
+  </si>
+  <si>
+    <t>DP-A2</t>
+  </si>
+  <si>
+    <t>Host 노출 API 계층과 권한 결정 지점</t>
+  </si>
+  <si>
+    <t>사용성, 보안, 상호운용성</t>
+  </si>
+  <si>
+    <t>DP-A3</t>
+  </si>
+  <si>
+    <t>장애 검출·복구 정책 구조</t>
+  </si>
+  <si>
+    <t>가용성, 성능, 기밀성</t>
+  </si>
+  <si>
+    <t>DP-B1</t>
+  </si>
+  <si>
+    <t>pVM 게스트 실행 환경(페이로드 OS) 선택</t>
+  </si>
+  <si>
+    <t>기밀성, 확장성, 성능</t>
+  </si>
+  <si>
+    <t>DP-B2</t>
+  </si>
+  <si>
+    <t>pVM 프로비저닝 시점 전략</t>
+  </si>
+  <si>
+    <t>성능, 자원 효율, 가용성</t>
+  </si>
+  <si>
+    <t>DP-B3</t>
+  </si>
+  <si>
+    <t>Workload 신뢰 체인(검증 아키텍처)</t>
+  </si>
+  <si>
+    <t>무결성, 기밀성, 확장성</t>
+  </si>
+  <si>
+    <t>DP-C1</t>
+  </si>
+  <si>
+    <t>성능, 기밀성, 확장성</t>
+  </si>
+  <si>
+    <t>DP-C2</t>
+  </si>
+  <si>
+    <t>성능, 기밀성, 가용성</t>
+  </si>
+  <si>
+    <t>DP-C3</t>
+  </si>
+  <si>
+    <t>DMA 격리와 메모리 소유권 전환 프로토콜</t>
+  </si>
+  <si>
+    <t>기밀성, 성능, 안전성</t>
+  </si>
+  <si>
+    <t>DP-C4</t>
+  </si>
+  <si>
+    <t>민감 데이터 암복호화 실행 위치와 키 관리 경로</t>
+  </si>
+  <si>
+    <t>기밀성, 성능, 상호운용성</t>
+  </si>
+  <si>
+    <t>DP-D1</t>
+  </si>
+  <si>
+    <t>상호운용성, 기밀성, 확장성</t>
+  </si>
+  <si>
+    <t>DP-E1</t>
+  </si>
+  <si>
+    <t>pVM 자원 할당·스케줄링(QoS) 정책 구조</t>
+  </si>
+  <si>
+    <t>DP-E2</t>
+  </si>
+  <si>
+    <t>격리 증빙(Attestation)과 감사 증적 구조</t>
+  </si>
+  <si>
+    <t>시험 용이성, 규제 증빙, 기밀성</t>
+  </si>
+  <si>
+    <t>DP-E3</t>
+  </si>
+  <si>
+    <t>인터페이스 버저닝과 호환성 유지 전략</t>
+  </si>
+  <si>
+    <t>변경 용이성, 확장성</t>
+  </si>
+  <si>
+    <t>DP-P1</t>
+  </si>
+  <si>
+    <t>프레임 버퍼 풀과 Stage-2 매핑 수명주기 전략</t>
+  </si>
+  <si>
+    <t>성능, 기밀성</t>
+  </si>
+  <si>
+    <t>DP-P2</t>
+  </si>
+  <si>
+    <t>파이프라인 실행 모델과 도메인 간 알림 메커니즘</t>
+  </si>
+  <si>
+    <t>성능</t>
+  </si>
+  <si>
+    <t>DP-P3</t>
+  </si>
+  <si>
+    <t>AI 모델 가중치 로딩·캐싱 전략</t>
+  </si>
+  <si>
+    <t>성능, 기밀성, 자원 효율</t>
+  </si>
+  <si>
+    <t>DP-S1</t>
+  </si>
+  <si>
+    <t>Workload 패키지·Manifest 스키마 설계</t>
+  </si>
+  <si>
+    <t>확장성, 무결성</t>
+  </si>
+  <si>
+    <t>DP-S2</t>
+  </si>
+  <si>
+    <t>파이프라인 토폴로지 구성 방식</t>
+  </si>
+  <si>
+    <t>확장성, 성능</t>
+  </si>
+  <si>
+    <t>DP-S3</t>
+  </si>
+  <si>
+    <t>HW IP 추상화 계층과 신규 가속기 수용 구조</t>
+  </si>
+  <si>
+    <t>확장성, 변경 용이성</t>
+  </si>
+  <si>
+    <t>DP 채택</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미채택. Secure OS 제약사항</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미채택. AD와 관련없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미채택. AD와 연관없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미채택. SW구조설계와 연관성 떨어짐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(DP-A1 과 연계)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미채택. S2MPU 제약사항</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>미채택. 외부모듈에서 결정할 문제</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(DP-C2 와 연계)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>채택</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>중요도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도메인 간 프레임 전달 채널 구조</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HW IP 중재(Mediation) 위치와 공유 방식</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TrustZone Secure OS 공존 토폴로지
+(GP 표준 준수를 위한 TEE 연동 구조 설계)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>성능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기밀성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확장성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>기밀성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가용성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>기밀성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확장성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>기밀성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확장성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가용성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">도메인 간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">DMABUF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전달</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HW IP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중재</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TEE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연동</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pVM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3250,6 +3719,44 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3271,7 +3778,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3337,13 +3844,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3419,24 +3941,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3454,6 +3958,51 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3770,9 +4319,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA4CBF-2B00-47DE-B890-6C9CADE53CC2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="3" width="22.625" customWidth="1"/>
+    <col min="2" max="3" width="22.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3839,9 +4388,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FC3EE2-E578-4F70-869F-9EBF67B87D76}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="5.125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="5.09765625" style="21" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
@@ -3981,101 +4530,101 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="29.09765625" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="74.625" customWidth="1"/>
-    <col min="3" max="3" width="57.125" customWidth="1"/>
+    <col min="2" max="2" width="74.59765625" customWidth="1"/>
+    <col min="3" max="3" width="57.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A1" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="31"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="C1" s="25"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A2" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="C2" s="32"/>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="32" t="s">
+      <c r="C2" s="26"/>
+    </row>
+    <row r="3" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A3" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="C3" s="32"/>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="32" t="s">
+      <c r="C3" s="26"/>
+    </row>
+    <row r="4" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A4" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="32"/>
-    </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="32" t="s">
+      <c r="C4" s="26"/>
+    </row>
+    <row r="5" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A5" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="C5" s="32"/>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="32" t="s">
+      <c r="C5" s="26"/>
+    </row>
+    <row r="6" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A6" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="C6" s="32"/>
-    </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="32" t="s">
+      <c r="C6" s="26"/>
+    </row>
+    <row r="7" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A7" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="32"/>
-    </row>
-    <row r="8" spans="1:3" ht="18" thickBot="1">
-      <c r="A8" s="32" t="s">
+      <c r="C7" s="26"/>
+    </row>
+    <row r="8" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A8" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="C8" s="32"/>
-    </row>
-    <row r="9" spans="1:3" ht="18" thickBot="1">
-      <c r="A9" s="32" t="s">
+      <c r="C8" s="26"/>
+    </row>
+    <row r="9" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A9" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="32"/>
-    </row>
-    <row r="10" spans="1:3" ht="18" thickBot="1">
-      <c r="A10" s="32" t="s">
+      <c r="C9" s="26"/>
+    </row>
+    <row r="10" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A10" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="32"/>
+      <c r="C10" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -4086,87 +4635,87 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.25" customWidth="1"/>
+    <col min="2" max="2" width="63.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A1" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="25" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A2" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="26" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="36" t="s">
+    <row r="3" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A3" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="26" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="36" t="s">
+    <row r="4" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A4" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="26" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A5" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="26" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A6" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="26" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="36" t="s">
+    <row r="7" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A7" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="26" t="s">
         <v>247</v>
       </c>
     </row>
@@ -4178,8 +4727,428 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E651437D-FAC7-4432-A76A-B730DB461C13}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="13.8984375" style="41" customWidth="1"/>
+    <col min="2" max="2" width="48.09765625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="31.3984375" style="41" customWidth="1"/>
+    <col min="4" max="4" width="11.8984375" style="41" customWidth="1"/>
+    <col min="5" max="5" width="31.59765625" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="23" customFormat="1">
+      <c r="A2" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F2" s="23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="23" customFormat="1">
+      <c r="A3" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1">
+      <c r="A4" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="42"/>
+      <c r="E4" s="40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1">
+      <c r="A5" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="42"/>
+      <c r="E5" s="40" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="23" customFormat="1">
+      <c r="A6" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="23" customFormat="1">
+      <c r="A7" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="23" customFormat="1">
+      <c r="A8" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F8" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="23" customFormat="1">
+      <c r="A9" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1">
+      <c r="A10" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="40" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1">
+      <c r="A11" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="42"/>
+      <c r="E11" s="40" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="23" customFormat="1" ht="31.2">
+      <c r="A12" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F12" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1">
+      <c r="A13" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1">
+      <c r="A14" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="42"/>
+      <c r="E14" s="40" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1">
+      <c r="A15" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="40" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1">
+      <c r="A16" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" s="42"/>
+      <c r="E16" s="40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1">
+      <c r="A17" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="D17" s="42"/>
+      <c r="E17" s="40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1">
+      <c r="A18" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="D18" s="42"/>
+      <c r="E18" s="40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" hidden="1">
+      <c r="A19" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="40" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1">
+      <c r="A20" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="D20" s="42"/>
+      <c r="E20" s="40" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="23" customFormat="1">
+      <c r="A21" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18" thickBot="1"/>
+    <row r="25" spans="1:5" ht="18" thickBot="1">
+      <c r="A25" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18" thickBot="1">
+      <c r="A26" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="18" thickBot="1">
+      <c r="A27" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="18" thickBot="1">
+      <c r="A28" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E21" xr:uid="{E651437D-FAC7-4432-A76A-B730DB461C13}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C70C73-9E29-4A82-9F0B-6BA2B6E58795}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4189,11 +5158,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4304,10 +5273,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.25" customWidth="1"/>
+    <col min="3" max="3" width="57.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4506,9 +5475,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4643,12 +5612,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4668,7 +5637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="21">
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -4702,7 +5671,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="21">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
@@ -4719,7 +5688,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="21">
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -4753,7 +5722,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="21">
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -4779,9 +5748,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" customWidth="1"/>
     <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4850,12 +5819,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="99.875" customWidth="1"/>
-    <col min="4" max="5" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.8984375" customWidth="1"/>
+    <col min="4" max="5" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4879,322 +5848,322 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="31" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="31" t="s">
         <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="27"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="32">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="32"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="31" t="s">
         <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="32">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="27"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="32"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="31" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="32">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="34" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="32">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="31" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="32">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="31" t="s">
         <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="32">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="31" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="32">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5204,9 +6173,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
   <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="16" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5338,23 +6307,23 @@
       <c r="A5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
@@ -5384,23 +6353,23 @@
       <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
@@ -5544,45 +6513,45 @@
       <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
@@ -5645,21 +6614,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="64.125" customWidth="1"/>
-    <col min="3" max="3" width="40.875" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="1" max="1" width="25.69921875" customWidth="1"/>
+    <col min="2" max="2" width="64.09765625" customWidth="1"/>
+    <col min="3" max="3" width="40.8984375" customWidth="1"/>
+    <col min="4" max="4" width="25.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
-    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+    <row r="2" spans="1:3" ht="18" thickBot="1"/>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
       <c r="A3" s="15" t="s">
         <v>168</v>
       </c>
@@ -5670,7 +6639,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="29.25" thickBot="1">
+    <row r="4" spans="1:3" ht="28.2" thickBot="1">
       <c r="A4" s="16" t="s">
         <v>171</v>
       </c>
@@ -5681,7 +6650,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43.5" thickBot="1">
+    <row r="5" spans="1:3" ht="42" thickBot="1">
       <c r="A5" s="16" t="s">
         <v>174</v>
       </c>
@@ -5692,7 +6661,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" thickBot="1">
+    <row r="6" spans="1:3" ht="42" thickBot="1">
       <c r="A6" s="16" t="s">
         <v>177</v>
       </c>
@@ -5703,7 +6672,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" thickBot="1">
+    <row r="7" spans="1:3" ht="42" thickBot="1">
       <c r="A7" s="16" t="s">
         <v>180</v>
       </c>
@@ -5714,7 +6683,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" thickBot="1">
+    <row r="8" spans="1:3" ht="42" thickBot="1">
       <c r="A8" s="19" t="s">
         <v>188</v>
       </c>
@@ -5725,7 +6694,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.5">
+    <row r="9" spans="1:3" ht="27.6">
       <c r="A9" s="19" t="s">
         <v>187</v>
       </c>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -3865,7 +3865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3959,13 +3959,37 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3976,33 +4000,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4731,48 +4728,47 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="13.8984375" style="41" customWidth="1"/>
-    <col min="2" max="2" width="48.09765625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="31.3984375" style="41" customWidth="1"/>
-    <col min="4" max="4" width="11.8984375" style="41" customWidth="1"/>
-    <col min="5" max="5" width="31.59765625" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="41"/>
+    <col min="1" max="1" width="13.8984375" customWidth="1"/>
+    <col min="2" max="2" width="48.09765625" customWidth="1"/>
+    <col min="3" max="3" width="31.3984375" customWidth="1"/>
+    <col min="4" max="4" width="11.8984375" customWidth="1"/>
+    <col min="5" max="5" width="31.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="33" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="23" customFormat="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="32" t="s">
         <v>306</v>
       </c>
       <c r="F2" s="23">
@@ -4780,100 +4776,100 @@
       </c>
     </row>
     <row r="3" spans="1:6" s="23" customFormat="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="32" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:6" hidden="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="40" t="s">
+      <c r="D4" s="35"/>
+      <c r="E4" s="34" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6" hidden="1">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="40" t="s">
+      <c r="D5" s="35"/>
+      <c r="E5" s="34" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="23" customFormat="1">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="32" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="23" customFormat="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="32" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="23" customFormat="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="32" t="s">
         <v>306</v>
       </c>
       <c r="F8" s="23">
@@ -4881,19 +4877,19 @@
       </c>
     </row>
     <row r="9" spans="1:6" s="23" customFormat="1">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="32" t="s">
         <v>306</v>
       </c>
       <c r="F9" s="23">
@@ -4901,49 +4897,49 @@
       </c>
     </row>
     <row r="10" spans="1:6" hidden="1">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="40" t="s">
+      <c r="D10" s="35"/>
+      <c r="E10" s="34" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:6" hidden="1">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="40" t="s">
+      <c r="D11" s="35"/>
+      <c r="E11" s="34" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="23" customFormat="1" ht="31.2">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="32" t="s">
         <v>306</v>
       </c>
       <c r="F12" s="23">
@@ -4951,184 +4947,184 @@
       </c>
     </row>
     <row r="13" spans="1:6" hidden="1">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="40" t="s">
+      <c r="D13" s="35"/>
+      <c r="E13" s="34" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:6" hidden="1">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="35" t="s">
         <v>284</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="40" t="s">
+      <c r="D14" s="35"/>
+      <c r="E14" s="34" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:6" hidden="1">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="40" t="s">
+      <c r="D15" s="35"/>
+      <c r="E15" s="34" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:6" hidden="1">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="40" t="s">
+      <c r="D16" s="35"/>
+      <c r="E16" s="34" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:5" hidden="1">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="40" t="s">
+      <c r="D17" s="35"/>
+      <c r="E17" s="34" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:5" hidden="1">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="40" t="s">
+      <c r="D18" s="35"/>
+      <c r="E18" s="34" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:5" hidden="1">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="40" t="s">
+      <c r="D19" s="35"/>
+      <c r="E19" s="34" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:5" hidden="1">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="40" t="s">
+      <c r="D20" s="35"/>
+      <c r="E20" s="34" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="23" customFormat="1">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="31" t="s">
         <v>304</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="32" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" thickBot="1"/>
     <row r="25" spans="1:5" ht="18" thickBot="1">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="37" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" thickBot="1">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="37" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" thickBot="1">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="37" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" thickBot="1">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="37" t="s">
         <v>325</v>
       </c>
     </row>
@@ -5848,322 +5844,322 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="39" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="32"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="39" t="s">
         <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="41">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="32"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="41"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="41">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="32"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="39" t="s">
         <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="32"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="39" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="42" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="41">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="39" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="41">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="39" t="s">
         <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="41">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="31"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="41">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6307,23 +6303,23 @@
       <c r="A5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
@@ -6353,23 +6349,23 @@
       <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
@@ -6513,45 +6509,45 @@
       <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F3D21C-41EC-4FC6-BD3C-F118385EFAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A90F13-B819-436D-9549-A095C44A761C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="12" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="915" activeTab="13" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="ContextView" sheetId="12" r:id="rId11"/>
     <sheet name="DP" sheetId="13" r:id="rId12"/>
     <sheet name="New DP" sheetId="14" r:id="rId13"/>
-    <sheet name="Sheet1" sheetId="15" r:id="rId14"/>
+    <sheet name="DP1" sheetId="15" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'New DP'!$A$1:$E$21</definedName>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="337">
   <si>
     <t>품질 속성</t>
   </si>
@@ -3545,6 +3545,64 @@
       </rPr>
       <t>관리</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pVM과 workload 바이너리의 기밀성, 무결성이 확보되면 pVM을 생성하는 주체, Workload를 탑재/실행하는 주체가 침해당해도 시스템이 신뢰할 수 있도고 볼 수 있어?</t>
+  </si>
+  <si>
+    <r>
+      <t>네, 신뢰할 수 있다고 볼 수 있습니다.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 다만 이는 '어디까지를 신뢰 범위(Trust Boundary)로 설정하고 하이퍼바이저가 이를 어떻게 강제하는가'에 대한 아키텍처적 전제 조건이 충족되어야 합니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>구글의 AVF(Android Virtualization Framework)나 pKVM 기반 보안 가상화 환경에서는 호스트(Host OS)나 가상머신 매니저(VMM)를 잠재적으로 침해당할 수 있는 요소(Untrusted Host Model)로 간주하고 설계를 진행</t>
+  </si>
+  <si>
+    <t>1. 생성/실행 주체가 침해당해도 안전한 이유 (Zero-Trust Host)
+ - Stage-2 격리의 하이퍼바이저 강제: pKVM(EL2 하이퍼바이저 레벨)은 Stage-2 페이지 테이블을 제어하여 각 pVM의 독점 메모리 영역을 호스트(EL1)가 절대 접근할 수 없도록 철저히 격리
+ - Stateless VMM 구조: 호스트의 VMM(예: crosvm)은 단순히 자원 스케줄링, 라우팅, 가상 디바이스 에뮬레이션만 담당할 뿐, pVM 내부의 보안 상태나 기밀 데이터를 들고 있지 않습니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Workload 바이너리의 무결성 보장 (정형화된 검증)
+- pvmfw (pVM Firmware) 기반 검증: pVM이 구동될 때 가장 먼저 실행되는 pvmfw는 탑재된 워크로드 바이너리의 해시값을 측정하고, 신뢰할 수 있는 서명(Signature)과 일치하는지 검증
+ - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변조된 바이너리가 탑재되었다면 실행 자체가 거부되므로, 워크로드를 탑재하는 주체(호스트)가 변조를 시도하더라도 무결성이 확보된 올바른 바이너리만 pVM 내에서 실행됨을 보장</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 통신 및 자원 공유 시의 안전장치
+ - 동적 하이퍼콜(MEM_SHARE) 기반 제어: pVM 간 버퍼(DMABUF 등)를 공유할 때, pKVM 하이퍼바이저는 명시적인 하이퍼콜을 통해서만 임시로 접근 권한을 부여
+ - 공유 해제 및 제로화(Sanitization): 데이터 공유가 끝나면 하이퍼바이저가 즉시 매핑을 해제(Unmap)하고, 해당 메모리 영역을 완전히 제로화(Zeroing)한 후 원래 pVM에 귀속</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>호스트 중재 구조 (기본 AVF 표준): 호스트 VMM이 통신 토큰을 중재하므로 구현이 쉬우나, 호스트가 완전히 장악당했을 때 어떤 pVM들이 서로 연결되어 있는지와 같은 메타데이터(통신 관계)는 노출될 수 있습니다.
+Coordinator pVM 구조: 완전히 격리된 별도의 특권 VM(Control Plane)이 pVM들의 생명주기와 자원 공유를 통제합니다. 이 경우 호스트 OS는 두 pVM이 데이터를 주고받는지조차 알 수 없어 극단의 기밀성(Zero-Trust)을 달성할 수 있습니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3552,7 +3610,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3757,6 +3815,29 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3865,7 +3946,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3986,10 +4067,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4000,6 +4081,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5143,9 +5233,48 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C70C73-9E29-4A82-9F0B-6BA2B6E58795}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="147.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="45" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="46" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="87">
+      <c r="A5" s="47" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="87">
+      <c r="A6" s="47" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="52.2">
+      <c r="A7" s="47" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="104.4">
+      <c r="A8" s="47" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5853,13 +5982,13 @@
       <c r="C2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="41">
+      <c r="F2" s="40">
         <v>1</v>
       </c>
     </row>
@@ -5869,9 +5998,9 @@
       <c r="C3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="39" t="s">
@@ -5883,13 +6012,13 @@
       <c r="C4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="40">
         <v>2</v>
       </c>
     </row>
@@ -5899,9 +6028,9 @@
       <c r="C5" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="39" t="s">
@@ -5913,13 +6042,13 @@
       <c r="C6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="40">
         <v>3</v>
       </c>
     </row>
@@ -5929,9 +6058,9 @@
       <c r="C7" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="39" t="s">
@@ -5943,13 +6072,13 @@
       <c r="C8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="40">
         <v>4</v>
       </c>
     </row>
@@ -5959,9 +6088,9 @@
       <c r="C9" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="39" t="s">
@@ -5973,13 +6102,13 @@
       <c r="C10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="40">
         <v>5</v>
       </c>
     </row>
@@ -5989,9 +6118,9 @@
       <c r="C11" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="39" t="s">
@@ -6003,13 +6132,13 @@
       <c r="C12" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="40">
         <v>6</v>
       </c>
     </row>
@@ -6019,9 +6148,9 @@
       <c r="C13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="39" t="s">
@@ -6033,13 +6162,13 @@
       <c r="C14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="40">
         <v>7</v>
       </c>
     </row>
@@ -6049,9 +6178,9 @@
       <c r="C15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="39" t="s">
@@ -6063,13 +6192,13 @@
       <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="40">
         <v>8</v>
       </c>
     </row>
@@ -6079,9 +6208,9 @@
       <c r="C17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="39" t="s">
@@ -6093,13 +6222,13 @@
       <c r="C18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="40">
         <v>9</v>
       </c>
     </row>
@@ -6109,57 +6238,57 @@
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="D18:D19"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A90F13-B819-436D-9549-A095C44A761C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A745098-B547-4A2C-89CF-840242209A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="915" activeTab="13" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="13" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="336">
   <si>
     <t>품질 속성</t>
   </si>
@@ -3548,61 +3548,531 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>pVM과 workload 바이너리의 기밀성, 무결성이 확보되면 pVM을 생성하는 주체, Workload를 탑재/실행하는 주체가 침해당해도 시스템이 신뢰할 수 있도고 볼 수 있어?</t>
-  </si>
-  <si>
-    <r>
-      <t>네, 신뢰할 수 있다고 볼 수 있습니다.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 다만 이는 '어디까지를 신뢰 범위(Trust Boundary)로 설정하고 하이퍼바이저가 이를 어떻게 강제하는가'에 대한 아키텍처적 전제 조건이 충족되어야 합니다.</t>
-    </r>
-  </si>
-  <si>
-    <t>구글의 AVF(Android Virtualization Framework)나 pKVM 기반 보안 가상화 환경에서는 호스트(Host OS)나 가상머신 매니저(VMM)를 잠재적으로 침해당할 수 있는 요소(Untrusted Host Model)로 간주하고 설계를 진행</t>
-  </si>
-  <si>
-    <t>1. 생성/실행 주체가 침해당해도 안전한 이유 (Zero-Trust Host)
- - Stage-2 격리의 하이퍼바이저 강제: pKVM(EL2 하이퍼바이저 레벨)은 Stage-2 페이지 테이블을 제어하여 각 pVM의 독점 메모리 영역을 호스트(EL1)가 절대 접근할 수 없도록 철저히 격리
- - Stateless VMM 구조: 호스트의 VMM(예: crosvm)은 단순히 자원 스케줄링, 라우팅, 가상 디바이스 에뮬레이션만 담당할 뿐, pVM 내부의 보안 상태나 기밀 데이터를 들고 있지 않습니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2. Workload 바이너리의 무결성 보장 (정형화된 검증)
-- pvmfw (pVM Firmware) 기반 검증: pVM이 구동될 때 가장 먼저 실행되는 pvmfw는 탑재된 워크로드 바이너리의 해시값을 측정하고, 신뢰할 수 있는 서명(Signature)과 일치하는지 검증
- - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>변조된 바이너리가 탑재되었다면 실행 자체가 거부되므로, 워크로드를 탑재하는 주체(호스트)가 변조를 시도하더라도 무결성이 확보된 올바른 바이너리만 pVM 내에서 실행됨을 보장</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 통신 및 자원 공유 시의 안전장치
- - 동적 하이퍼콜(MEM_SHARE) 기반 제어: pVM 간 버퍼(DMABUF 등)를 공유할 때, pKVM 하이퍼바이저는 명시적인 하이퍼콜을 통해서만 임시로 접근 권한을 부여
- - 공유 해제 및 제로화(Sanitization): 데이터 공유가 끝나면 하이퍼바이저가 즉시 매핑을 해제(Unmap)하고, 해당 메모리 영역을 완전히 제로화(Zeroing)한 후 원래 pVM에 귀속</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>호스트 중재 구조 (기본 AVF 표준): 호스트 VMM이 통신 토큰을 중재하므로 구현이 쉬우나, 호스트가 완전히 장악당했을 때 어떤 pVM들이 서로 연결되어 있는지와 같은 메타데이터(통신 관계)는 노출될 수 있습니다.
-Coordinator pVM 구조: 완전히 격리된 별도의 특권 VM(Control Plane)이 pVM들의 생명주기와 자원 공유를 통제합니다. 이 경우 호스트 OS는 두 pVM이 데이터를 주고받는지조차 알 수 없어 극단의 기밀성(Zero-Trust)을 달성할 수 있습니다.</t>
+    <t>A1-2. pVM별 위임형 인스턴스 모니터</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A1-5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pVM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위임형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Control pVM)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C2-3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요청별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>직접</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배타적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소유권</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스위칭</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C2-1. Host </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>커널</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드라이버</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시분할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DMA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검증</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C1-3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프레임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소유권</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채널</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (exclusive lend hand-off)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">C1-1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버퍼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>풀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + zero-copy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (lend/share </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매핑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3610,7 +4080,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3816,27 +4286,17 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
+      <sz val="13.75"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13.75"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3946,7 +4406,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4064,13 +4524,16 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4082,13 +4545,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4406,9 +4863,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA4CBF-2B00-47DE-B890-6C9CADE53CC2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="22.59765625" customWidth="1"/>
+    <col min="2" max="3" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4475,9 +4932,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FC3EE2-E578-4F70-869F-9EBF67B87D76}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="5.09765625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="5.125" style="21" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
@@ -4617,13 +5074,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="29.09765625" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="74.59765625" customWidth="1"/>
-    <col min="3" max="3" width="57.09765625" customWidth="1"/>
+    <col min="2" max="2" width="74.625" customWidth="1"/>
+    <col min="3" max="3" width="57.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.8" thickBot="1">
+    <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" s="28" t="s">
         <v>225</v>
       </c>
@@ -4632,7 +5089,7 @@
       </c>
       <c r="C1" s="25"/>
     </row>
-    <row r="2" spans="1:3" ht="19.8" thickBot="1">
+    <row r="2" spans="1:3" ht="18" thickBot="1">
       <c r="A2" s="26" t="s">
         <v>207</v>
       </c>
@@ -4641,7 +5098,7 @@
       </c>
       <c r="C2" s="26"/>
     </row>
-    <row r="3" spans="1:3" ht="19.8" thickBot="1">
+    <row r="3" spans="1:3" ht="18" thickBot="1">
       <c r="A3" s="26" t="s">
         <v>208</v>
       </c>
@@ -4650,7 +5107,7 @@
       </c>
       <c r="C3" s="26"/>
     </row>
-    <row r="4" spans="1:3" ht="19.8" thickBot="1">
+    <row r="4" spans="1:3" ht="18" thickBot="1">
       <c r="A4" s="26" t="s">
         <v>216</v>
       </c>
@@ -4659,7 +5116,7 @@
       </c>
       <c r="C4" s="26"/>
     </row>
-    <row r="5" spans="1:3" ht="19.8" thickBot="1">
+    <row r="5" spans="1:3" ht="18" thickBot="1">
       <c r="A5" s="26" t="s">
         <v>215</v>
       </c>
@@ -4668,7 +5125,7 @@
       </c>
       <c r="C5" s="26"/>
     </row>
-    <row r="6" spans="1:3" ht="19.8" thickBot="1">
+    <row r="6" spans="1:3" ht="18" thickBot="1">
       <c r="A6" s="26" t="s">
         <v>209</v>
       </c>
@@ -4677,7 +5134,7 @@
       </c>
       <c r="C6" s="26"/>
     </row>
-    <row r="7" spans="1:3" ht="19.8" thickBot="1">
+    <row r="7" spans="1:3" ht="18" thickBot="1">
       <c r="A7" s="26" t="s">
         <v>210</v>
       </c>
@@ -4686,7 +5143,7 @@
       </c>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" ht="19.8" thickBot="1">
+    <row r="8" spans="1:3" ht="18" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>211</v>
       </c>
@@ -4695,7 +5152,7 @@
       </c>
       <c r="C8" s="26"/>
     </row>
-    <row r="9" spans="1:3" ht="19.8" thickBot="1">
+    <row r="9" spans="1:3" ht="18" thickBot="1">
       <c r="A9" s="26" t="s">
         <v>212</v>
       </c>
@@ -4704,7 +5161,7 @@
       </c>
       <c r="C9" s="26"/>
     </row>
-    <row r="10" spans="1:3" ht="19.8" thickBot="1">
+    <row r="10" spans="1:3" ht="18" thickBot="1">
       <c r="A10" s="26" t="s">
         <v>213</v>
       </c>
@@ -4722,14 +5179,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.19921875" customWidth="1"/>
+    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.8" thickBot="1">
+    <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" s="25" t="s">
         <v>240</v>
       </c>
@@ -4740,7 +5197,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.8" thickBot="1">
+    <row r="2" spans="1:3" ht="18" thickBot="1">
       <c r="A2" s="30" t="s">
         <v>227</v>
       </c>
@@ -4751,7 +5208,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="19.8" thickBot="1">
+    <row r="3" spans="1:3" ht="18" thickBot="1">
       <c r="A3" s="30" t="s">
         <v>229</v>
       </c>
@@ -4762,7 +5219,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="19.8" thickBot="1">
+    <row r="4" spans="1:3" ht="18" thickBot="1">
       <c r="A4" s="30" t="s">
         <v>231</v>
       </c>
@@ -4773,7 +5230,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19.8" thickBot="1">
+    <row r="5" spans="1:3" ht="18" thickBot="1">
       <c r="A5" s="30" t="s">
         <v>233</v>
       </c>
@@ -4784,7 +5241,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="19.8" thickBot="1">
+    <row r="6" spans="1:3" ht="18" thickBot="1">
       <c r="A6" s="30" t="s">
         <v>235</v>
       </c>
@@ -4795,7 +5252,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.8" thickBot="1">
+    <row r="7" spans="1:3" ht="18" thickBot="1">
       <c r="A7" s="30" t="s">
         <v>237</v>
       </c>
@@ -4816,13 +5273,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E651437D-FAC7-4432-A76A-B730DB461C13}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="13.8984375" customWidth="1"/>
-    <col min="2" max="2" width="48.09765625" customWidth="1"/>
-    <col min="3" max="3" width="31.3984375" customWidth="1"/>
-    <col min="4" max="4" width="11.8984375" customWidth="1"/>
-    <col min="5" max="5" width="31.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="48.125" customWidth="1"/>
+    <col min="3" max="3" width="31.375" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5016,7 +5473,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="23" customFormat="1" ht="31.2">
+    <row r="12" spans="1:6" s="23" customFormat="1" ht="27">
       <c r="A12" s="31" t="s">
         <v>278</v>
       </c>
@@ -5173,8 +5630,8 @@
         <v>314</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18" thickBot="1"/>
-    <row r="25" spans="1:5" ht="18" thickBot="1">
+    <row r="24" spans="1:5" ht="17.25" thickBot="1"/>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1">
       <c r="A25" s="36" t="s">
         <v>227</v>
       </c>
@@ -5185,7 +5642,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18" thickBot="1">
+    <row r="26" spans="1:5" ht="17.25" thickBot="1">
       <c r="A26" s="36" t="s">
         <v>229</v>
       </c>
@@ -5196,7 +5653,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18" thickBot="1">
+    <row r="27" spans="1:5" ht="17.25" thickBot="1">
       <c r="A27" s="36" t="s">
         <v>231</v>
       </c>
@@ -5207,7 +5664,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="18" thickBot="1">
+    <row r="28" spans="1:5" ht="17.25" thickBot="1">
       <c r="A28" s="36" t="s">
         <v>233</v>
       </c>
@@ -5234,45 +5691,46 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C70C73-9E29-4A82-9F0B-6BA2B6E58795}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="147.19921875" customWidth="1"/>
+    <col min="1" max="1" width="147.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:1" ht="21">
+      <c r="A1" s="46" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" ht="21.75">
       <c r="A2" s="46" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:1" ht="21.75">
+      <c r="A3" s="46" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="21.75">
+      <c r="A4" s="46" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="21.75">
+      <c r="A5" s="46" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="21.75">
+      <c r="A6" s="46" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="87">
-      <c r="A5" s="47" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="87">
-      <c r="A6" s="47" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="52.2">
-      <c r="A7" s="47" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="104.4">
-      <c r="A8" s="47" t="s">
-        <v>336</v>
-      </c>
+    <row r="7" spans="1:1" ht="21">
+      <c r="A7" s="46"/>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -5283,11 +5741,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5398,10 +5856,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.19921875" customWidth="1"/>
+    <col min="3" max="3" width="57.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5600,9 +6058,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5737,12 +6195,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5762,7 +6220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="21">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -5796,7 +6254,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="21">
       <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
@@ -5813,7 +6271,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="21">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -5847,7 +6305,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="21">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -5873,9 +6331,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="14.19921875" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5944,12 +6402,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="99.8984375" customWidth="1"/>
-    <col min="4" max="5" width="5.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.875" customWidth="1"/>
+    <col min="4" max="5" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5973,10 +6431,10 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -5988,25 +6446,25 @@
       <c r="E2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="42">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7" t="s">
         <v>128</v>
       </c>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
-      <c r="F3" s="40"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="40" t="s">
         <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -6018,25 +6476,25 @@
       <c r="E4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="42">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7" t="s">
         <v>133</v>
       </c>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
-      <c r="F5" s="40"/>
+      <c r="F5" s="42"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="40" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -6048,25 +6506,25 @@
       <c r="E6" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="42">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="7" t="s">
         <v>134</v>
       </c>
       <c r="D7" s="41"/>
       <c r="E7" s="41"/>
-      <c r="F7" s="40"/>
+      <c r="F7" s="42"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="40" t="s">
         <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -6078,25 +6536,25 @@
       <c r="E8" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="42">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="39"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="7" t="s">
         <v>205</v>
       </c>
       <c r="D9" s="41"/>
       <c r="E9" s="41"/>
-      <c r="F9" s="40"/>
+      <c r="F9" s="42"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="40" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -6105,28 +6563,28 @@
       <c r="D10" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="7" t="s">
         <v>135</v>
       </c>
       <c r="D11" s="41"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="43" t="s">
         <v>166</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -6135,160 +6593,160 @@
       <c r="D12" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="42">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="7" t="s">
         <v>204</v>
       </c>
       <c r="D13" s="41"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="40" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="42">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>130</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="42">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="40" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="42">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="39"/>
-      <c r="B19" s="39"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6298,9 +6756,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
   <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" customWidth="1"/>
+    <col min="1" max="1" width="7.375" customWidth="1"/>
     <col min="2" max="16" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6432,23 +6890,23 @@
       <c r="A5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="9" t="s">
@@ -6478,23 +6936,23 @@
       <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="9" t="s">
@@ -6638,45 +7096,45 @@
       <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="45"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="9" t="s">
@@ -6739,21 +7197,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="25.69921875" customWidth="1"/>
-    <col min="2" max="2" width="64.09765625" customWidth="1"/>
-    <col min="3" max="3" width="40.8984375" customWidth="1"/>
-    <col min="4" max="4" width="25.69921875" customWidth="1"/>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="64.125" customWidth="1"/>
+    <col min="3" max="3" width="40.875" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="17.25">
       <c r="A1" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1"/>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
+    <row r="3" spans="1:3" ht="17.25" thickBot="1">
       <c r="A3" s="15" t="s">
         <v>168</v>
       </c>
@@ -6764,7 +7222,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.2" thickBot="1">
+    <row r="4" spans="1:3" ht="29.25" thickBot="1">
       <c r="A4" s="16" t="s">
         <v>171</v>
       </c>
@@ -6775,7 +7233,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="42" thickBot="1">
+    <row r="5" spans="1:3" ht="43.5" thickBot="1">
       <c r="A5" s="16" t="s">
         <v>174</v>
       </c>
@@ -6786,7 +7244,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="42" thickBot="1">
+    <row r="6" spans="1:3" ht="43.5" thickBot="1">
       <c r="A6" s="16" t="s">
         <v>177</v>
       </c>
@@ -6797,7 +7255,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="42" thickBot="1">
+    <row r="7" spans="1:3" ht="45" thickBot="1">
       <c r="A7" s="16" t="s">
         <v>180</v>
       </c>
@@ -6808,7 +7266,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="42" thickBot="1">
+    <row r="8" spans="1:3" ht="45" thickBot="1">
       <c r="A8" s="19" t="s">
         <v>188</v>
       </c>
@@ -6819,7 +7277,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="27.6">
+    <row r="9" spans="1:3" ht="28.5">
       <c r="A9" s="19" t="s">
         <v>187</v>
       </c>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F1581A-F265-482F-B9DB-6504A5538F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576B6C7D-E7BB-41E3-B523-5914CAAEDE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="915" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="915" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -3437,6 +3437,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3448,18 +3460,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4660,287 +4660,287 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="26" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="29" t="s">
         <v>219</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="27">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="27">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="32"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="26" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="27">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="29" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="26" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="27">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="26" t="s">
         <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="27">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="27">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5064,20 +5064,20 @@
       <c r="A5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="28"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="32"/>
       <c r="O5" s="24" t="s">
         <v>114</v>
       </c>
@@ -5107,20 +5107,20 @@
       <c r="A7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="28"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="32"/>
       <c r="O7" s="25" t="s">
         <v>130</v>
       </c>
@@ -5249,20 +5249,20 @@
       <c r="A14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="28"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="32"/>
       <c r="O14" s="24" t="s">
         <v>115</v>
       </c>
@@ -5271,20 +5271,20 @@
       <c r="A15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="28"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="32"/>
       <c r="O15" s="25" t="s">
         <v>129</v>
       </c>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576B6C7D-E7BB-41E3-B523-5914CAAEDE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECE81D3-6EC0-42EF-9BAB-48ECE2CD119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="915" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="7" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -20,10 +20,12 @@
     <sheet name="FR" sheetId="4" r:id="rId5"/>
     <sheet name="CONST" sheetId="5" r:id="rId6"/>
     <sheet name="QA" sheetId="6" r:id="rId7"/>
-    <sheet name="Matrix" sheetId="8" r:id="rId8"/>
-    <sheet name="pKVM interfacer" sheetId="10" r:id="rId9"/>
-    <sheet name="ContextView" sheetId="12" r:id="rId10"/>
-    <sheet name="DP" sheetId="13" r:id="rId11"/>
+    <sheet name="ISO 25010" sheetId="14" r:id="rId8"/>
+    <sheet name="ISO 25023" sheetId="15" r:id="rId9"/>
+    <sheet name="Matrix" sheetId="8" r:id="rId10"/>
+    <sheet name="pKVM interfacer" sheetId="10" r:id="rId11"/>
+    <sheet name="ContextView" sheetId="12" r:id="rId12"/>
+    <sheet name="DP" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="548">
   <si>
     <t>품질 속성</t>
   </si>
@@ -3053,6 +3055,989 @@
       </rPr>
       <t>아님</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성능 효율성 (Performance Efficiency)</t>
+  </si>
+  <si>
+    <t>시간 반응성 (Time behaviour)</t>
+  </si>
+  <si>
+    <t>자원 활용성 (Resource utilization)</t>
+  </si>
+  <si>
+    <t>용량 (Capacity)</t>
+  </si>
+  <si>
+    <t>호환성 (Compatibility)</t>
+  </si>
+  <si>
+    <t>공존성 (Co-existence)</t>
+  </si>
+  <si>
+    <t>사용성 (Usability)</t>
+  </si>
+  <si>
+    <t>적절성 인식성 (Appropriateness recognizability)</t>
+  </si>
+  <si>
+    <t>사용자가 제품/시스템이 자신의 요구에 적절한지 인식할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>학습성 (Learnability)</t>
+  </si>
+  <si>
+    <t>특정 사용자가 제품/시스템 사용법을 학습하여 목표를 달성할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>운용성 (Operability)</t>
+  </si>
+  <si>
+    <t>제품/시스템이 운용하고 제어하기 쉬운 속성을 갖는 정도</t>
+  </si>
+  <si>
+    <t>사용자 오류 방지 (User error protection)</t>
+  </si>
+  <si>
+    <t>시스템이 사용자의 오류 유발을 방지하는 정도</t>
+  </si>
+  <si>
+    <t>사용자 인터페이스 심미성 (User interface aesthetics)</t>
+  </si>
+  <si>
+    <t>사용자 인터페이스가 사용자에게 즐겁고 만족스러운 상호작용을 가능하게 하는 정도</t>
+  </si>
+  <si>
+    <t>접근성 (Accessibility)</t>
+  </si>
+  <si>
+    <t>다양한 특성과 능력을 가진 사람들이 명시된 사용 맥락에서 제품/시스템을 사용할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>기능 수행 시 응답 시간, 처리 시간, 처리율(throughput)이 요구사항을 충족하는 정도</t>
+  </si>
+  <si>
+    <t>기능 수행 시 사용하는 자원의 양과 유형이 요구사항을 충족하는 정도</t>
+  </si>
+  <si>
+    <t>제품/시스템 파라미터의 최대 한계가 요구사항을 충족하는 정도</t>
+  </si>
+  <si>
+    <t>공통 환경과 자원을 공유하는 다른 제품에 해로운 영향 없이 요구 기능을 효율적으로 수행하는 정도</t>
+  </si>
+  <si>
+    <t>상호운용성 (Interoperability)</t>
+  </si>
+  <si>
+    <t>둘 이상의 시스템/제품/컴포넌트가 정보를 교환하고 교환된 정보를 사용할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>신뢰성 (Reliability)</t>
+  </si>
+  <si>
+    <t>성숙성 (Maturity)</t>
+  </si>
+  <si>
+    <t>정상 운영 상태에서 신뢰성 요구를 충족하는 정도</t>
+  </si>
+  <si>
+    <t>가용성 (Availability)</t>
+  </si>
+  <si>
+    <t>사용이 요구되는 시점에 운영 가능하고 접근 가능한 정도</t>
+  </si>
+  <si>
+    <t>결함 허용성 (Fault tolerance)</t>
+  </si>
+  <si>
+    <t>하드웨어 또는 소프트웨어 결함에도 불구하고 의도된 대로 동작하는 정도</t>
+  </si>
+  <si>
+    <t>복구성 (Recoverability)</t>
+  </si>
+  <si>
+    <t>중단이나 고장 발생 시, 직접 영향을 받은 데이터를 복구하고 시스템을 원하는 상태로 재확립할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>보안성 (Security)</t>
+  </si>
+  <si>
+    <t>기밀성 (Confidentiality)</t>
+  </si>
+  <si>
+    <t>접근 권한이 있는 자에게만 데이터 접근이 허용됨을 보장하는 정도</t>
+  </si>
+  <si>
+    <t>무결성 (Integrity)</t>
+  </si>
+  <si>
+    <t>컴퓨터 프로그램 또는 데이터에 대한 비인가 접근/변경을 방지하는 정도</t>
+  </si>
+  <si>
+    <t>부인 방지 (Non-repudiation)</t>
+  </si>
+  <si>
+    <t>행위나 사건의 발생을 사후에 부인할 수 없도록 입증할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>책임 추적성 (Accountability)</t>
+  </si>
+  <si>
+    <t>어떤 실체(entity)의 행위를 그 실체로 유일하게 추적할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>인증성 (Authenticity)</t>
+  </si>
+  <si>
+    <t>주체(subject)나 자원의 신원이 주장된 것과 일치함을 입증할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>유지보수성 (Maintainability)</t>
+  </si>
+  <si>
+    <t>모듈성 (Modularity)</t>
+  </si>
+  <si>
+    <t>한 컴포넌트의 변경이 다른 컴포넌트에 미치는 영향이 최소화되도록 시스템이 분리된 컴포넌트로 구성된 정도</t>
+  </si>
+  <si>
+    <t>재사용성 (Reusability)</t>
+  </si>
+  <si>
+    <t>자산(asset)을 둘 이상의 시스템 또는 다른 자산 구축에 사용할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>분석성 (Analysability)</t>
+  </si>
+  <si>
+    <t>변경이 다른 부분에 미치는 영향 평가, 결함/고장 원인 진단, 수정 대상 식별을 효과적이고 효율적으로 할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>수정성 (Modifiability)</t>
+  </si>
+  <si>
+    <t>결함 유입이나 기존 품질 저하 없이 효과적이고 효율적으로 수정할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>시험성 (Testability)</t>
+  </si>
+  <si>
+    <t>시스템/제품/컴포넌트에 대한 시험 기준을 수립하고, 그 기준 충족 여부를 판정하는 시험을 효과적이고 효율적으로 수행할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>이식성 (Portability)</t>
+  </si>
+  <si>
+    <t>적응성 (Adaptability)</t>
+  </si>
+  <si>
+    <t>상이하거나 진화하는 하드웨어/소프트웨어/운영 환경에 효과적이고 효율적으로 적응할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>설치성 (Installability)</t>
+  </si>
+  <si>
+    <t>명시된 환경에서 효과적이고 효율적으로 설치/제거할 수 있는 정도</t>
+  </si>
+  <si>
+    <t>대체성 (Replaceability)</t>
+  </si>
+  <si>
+    <t>동일 환경에서 동일 목적의 다른 소프트웨어 제품을 대체할 수 있는 정도</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확장성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Scalability)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지표명</t>
+  </si>
+  <si>
+    <t>측정 함수 및 방법</t>
+  </si>
+  <si>
+    <t>PTb-1-G</t>
+  </si>
+  <si>
+    <t>평균 응답 시간 (Mean response time)</t>
+  </si>
+  <si>
+    <t>X = Σ(Bi − Ai)/n. Ai: i번째 과업 요청 시각, Bi: 응답 시작 시각, n: 측정 횟수</t>
+  </si>
+  <si>
+    <t>PTb-2-S</t>
+  </si>
+  <si>
+    <t>응답 시간 적정성 (Response time adequacy)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 실측 평균 응답 시간, B: 명세된 목표 응답 시간. 1 이하일수록 적정</t>
+  </si>
+  <si>
+    <t>PTb-3-G</t>
+  </si>
+  <si>
+    <t>평균 반환 시간 (Mean turnaround time)</t>
+  </si>
+  <si>
+    <t>X = Σ(작업 요청부터 작업 완료까지의 시간)/n. 작업(job) 완료 기준의 평균 소요 시간</t>
+  </si>
+  <si>
+    <t>PTb-4-S</t>
+  </si>
+  <si>
+    <t>반환 시간 적정성 (Turnaround time adequacy)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 실측 평균 반환 시간, B: 명세된 목표 반환 시간</t>
+  </si>
+  <si>
+    <t>PTb-5-G</t>
+  </si>
+  <si>
+    <t>평균 처리율 (Mean throughput)</t>
+  </si>
+  <si>
+    <t>X = Σ(단위 시간당 완료 작업 수)/n. 관측 구간별 처리율의 평균</t>
+  </si>
+  <si>
+    <t>PRu-1-G</t>
+  </si>
+  <si>
+    <t>평균 프로세서 사용률 (Mean processor utilization)</t>
+  </si>
+  <si>
+    <t>X = Σ(Ai/Bi)/n. Ai: 실제 사용한 프로세서 시간, Bi: 운영 시간. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>PRu-2-G</t>
+  </si>
+  <si>
+    <t>평균 메모리 사용률 (Mean memory utilization)</t>
+  </si>
+  <si>
+    <t>X = Σ(Ai/Bi)/n. Ai: 실제 사용한 메모리 크기, Bi: 가용 메모리 크기. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>PRu-3-G</t>
+  </si>
+  <si>
+    <t>평균 I/O 장치 사용률 (Mean I/O devices utilization)</t>
+  </si>
+  <si>
+    <t>X = Σ(Ai/Bi)/n. Ai: I/O 장치 점유(busy) 시간, Bi: I/O 작업에 요구되는 시간. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>PRu-4-S</t>
+  </si>
+  <si>
+    <t>대역폭 사용률 (Bandwidth utilization)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 사용한 전송 대역폭, B: 가용(용량) 대역폭</t>
+  </si>
+  <si>
+    <t>PCa-1-G</t>
+  </si>
+  <si>
+    <t>트랜잭션 처리 용량 (Transaction processing capacity)</t>
+  </si>
+  <si>
+    <t>X = A/T. A: 완료된 트랜잭션 수, T: 관측 시간. 단위 시간당 처리 가능한 트랜잭션 수</t>
+  </si>
+  <si>
+    <t>PCa-2-S</t>
+  </si>
+  <si>
+    <t>사용자 접속 용량 (User access capacity)</t>
+  </si>
+  <si>
+    <t>X = 단위 시간 내 시스템이 정상 처리 가능한 최대 동시 사용자 수</t>
+  </si>
+  <si>
+    <t>PCa-3-S</t>
+  </si>
+  <si>
+    <t>사용자 접속 증가 적정성 (User access increase adequacy)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 수용 가능한 추가 동시 사용자 수, B: 요구되는 추가 동시 사용자 수</t>
+  </si>
+  <si>
+    <t>성능 효율성 측정 (8.3)</t>
+  </si>
+  <si>
+    <t> 호환성 측정 (8.4)</t>
+  </si>
+  <si>
+    <t>CCo-1-G</t>
+  </si>
+  <si>
+    <t>타 제품과의 공존성 (Co-existence with other products)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 환경 공유 중에도 품질 요구를 계속 충족하는 타 제품 수, B: 환경을 공유하는 타 제품 총수</t>
+  </si>
+  <si>
+    <t>CIn-1-G</t>
+  </si>
+  <si>
+    <t>데이터 형식 교환성 (Data formats exchangeability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 타 시스템과 교환 가능한 데이터 형식 수, B: 교환이 요구되는 데이터 형식 수</t>
+  </si>
+  <si>
+    <t>CIn-2-S</t>
+  </si>
+  <si>
+    <t>데이터 교환 프로토콜 충분성 (Data exchange protocol sufficiency)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 지원되는 데이터 교환 프로토콜 수, B: 요구되는 데이터 교환 프로토콜 수</t>
+  </si>
+  <si>
+    <t>CIn-3-S</t>
+  </si>
+  <si>
+    <t>외부 인터페이스 적정성 (External interface adequacy)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 명세대로 구현된 외부 인터페이스 수, B: 명세된 외부 인터페이스 수</t>
+  </si>
+  <si>
+    <t>사용성 측정 (8.5)</t>
+  </si>
+  <si>
+    <t>UAp-1-G</t>
+  </si>
+  <si>
+    <t>설명 완전성 (Description completeness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 제품 설명(문서)에 기술된 사용 시나리오 수, B: 제품이 수행 가능한 사용 시나리오 수</t>
+  </si>
+  <si>
+    <t>UAp-2-S</t>
+  </si>
+  <si>
+    <t>데모 커버리지 (Demonstration coverage)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 데모/튜토리얼이 제공되는 과업 수, B: 데모가 필요한 과업 수</t>
+  </si>
+  <si>
+    <t>UAp-3-S</t>
+  </si>
+  <si>
+    <t>진입점 자기 서술성 (Entry point self-descriptiveness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 목적과 내용을 스스로 설명하는 진입점(예: 웹사이트 랜딩) 수, B: 전체 진입점 수</t>
+  </si>
+  <si>
+    <t>ULe-1-G</t>
+  </si>
+  <si>
+    <t>사용자 안내 완전성 (User guidance completeness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 사용자 문서/도움말이 제공되는 기능 수, B: 전체 기능 수</t>
+  </si>
+  <si>
+    <t>ULe-2-S</t>
+  </si>
+  <si>
+    <t>입력 필드 기본값 (Entry fields defaults)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 기본값이 제공되는 입력 필드 수, B: 기본값 제공이 가능한 입력 필드 수</t>
+  </si>
+  <si>
+    <t>ULe-3-S</t>
+  </si>
+  <si>
+    <t>오류 메시지 이해성 (Error messages understandability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 원인과 해결 방법을 알려주는 오류 메시지 수, B: 전체 오류 메시지 수</t>
+  </si>
+  <si>
+    <t>ULe-4-S</t>
+  </si>
+  <si>
+    <t>자기 설명적 사용자 인터페이스 (Self-explanatory user interface)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 별도 설명 없이 이해 가능한 UI 요소 수, B: 전체 UI 요소 수</t>
+  </si>
+  <si>
+    <t>UOp-1-G</t>
+  </si>
+  <si>
+    <t>운용 일관성 (Operational consistency)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 유사 과업 간 조작이 일관되지 않은 상호작용 과업 수, B: 유사 조작을 갖는 상호작용 과업 수</t>
+  </si>
+  <si>
+    <t>UOp-2-G</t>
+  </si>
+  <si>
+    <t>메시지 명확성 (Message clarity)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 올바른 의미를 전달하는 메시지 수, B: 전체 메시지 수</t>
+  </si>
+  <si>
+    <t>UOp-3-S</t>
+  </si>
+  <si>
+    <t>기능 커스터마이즈 가능성 (Functional customizability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 커스터마이즈 가능한 기능 수, B: 커스터마이즈가 요구되는 기능 수</t>
+  </si>
+  <si>
+    <t>UOp-4-S</t>
+  </si>
+  <si>
+    <t>UI 커스터마이즈 가능성 (User interface customizability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 커스터마이즈 가능한 UI 요소 수, B: 커스터마이즈가 요구되는 UI 요소 수</t>
+  </si>
+  <si>
+    <t>UOp-5-S</t>
+  </si>
+  <si>
+    <t>모니터링 능력 (Monitoring capability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 구현된 상태 모니터링 기능 수, B: 요구되는 상태 모니터링 기능 수</t>
+  </si>
+  <si>
+    <t>UOp-6-S</t>
+  </si>
+  <si>
+    <t>실행 취소 능력 (Undo capability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 실행 취소(undo)가 가능한 과업 수, B: 실행 취소가 필요한 과업 수</t>
+  </si>
+  <si>
+    <t>UOp-7-S</t>
+  </si>
+  <si>
+    <t>정보 분류 이해성 (Understandable categorization of information)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 사용자가 이해하기 쉽게 분류된 정보 카테고리 수, B: 전체 정보 카테고리 수</t>
+  </si>
+  <si>
+    <t>UOp-8-S</t>
+  </si>
+  <si>
+    <t>외관 일관성 (Appearance consistency)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 유사 UI 요소 중 외관이 일관되지 않은 요소 수, B: 유사 외관이 요구되는 UI 요소 수</t>
+  </si>
+  <si>
+    <t>UOp-9-S</t>
+  </si>
+  <si>
+    <t>입력 장치 지원 (Input device support)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 적합한 모든 입력 방식으로 시작 가능한 과업 수, B: 전체 과업 수</t>
+  </si>
+  <si>
+    <t>UEp-1-G</t>
+  </si>
+  <si>
+    <t>사용자 조작 오류 회피 (Avoidance of user operation error)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 시스템 오동작을 유발하지 않도록 보호된 사용자 행위/입력 수, B: 오동작을 유발할 수 있는 사용자 행위/입력 수</t>
+  </si>
+  <si>
+    <t>UEp-2-S</t>
+  </si>
+  <si>
+    <t>사용자 입력 오류 수정 (User entry error correction)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 수정값이 제안되는 입력 오류 수, B: 전체 입력 오류 수</t>
+  </si>
+  <si>
+    <t>UEp-3-S</t>
+  </si>
+  <si>
+    <t>사용자 오류 복구성 (User error recoverability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 사용자 오류 후 복구(취소/되돌리기) 가능한 오류 수, B: 전체 사용자 오류 수</t>
+  </si>
+  <si>
+    <t>UIn-1-S</t>
+  </si>
+  <si>
+    <t>UI 외관 심미성 (Appearance aesthetics of user interfaces)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 사용자에게 심미적으로 만족스러운 화면 수, B: 전체 화면 수. 설문 등 주관 평가 기반</t>
+  </si>
+  <si>
+    <t>UAc-1-S</t>
+  </si>
+  <si>
+    <t>장애 사용자 접근성 (Accessibility for users with disabilities)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 특정 장애를 가진 사용자가 사용 가능한 기능 수, B: 구현된 기능 수</t>
+  </si>
+  <si>
+    <t>UAc-2-S</t>
+  </si>
+  <si>
+    <t>지원 언어 적정성 (Supported languages adequacy)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 지원되는 언어 수, B: 요구되는 언어 수</t>
+  </si>
+  <si>
+    <t> 신뢰성 측정 (8.6)</t>
+  </si>
+  <si>
+    <t>RMa-1-G</t>
+  </si>
+  <si>
+    <t>결함 수정률 (Fault correction)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 설계/코딩/시험 단계에서 수정된 결함 수, B: 탐지된 결함 수</t>
+  </si>
+  <si>
+    <t>RMa-2-G</t>
+  </si>
+  <si>
+    <t>평균 고장 간격 (Mean time between failure, MTBF)</t>
+  </si>
+  <si>
+    <t>X = T/A. T: 운영 시간, A: 발생한 고장 수. 높을수록 좋음(0~1 정규화 아님)</t>
+  </si>
+  <si>
+    <t>RMa-3-G</t>
+  </si>
+  <si>
+    <t>고장률 (Failure rate)</t>
+  </si>
+  <si>
+    <t>X = A/T. A: 관측 기간 내 고장 수, T: 관측 시간. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>RMa-4-S</t>
+  </si>
+  <si>
+    <t>시험 커버리지 (Test coverage)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 실제 수행된 시험 케이스 수, B: 요구사항 커버에 필요한 시험 케이스 수</t>
+  </si>
+  <si>
+    <t>RAv-1-G</t>
+  </si>
+  <si>
+    <t>시스템 가용성 (System availability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 실제 시스템이 운영 가능했던 시간, B: 운영이 계획된 시간</t>
+  </si>
+  <si>
+    <t>RAv-2-S</t>
+  </si>
+  <si>
+    <t>평균 다운 시간 (Mean down time)</t>
+  </si>
+  <si>
+    <t>X = T/N. T: 총 다운 시간(수리, 시정/예방 정비, 물류 지연 포함), N: 고장(중단) 횟수. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>RFt-1-G</t>
+  </si>
+  <si>
+    <t>고장 회피 (Failure avoidance)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 치명적/중대한 고장으로 이어지지 않도록 통제된 결함 패턴 수, B: 고려한 결함 패턴 수. 결함 주입 시험 등으로 측정</t>
+  </si>
+  <si>
+    <t>RFt-2-S</t>
+  </si>
+  <si>
+    <t>컴포넌트 이중화 (Redundancy of components)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 이중화 설치된 컴포넌트 수, B: 시스템 고장 회피를 위해 이중화가 필요한 컴포넌트 수</t>
+  </si>
+  <si>
+    <t>RFt-3-S</t>
+  </si>
+  <si>
+    <t>평균 결함 통지 시간 (Mean fault notification time)</t>
+  </si>
+  <si>
+    <t>X = Σ(결함 발생 시각부터 시스템이 통지한 시각까지의 시간)/N. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>RRe-1-G</t>
+  </si>
+  <si>
+    <t>평균 복구 시간 (Mean recovery time)</t>
+  </si>
+  <si>
+    <t>X = Σ(고장 후 복구 완료까지의 시간)/N. 낮을수록 좋음</t>
+  </si>
+  <si>
+    <t>RRe-2-S</t>
+  </si>
+  <si>
+    <t>백업 데이터 완전성 (Backup data completeness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 정기적으로 백업되는 데이터 항목 수, B: 백업이 요구되는 데이터 항목 수</t>
+  </si>
+  <si>
+    <t>보안성 측정 (8.7)</t>
+  </si>
+  <si>
+    <t>SCo-1-G</t>
+  </si>
+  <si>
+    <t>접근 통제성 (Access controllability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 적절한 인가 절차를 통해서만 접근 가능하도록 통제된 기밀 데이터 항목 수, B: 접근 통제가 요구되는 기밀 데이터 항목 수</t>
+  </si>
+  <si>
+    <t>SCo-2-S</t>
+  </si>
+  <si>
+    <t>데이터 암호화 정확성 (Data encryption correctness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 올바르게 암·복호화되는 데이터 항목 수, B: 암·복호화가 요구되는 데이터 항목 수</t>
+  </si>
+  <si>
+    <t>SCo-3-S</t>
+  </si>
+  <si>
+    <t>암호 알고리즘 강도 (Strength of cryptographic algorithms)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 충분히 강한(파훼되지 않은) 암호 알고리즘이 적용된 데이터 항목 수, B: 암호 알고리즘이 적용된 데이터 항목 수</t>
+  </si>
+  <si>
+    <t>SIn-1-G</t>
+  </si>
+  <si>
+    <t>데이터 무결성 (Data integrity)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 손상(corruption)이 방지된 데이터 항목 수, B: 손상 방지가 요구되는 데이터 항목 수</t>
+  </si>
+  <si>
+    <t>SIn-2-S</t>
+  </si>
+  <si>
+    <t>내부 데이터 손상 방지 (Internal data corruption prevention)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 구현된 데이터 손상 방지 방법 수, B: 가용/권고되는 데이터 손상 방지 방법 수</t>
+  </si>
+  <si>
+    <t>SIn-3-S</t>
+  </si>
+  <si>
+    <t>버퍼 오버플로 방지 (Buffer overflow prevention)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 경계 검사가 수행되는 사용자 입력 기반 메모리 접근 수, B: 사용자 입력 기반 메모리 접근 총수</t>
+  </si>
+  <si>
+    <t>SNo-1-G</t>
+  </si>
+  <si>
+    <t>전자 서명 사용률 (Digital signature usage)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 전자 서명 등으로 캡처되는 이벤트 수, B: 부인 방지가 요구되는 이벤트 수</t>
+  </si>
+  <si>
+    <t>SAc-1-G</t>
+  </si>
+  <si>
+    <t>사용자 감사 추적 완전성 (User audit trail completeness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 로그에 기록되는 사용자 접근 수, B: 전체 사용자 접근 수</t>
+  </si>
+  <si>
+    <t>SAc-2-S</t>
+  </si>
+  <si>
+    <t>시스템 로그 보존성 (System log retention)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 안정적 저장소에 로그가 실제 보존되는 기간, B: 요구되는 로그 보존 기간</t>
+  </si>
+  <si>
+    <t>인증 메커니즘 충분성 (Authentication mechanism sufficiency)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 구현된 인증 메커니즘 수, B: 명세된 인증 메커니즘 수</t>
+  </si>
+  <si>
+    <t>SAu-2-S</t>
+  </si>
+  <si>
+    <t>인증 규칙 준수성 (Authentication rules conformity)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 구현된 인증 규칙 수, B: 명세된 인증 규칙 수</t>
+  </si>
+  <si>
+    <t>유지보수성 측정 (8.8)</t>
+  </si>
+  <si>
+    <t>MMo-1-G</t>
+  </si>
+  <si>
+    <t>컴포넌트 결합도 (Coupling of components)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 다른 컴포넌트에 영향을 주지 않는(독립적인) 컴포넌트 수, B: 독립적이어야 하는 컴포넌트 수</t>
+  </si>
+  <si>
+    <t>MMo-2-S</t>
+  </si>
+  <si>
+    <t>순환 복잡도 적정성 (Cyclomatic complexity adequacy)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 허용 임계값을 초과하는 순환 복잡도를 갖는 모듈 수, B: 전체 모듈 수</t>
+  </si>
+  <si>
+    <t>MRe-1-G</t>
+  </si>
+  <si>
+    <t>자산 재사용성 (Reusability of assets)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 재사용 가능하도록 설계/구축된 자산 수, B: 전체 자산 수</t>
+  </si>
+  <si>
+    <t>MRe-2-S</t>
+  </si>
+  <si>
+    <t>코딩 규칙 준수성 (Coding rules conformity)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 코딩 규칙을 준수하는 모듈 수, B: 전체 모듈 수</t>
+  </si>
+  <si>
+    <t>MAn-1-G</t>
+  </si>
+  <si>
+    <t>시스템 로그 완전성 (System log completeness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 실제 기록되는 로그 수, B: 감사(audit)에 필요한 것으로 요구되는 로그 수</t>
+  </si>
+  <si>
+    <t>MAn-2-S</t>
+  </si>
+  <si>
+    <t>진단 기능 유효성 (Diagnosis function effectiveness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 원인 분석에 유용한 진단 기능 수, B: 구현된 진단 기능 수</t>
+  </si>
+  <si>
+    <t>MAn-3-S</t>
+  </si>
+  <si>
+    <t>진단 기능 충분성 (Diagnosis function sufficiency)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 구현된 진단 기능 수, B: 요구되는 진단 기능 수</t>
+  </si>
+  <si>
+    <t>MMd-1-G</t>
+  </si>
+  <si>
+    <t>수정 효율성 (Modification efficiency)</t>
+  </si>
+  <si>
+    <t>X = Σ(Ai/Bi)/n. Ai: i번째 수정의 예상(기대) 소요 시간, Bi: 실제 소요 시간. 수정별 기대 대비 실적의 평균</t>
+  </si>
+  <si>
+    <t>MMd-2-S</t>
+  </si>
+  <si>
+    <t>수정 정확성 (Modification correctness)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 수정 후 일정 기간 내 장애/품질 저하를 유발한 수정 수, B: 수행된 수정 수</t>
+  </si>
+  <si>
+    <t>MMd-3-S</t>
+  </si>
+  <si>
+    <t>수정 능력 (Modification capability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 요구된 기간(time-box) 내 실제 구현된 수정 수, B: 요구된 수정 수</t>
+  </si>
+  <si>
+    <t>MTe-1-G</t>
+  </si>
+  <si>
+    <t>시험 기능 완전성 (Test function completeness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 요구대로 구현된 시험 기능(테스트 지원 기능) 수, B: 요구되는 시험 기능 수</t>
+  </si>
+  <si>
+    <t>MTe-2-S</t>
+  </si>
+  <si>
+    <t>자율 시험성 (Autonomous testability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 다른 (하위)시스템에 의존하지 않고 단독 수행 가능한 시험 수, B: 시뮬레이션으로 단독 시험이 가능해야 하는 시험 수</t>
+  </si>
+  <si>
+    <t>MTe-3-S</t>
+  </si>
+  <si>
+    <t>시험 재시작성 (Test restartability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 중단 후 체크포인트에서 재개 가능한 시험 수, B: 일시 중지가 필요한 시험 수</t>
+  </si>
+  <si>
+    <t> 이식성 측정 (8.9)</t>
+  </si>
+  <si>
+    <t>PAd-1-G</t>
+  </si>
+  <si>
+    <t>하드웨어 환경 적응성 (Hardware environmental adaptability)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 새 하드웨어 환경에서 과업을 완료하지 못했거나 요구 수준에 미달한 기능 수, B: 새 하드웨어 환경에서 시험한 기능 수</t>
+  </si>
+  <si>
+    <t>PAd-2-S</t>
+  </si>
+  <si>
+    <t>시스템 소프트웨어 환경 적응성 (System software environmental adaptability)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 새 OS/미들웨어 등 시스템 소프트웨어 환경에서 과업을 완료하지 못한 기능 수, B: 시험한 기능 수</t>
+  </si>
+  <si>
+    <t>PAd-3-S</t>
+  </si>
+  <si>
+    <t>운영 환경 적응성 (Operational environment adaptability)</t>
+  </si>
+  <si>
+    <t>X = 1 − A/B. A: 기타 새로운 운영 환경에서 과업을 완료하지 못한 기능 수, B: 시험한 기능 수</t>
+  </si>
+  <si>
+    <t>PIn-1-G</t>
+  </si>
+  <si>
+    <t>설치 시간 효율성 (Installation time efficiency)</t>
+  </si>
+  <si>
+    <t>X = Σ(Ai/Bi)/n. Ai: 예상 설치 시간, Bi: 실제 설치 시간. 설치 작업별 기대 대비 실적의 평균</t>
+  </si>
+  <si>
+    <t>PIn-2-S</t>
+  </si>
+  <si>
+    <t>설치 용이성 (Ease of installation)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 사용자 편의에 맞게 커스터마이즈 가능한 설치 절차 수, B: 커스터마이즈가 요구되는 설치 절차 수</t>
+  </si>
+  <si>
+    <t>PRe-1-G</t>
+  </si>
+  <si>
+    <t>사용 유사성 (Usage similarity)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 추가 학습이나 우회 없이 기존 제품과 유사하게 수행 가능한 기능 수, B: 기존 제품의 대응 기능 수</t>
+  </si>
+  <si>
+    <t>PRe-2-S</t>
+  </si>
+  <si>
+    <t>제품 품질 동등성 (Product quality equivalence)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 기존 제품과 동등 이상인 품질 측정 지표 수, B: 비교한 품질 측정 지표 수</t>
+  </si>
+  <si>
+    <t>PRe-3-S</t>
+  </si>
+  <si>
+    <t>기능 포괄성 (Functional inclusiveness)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 기존 제품과 유사한 결과를 산출하는 기능 수, B: 대체 대상 기존 제품의 기능 수</t>
+  </si>
+  <si>
+    <t>PRe-4-S</t>
+  </si>
+  <si>
+    <t>데이터 재사용/가져오기 능력 (Data reusability/import capability)</t>
+  </si>
+  <si>
+    <t>X = A/B. A: 기존 제품 데이터 중 계속 사용(가져오기) 가능한 데이터 수, B: 재사용이 요구되는 기존 제품 데이터 수</t>
+  </si>
+  <si>
+    <t>SAu-1-G</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3060,7 +4045,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3234,8 +4219,38 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="13.75"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3248,8 +4263,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3352,13 +4373,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3440,10 +4472,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3461,11 +4493,99 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3776,9 +4896,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA4CBF-2B00-47DE-B890-6C9CADE53CC2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="3" width="22.59765625" customWidth="1"/>
+    <col min="2" max="3" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3843,1116 +4963,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="29.09765625" defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="2" max="2" width="74.59765625" customWidth="1"/>
-    <col min="3" max="3" width="57.09765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A1" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="17"/>
-    </row>
-    <row r="2" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A2" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="18"/>
-    </row>
-    <row r="3" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A3" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="18"/>
-    </row>
-    <row r="4" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A4" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="18"/>
-    </row>
-    <row r="5" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A5" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="18"/>
-    </row>
-    <row r="6" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A6" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="18"/>
-    </row>
-    <row r="7" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A7" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="18"/>
-    </row>
-    <row r="8" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A8" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="18"/>
-    </row>
-    <row r="9" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A9" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="18"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.19921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A1" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A2" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A3" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A4" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A5" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A6" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="19.8" thickBot="1">
-      <c r="A7" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.69921875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.19921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="2" max="2" width="26.8984375" customWidth="1"/>
-    <col min="3" max="3" width="69" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="2" max="2" width="14.19921875" customWidth="1"/>
-    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
-  <cols>
-    <col min="2" max="2" width="20.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="99.8984375" customWidth="1"/>
-    <col min="4" max="5" width="5.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.19921875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="27"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="27"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="27"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="27">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" customWidth="1"/>
+    <col min="1" max="1" width="7.375" customWidth="1"/>
     <col min="2" max="13" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5339,24 +5354,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="25.69921875" customWidth="1"/>
-    <col min="2" max="2" width="64.09765625" customWidth="1"/>
-    <col min="3" max="3" width="40.8984375" customWidth="1"/>
-    <col min="4" max="4" width="25.69921875" customWidth="1"/>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="64.125" customWidth="1"/>
+    <col min="3" max="3" width="40.875" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="17.25">
       <c r="A1" s="10" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1"/>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
+    <row r="3" spans="1:3" ht="17.25" thickBot="1">
       <c r="A3" s="11" t="s">
         <v>135</v>
       </c>
@@ -5367,7 +5382,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.2" thickBot="1">
+    <row r="4" spans="1:3" ht="29.25" thickBot="1">
       <c r="A4" s="12" t="s">
         <v>138</v>
       </c>
@@ -5378,7 +5393,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="42" thickBot="1">
+    <row r="5" spans="1:3" ht="43.5" thickBot="1">
       <c r="A5" s="12" t="s">
         <v>141</v>
       </c>
@@ -5389,7 +5404,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="42" thickBot="1">
+    <row r="6" spans="1:3" ht="43.5" thickBot="1">
       <c r="A6" s="12" t="s">
         <v>144</v>
       </c>
@@ -5400,7 +5415,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="42" thickBot="1">
+    <row r="7" spans="1:3" ht="45" thickBot="1">
       <c r="A7" s="12" t="s">
         <v>147</v>
       </c>
@@ -5411,7 +5426,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="42" thickBot="1">
+    <row r="8" spans="1:3" ht="45" thickBot="1">
       <c r="A8" s="15" t="s">
         <v>155</v>
       </c>
@@ -5422,7 +5437,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="27.6">
+    <row r="9" spans="1:3" ht="28.5">
       <c r="A9" s="15" t="s">
         <v>154</v>
       </c>
@@ -5437,4 +5452,2464 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="74.625" customWidth="1"/>
+    <col min="3" max="3" width="57.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="18" thickBot="1">
+      <c r="A8" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9" spans="1:3" ht="18" thickBot="1">
+      <c r="A9" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="18"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="69" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="99.875" customWidth="1"/>
+    <col min="4" max="5" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12054B3A-2648-4FB0-BBA9-9ACDCE3B68E0}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="39.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="105" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="36"/>
+      <c r="B3" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="36"/>
+      <c r="B4" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A5" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="36"/>
+      <c r="B6" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A7" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A8" s="41"/>
+      <c r="B8" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A9" s="41"/>
+      <c r="B9" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A10" s="41"/>
+      <c r="B10" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A11" s="41"/>
+      <c r="B11" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A12" s="41"/>
+      <c r="B12" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A13" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A14" s="36"/>
+      <c r="B14" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A15" s="36"/>
+      <c r="B15" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" thickBot="1">
+      <c r="A16" s="36"/>
+      <c r="B16" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" thickBot="1">
+      <c r="A17" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A18" s="36"/>
+      <c r="B18" s="38" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A19" s="36"/>
+      <c r="B19" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A20" s="36"/>
+      <c r="B20" s="38" t="s">
+        <v>270</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A21" s="36"/>
+      <c r="B21" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" thickBot="1">
+      <c r="A22" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A23" s="36"/>
+      <c r="B23" s="38" t="s">
+        <v>277</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A24" s="41"/>
+      <c r="B24" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A25" s="36"/>
+      <c r="B25" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A26" s="41"/>
+      <c r="B26" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
+      <c r="A27" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="35" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A28" s="41"/>
+      <c r="B28" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="35" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A29" s="41"/>
+      <c r="B29" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="17.25">
+      <c r="B30" s="42" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57942659-D9CB-45B1-9A8D-84CB397A0EAA}">
+  <dimension ref="A1:C96"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="97.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B1" s="34" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" thickBot="1">
+      <c r="A8" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" thickBot="1">
+      <c r="A9" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" thickBot="1">
+      <c r="A10" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" thickBot="1">
+      <c r="A11" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" thickBot="1">
+      <c r="A12" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" thickBot="1">
+      <c r="A13" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" thickBot="1">
+      <c r="A14" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B15" s="34" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" thickBot="1">
+      <c r="A16" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" thickBot="1">
+      <c r="A17" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" thickBot="1">
+      <c r="A18" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" thickBot="1">
+      <c r="A19" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" thickBot="1">
+      <c r="A20" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B21" s="34" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" thickBot="1">
+      <c r="A22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" thickBot="1">
+      <c r="A23" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" thickBot="1">
+      <c r="A24" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" thickBot="1">
+      <c r="A25" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18" thickBot="1">
+      <c r="A26" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18" thickBot="1">
+      <c r="A27" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18" thickBot="1">
+      <c r="A28" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" thickBot="1">
+      <c r="A29" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18" thickBot="1">
+      <c r="A30" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18" thickBot="1">
+      <c r="A31" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18" thickBot="1">
+      <c r="A32" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" thickBot="1">
+      <c r="A33" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" thickBot="1">
+      <c r="A34" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18" thickBot="1">
+      <c r="A35" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18" thickBot="1">
+      <c r="A36" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18" thickBot="1">
+      <c r="A37" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18" thickBot="1">
+      <c r="A38" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A39" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18" thickBot="1">
+      <c r="A40" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18" thickBot="1">
+      <c r="A41" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18" thickBot="1">
+      <c r="A42" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18" thickBot="1">
+      <c r="A43" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" thickBot="1">
+      <c r="A44" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B45" s="34" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="18" thickBot="1">
+      <c r="A46" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="18" thickBot="1">
+      <c r="A47" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="18" thickBot="1">
+      <c r="A48" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18" thickBot="1">
+      <c r="A49" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18" thickBot="1">
+      <c r="A50" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18" thickBot="1">
+      <c r="A51" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18" thickBot="1">
+      <c r="A52" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A53" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18" thickBot="1">
+      <c r="A54" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18" thickBot="1">
+      <c r="A55" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18" thickBot="1">
+      <c r="A56" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18" thickBot="1">
+      <c r="A57" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>444</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B58" s="34" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18" thickBot="1">
+      <c r="A59" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A60" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="18" thickBot="1">
+      <c r="A61" s="18" t="s">
+        <v>450</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A62" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="18" thickBot="1">
+      <c r="A63" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="18" thickBot="1">
+      <c r="A64" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="18" thickBot="1">
+      <c r="A65" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="18" thickBot="1">
+      <c r="A66" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="18" thickBot="1">
+      <c r="A67" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="18" thickBot="1">
+      <c r="A68" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="18" thickBot="1">
+      <c r="A69" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="18" thickBot="1">
+      <c r="A70" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B71" s="34" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="18" thickBot="1">
+      <c r="A72" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="18" thickBot="1">
+      <c r="A73" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="18" thickBot="1">
+      <c r="A74" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="18" thickBot="1">
+      <c r="A75" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="18" thickBot="1">
+      <c r="A76" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="18" thickBot="1">
+      <c r="A77" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="18" thickBot="1">
+      <c r="A78" s="18" t="s">
+        <v>495</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="18" thickBot="1">
+      <c r="A79" s="18" t="s">
+        <v>498</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="18" thickBot="1">
+      <c r="A80" s="18" t="s">
+        <v>501</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>502</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="18" thickBot="1">
+      <c r="A81" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>505</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="18" thickBot="1">
+      <c r="A82" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="18" thickBot="1">
+      <c r="A83" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A84" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="18" thickBot="1">
+      <c r="A85" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>517</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="21.75" thickBot="1">
+      <c r="B86" s="34" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="18" thickBot="1">
+      <c r="A87" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A88" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>521</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A89" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="18" thickBot="1">
+      <c r="A90" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>527</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="18" thickBot="1">
+      <c r="A91" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="18" thickBot="1">
+      <c r="A92" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="18" thickBot="1">
+      <c r="A93" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="18" thickBot="1">
+      <c r="A94" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>539</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="18" thickBot="1">
+      <c r="A95" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="35.25" thickBot="1">
+      <c r="A96" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>546</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="G">
+      <formula>NOT(ISERROR(SEARCH("G",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{DC55A607-D788-43DD-B6E0-8B9BFF0D89E9}">
+            <xm:f>NOT(ISERROR(SEARCH(-G,A1)))</xm:f>
+            <xm:f>-G</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A1:A1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECE81D3-6EC0-42EF-9BAB-48ECE2CD119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9978906F-4E91-4AD1-9EF2-946CCB5CA628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="7" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -27,6 +27,9 @@
     <sheet name="ContextView" sheetId="12" r:id="rId12"/>
     <sheet name="DP" sheetId="13" r:id="rId13"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ISO 25023'!$A$2:$J$96</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -45,38 +48,396 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>boram1288</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{1A4EB176-0ADA-4A1D-AF39-9BF5EA40BFA0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>boram1288:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>모든</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> Generic(G) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>지표는</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>반드시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">사용
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Specific(S) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>지표는</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>관련성이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>있을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>때</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>선택적으로</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용
+지표를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>수정하면</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>근거를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>제시하고</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>추가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>지표는</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> ISO/IEC 25021</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> QME </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>규칙에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>따라</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>정의</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="548">
-  <si>
-    <t>품질 속성</t>
-  </si>
-  <si>
-    <t>중요도</t>
-  </si>
-  <si>
-    <t>난이도</t>
-  </si>
-  <si>
-    <t>보안 (Host 침해 기밀성)</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>성능 (실시간 처리)</t>
-  </si>
-  <si>
-    <t>성능 (통신 오버헤드)</t>
-  </si>
-  <si>
-    <t>자원 효율</t>
-  </si>
-  <si>
-    <t>변경 용이성 (Secure OS 교체)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="578">
   <si>
     <t>QA-01</t>
   </si>
@@ -333,24 +694,6 @@
     <t>Android 스택에 의존하지 않고 Linux에서 네이티브로 동작한다.</t>
   </si>
   <si>
-    <t>Host가 완전히 침해되어도 pVM 내 영상/모델/추론 데이터는 노출되지 않는다.</t>
-  </si>
-  <si>
-    <t>영상 입력이 유입될 때 Camera/AI HW 가속으로 격리 환경에서도 실시간 처리 속도를 만족한다.</t>
-  </si>
-  <si>
-    <t>도메인 간 대용량 데이터 전달 시 통신 오버헤드가 실시간성을 해치지 않는다.</t>
-  </si>
-  <si>
-    <t>보안 기능 활성화 시 메모리/전력 오버헤드가 탑재 가능 한도 이내로 유지된다.</t>
-  </si>
-  <si>
-    <t>Secure OS/Framework 버전이 변경될 때 정의된 인터페이스만으로 대응하고 재이식하지 않는다.</t>
-  </si>
-  <si>
-    <t>격리 검증이 필요할 때 Host 침해를 모사한 시험으로 객관적으로 검증할 수 있다.</t>
-  </si>
-  <si>
     <r>
       <t>pVM</t>
     </r>
@@ -460,30 +803,6 @@
       <t>전송한다</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>우선순위</t>
-  </si>
-  <si>
-    <t>[침해 테스트 시험에서 pVM 소유 메모리로부터 읽힌 바이트 수 = 0건]</t>
-  </si>
-  <si>
-    <t>시험 용이성 (격리 검증)</t>
-  </si>
-  <si>
-    <t>[전체 파이프라인에 대해서 (비격리 fps - 격리 fps) / 비격리 fps &lt;= 10%]</t>
-  </si>
-  <si>
-    <t>[도메인 간 dma-buf 버퍼 전달 시 memcpy 호출 횟수 = 0회]</t>
-  </si>
-  <si>
-    <t>[(격리 메모리 - 비격리 메모리) &lt;= 256MB, (격리 전력 - 비격리 전력) / 비격리 전력 &lt;= 5%]</t>
-  </si>
-  <si>
-    <t>[(전체 공격 벡터 항목 - 미커버 항목) / 전체 항목 = 100%]</t>
-  </si>
-  <si>
-    <t>[Secure OS 교체 전후 diff에서 Secure OS 패키지 외부 변경 파일 수 = 0개]</t>
   </si>
   <si>
     <r>
@@ -1005,70 +1324,6 @@
   </si>
   <si>
     <t>H</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QA-06</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가용성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (pVM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장애</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>격리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1215,404 +1470,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>[Host/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다른</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> VM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비정상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>동작</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비정상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>동작</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)]</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[Workload </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전후</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> diff</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> Framework </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>라인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = 0 LoC]</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>pVM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비정상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>종료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>오동작해도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Host/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다른</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> pVM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>동작은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>유지된다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Host Application</t>
   </si>
   <si>
@@ -2794,198 +2651,6 @@
     <t>pVM내에서 암호화/복호화 명령을 Secure OS에 전달하는 기능을 제공한다.</t>
   </si>
   <si>
-    <t>QA-02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QA-03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QA-04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QA-05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QA-07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>QA-08</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>신규</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시나리오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Framework </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>코드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수정이 없어야 한다.</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확장성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>신규 시나리오</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>2026-10-30까지 제한된 인력으로 E2E 데모를 완료해야 한다.</t>
   </si>
   <si>
@@ -3818,6 +3483,9 @@
     <t>X = A/B. A: 안정적 저장소에 로그가 실제 보존되는 기간, B: 요구되는 로그 보존 기간</t>
   </si>
   <si>
+    <t>SAu-1-G</t>
+  </si>
+  <si>
     <t>인증 메커니즘 충분성 (Authentication mechanism sufficiency)</t>
   </si>
   <si>
@@ -4037,7 +3705,297 @@
     <t>X = A/B. A: 기존 제품 데이터 중 계속 사용(가져오기) 가능한 데이터 수, B: 재사용이 요구되는 기존 제품 데이터 수</t>
   </si>
   <si>
-    <t>SAu-1-G</t>
+    <t>부특성</t>
+  </si>
+  <si>
+    <t>시간 반응성</t>
+  </si>
+  <si>
+    <t>자원 활용성</t>
+  </si>
+  <si>
+    <t>용량</t>
+  </si>
+  <si>
+    <t>공존성</t>
+  </si>
+  <si>
+    <t>상호운용성</t>
+  </si>
+  <si>
+    <t>적절성 인식성</t>
+  </si>
+  <si>
+    <t>학습성</t>
+  </si>
+  <si>
+    <t>운용성</t>
+  </si>
+  <si>
+    <t>사용자 오류 방지</t>
+  </si>
+  <si>
+    <t>UI 심미성</t>
+  </si>
+  <si>
+    <t>접근성</t>
+  </si>
+  <si>
+    <t>성숙성</t>
+  </si>
+  <si>
+    <t>가용성</t>
+  </si>
+  <si>
+    <t>결함 허용성</t>
+  </si>
+  <si>
+    <t>복구성</t>
+  </si>
+  <si>
+    <t>기밀성</t>
+  </si>
+  <si>
+    <t>무결성</t>
+  </si>
+  <si>
+    <t>부인 방지</t>
+  </si>
+  <si>
+    <t>책임 추적성</t>
+  </si>
+  <si>
+    <t>인증성</t>
+  </si>
+  <si>
+    <t>모듈성</t>
+  </si>
+  <si>
+    <t>재사용성</t>
+  </si>
+  <si>
+    <t>분석성</t>
+  </si>
+  <si>
+    <t>수정성</t>
+  </si>
+  <si>
+    <t>시험성</t>
+  </si>
+  <si>
+    <t>적응성</t>
+  </si>
+  <si>
+    <t>설치성</t>
+  </si>
+  <si>
+    <t>대체성</t>
+  </si>
+  <si>
+    <t>중요도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>난이도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>측정방법</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 항목 수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재사용되는 모듈 수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>결함 패턴 수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용되는 메모리 크기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>720p, RGB24 기준, AI구간 제외, E2E 평균 시간 ms</t>
+  </si>
+  <si>
+    <t>구체적인 고객, HW제약사항이 정해져 있지 않음으로 정의 불가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>관련성 없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B가 고객사에 따라 가변적</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 자동화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OS update에 따른 변경 최소화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>결합도가 낮아야 함</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HW 변경에 따른 변경 최소화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신뢰성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>보안성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유지보수성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이식성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>품질 속성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(720p, RGB24 기준, AI 추론 구간 제외) 카메라 영상 입력부터 Host Application전달 완료까지 평균 시간 ms</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KPI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>다중 시나리오가 운용중 일때 사용되는 메모리의 사이즈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>낮을 수록 좋음 (상대 평가)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>결함 주입 시험 테스트 통과율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도메인간 전달되는 기밀 데이터 항목 수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>요구사항 추가시 수정되지 않는 모듈 수의 최대화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시나리오 추가시에 재사용되는 모듈 수의 최대화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOC 변경에 따라 변경되는 모듈 수의 최소화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OS update에 따라 변경되는 모듈 수의 최소화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하드웨어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>환경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적응성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Hardware environmental adaptability)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도메인간 전달시 손상이 방지된 데이터의 항목수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선순위</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4045,7 +4003,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4096,12 +4054,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFA31515"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
@@ -4139,13 +4091,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Google Sans Text"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFA31515"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -4249,8 +4194,36 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4266,6 +4239,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4390,15 +4381,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4412,23 +4400,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4436,31 +4415,37 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -4469,17 +4454,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4493,38 +4514,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="9" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -4552,36 +4585,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4903,24 +4906,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>2021</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4928,10 +4931,10 @@
         <v>2022</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4939,10 +4942,10 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4950,10 +4953,10 @@
         <v>2025</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4972,375 +4975,375 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="42"/>
+      <c r="O5" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="42"/>
+      <c r="O7" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="5" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="32"/>
-      <c r="O5" s="24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="5" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="O7" s="25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="5" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="42"/>
+      <c r="O14" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="42"/>
+      <c r="O15" s="23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="32"/>
-      <c r="O14" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="32"/>
-      <c r="O15" s="25" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5366,86 +5369,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25">
-      <c r="A1" s="10" t="s">
-        <v>134</v>
+      <c r="A1" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>136</v>
+      <c r="A3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A4" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>139</v>
+      <c r="A4" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.5" thickBot="1">
-      <c r="A5" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>142</v>
+      <c r="A5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="43.5" thickBot="1">
-      <c r="A6" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>145</v>
+      <c r="A6" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" thickBot="1">
-      <c r="A7" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>148</v>
+      <c r="A7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" thickBot="1">
-      <c r="A8" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>150</v>
+      <c r="A8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.5">
-      <c r="A9" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>152</v>
+      <c r="A9" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -5464,85 +5467,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="17"/>
+      <c r="A1" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="18"/>
+      <c r="A2" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="18"/>
+      <c r="A3" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="18"/>
+      <c r="A4" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="16"/>
     </row>
     <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="18"/>
+      <c r="A5" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="18"/>
+      <c r="A6" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="18"/>
+      <c r="A7" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3" ht="18" thickBot="1">
-      <c r="A8" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="18"/>
+      <c r="A8" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="16"/>
     </row>
     <row r="9" spans="1:3" ht="18" thickBot="1">
-      <c r="A9" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="18"/>
+      <c r="A9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -5561,80 +5564,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>191</v>
+      <c r="A1" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>192</v>
+      <c r="A2" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>193</v>
+      <c r="A3" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>194</v>
+      <c r="A4" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>195</v>
+      <c r="A5" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>196</v>
+      <c r="A6" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>197</v>
+      <c r="A7" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5654,102 +5657,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5768,190 +5771,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="5" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="5" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -5971,125 +5974,125 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -6108,79 +6111,79 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>209</v>
+      <c r="C5" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>210</v>
+      <c r="A6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>211</v>
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -6200,39 +6203,39 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="3"/>
+      <c r="A2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -6242,318 +6245,346 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="20.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="99.875" customWidth="1"/>
-    <col min="4" max="5" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="51.25" customWidth="1"/>
+    <col min="5" max="5" width="86.25" customWidth="1"/>
+    <col min="6" max="6" width="12.25" customWidth="1"/>
+    <col min="7" max="8" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:9" s="39" customFormat="1" ht="17.25">
+      <c r="A1" s="37" t="s">
+        <v>562</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>511</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>563</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>565</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>540</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>541</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.25">
+      <c r="A2" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>512</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>564</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>566</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="32">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="51.75">
+      <c r="A3" s="44" t="s">
+        <v>557</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>513</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>567</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>568</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="32">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="26" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="34.5">
+      <c r="A4" s="44" t="s">
+        <v>558</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>525</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>569</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="54">
+        <v>1</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>555</v>
+      </c>
+      <c r="I4" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="34.5">
+      <c r="A5" s="44" t="s">
+        <v>559</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>527</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>570</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>412</v>
+      </c>
+      <c r="F5" s="54">
+        <v>1</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>555</v>
+      </c>
+      <c r="I5" s="32">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="27" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="17.25">
+      <c r="A6" s="47" t="s">
+        <v>559</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>528</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>420</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>576</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="F6" s="53">
+        <v>1</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="1:9" ht="34.5">
+      <c r="A7" s="47" t="s">
+        <v>560</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>532</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>445</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>571</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>446</v>
+      </c>
+      <c r="F7" s="53">
+        <v>1</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:9" ht="17.25">
+      <c r="A8" s="44" t="s">
+        <v>560</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>533</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>572</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>452</v>
+      </c>
+      <c r="F8" s="54">
+        <v>1</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>555</v>
+      </c>
+      <c r="I8" s="32">
         <v>4</v>
       </c>
-      <c r="E2" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="28">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
+    </row>
+    <row r="9" spans="1:9" ht="51.75">
+      <c r="A9" s="47" t="s">
+        <v>561</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>575</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>573</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>486</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9" ht="51.75">
+      <c r="A10" s="47" t="s">
+        <v>561</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>574</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>489</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6570,281 +6601,281 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="25"/>
+      <c r="B3" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A5" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="25"/>
+      <c r="B6" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A7" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A9" s="30"/>
+      <c r="B9" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A10" s="30"/>
+      <c r="B10" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A11" s="30"/>
+      <c r="B11" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A12" s="30"/>
+      <c r="B12" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A13" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A14" s="25"/>
+      <c r="B14" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A15" s="25"/>
+      <c r="B15" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" thickBot="1">
+      <c r="A16" s="25"/>
+      <c r="B16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" thickBot="1">
+      <c r="A17" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="37" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A18" s="25"/>
+      <c r="B18" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="C18" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="38" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A19" s="25"/>
+      <c r="B19" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A20" s="25"/>
+      <c r="B20" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A21" s="25"/>
+      <c r="B21" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" thickBot="1">
+      <c r="A22" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A23" s="25"/>
+      <c r="B23" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A24" s="30"/>
+      <c r="B24" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A25" s="25"/>
+      <c r="B25" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A27" s="28" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="38" t="s">
+      <c r="B27" s="29" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="36"/>
-      <c r="B4" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="38" t="s">
+      <c r="C27" s="29" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A5" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="40" t="s">
+    <row r="28" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A28" s="30"/>
+      <c r="B28" s="29" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="38" t="s">
+      <c r="C28" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="38" t="s">
+    </row>
+    <row r="29" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A29" s="30"/>
+      <c r="B29" s="29" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A7" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A9" s="41"/>
-      <c r="B9" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A10" s="41"/>
-      <c r="B10" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A11" s="41"/>
-      <c r="B11" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A12" s="41"/>
-      <c r="B12" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A13" s="39" t="s">
+      <c r="C29" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="40" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="17.25">
+      <c r="B30" s="31" t="s">
         <v>255</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" thickBot="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" thickBot="1">
-      <c r="A17" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A18" s="36"/>
-      <c r="B18" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A19" s="36"/>
-      <c r="B19" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A20" s="36"/>
-      <c r="B20" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A21" s="36"/>
-      <c r="B21" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" thickBot="1">
-      <c r="A22" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A23" s="36"/>
-      <c r="B23" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="35" customFormat="1" ht="18" thickBot="1">
-      <c r="A27" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="B27" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="35" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="35" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.25">
-      <c r="B30" s="42" t="s">
-        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -6854,1046 +6885,1750 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57942659-D9CB-45B1-9A8D-84CB397A0EAA}">
-  <dimension ref="A1:C96"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57942659-D9CB-45B1-9A8D-84CB397A0EAA}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18.25" customWidth="1"/>
-    <col min="2" max="2" width="62" customWidth="1"/>
-    <col min="3" max="3" width="97.625" customWidth="1"/>
+    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="97.625" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B1" s="34" t="s">
+    <row r="1" spans="1:9" s="39" customFormat="1" ht="21">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="38" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37" t="s">
+        <v>540</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>541</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.25">
+      <c r="A2" s="39" t="s">
+        <v>562</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="33"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:9" ht="17.25" hidden="1">
+      <c r="B3" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="F3" s="34"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+    </row>
+    <row r="4" spans="1:9" ht="17.25" hidden="1">
+      <c r="B4" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="F4" s="34"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+    </row>
+    <row r="5" spans="1:9" ht="17.25" hidden="1">
+      <c r="B5" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F5" s="34"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="1:9" s="46" customFormat="1" ht="17.25">
+      <c r="A6" s="46" t="s">
+        <v>557</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>512</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="44"/>
+      <c r="I6" s="46" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.25" hidden="1">
+      <c r="B7" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="34"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+    </row>
+    <row r="8" spans="1:9" ht="17.25" hidden="1">
+      <c r="B8" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="F8" s="34"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+    </row>
+    <row r="9" spans="1:9" s="46" customFormat="1" ht="17.25">
+      <c r="A9" s="46" t="s">
+        <v>557</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="44"/>
+      <c r="I9" s="46" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" hidden="1">
+      <c r="B10" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="F10" s="34"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" hidden="1">
+      <c r="B11" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="34"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" hidden="1">
+      <c r="B12" s="32" t="s">
+        <v>514</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" hidden="1">
+      <c r="B13" s="32" t="s">
+        <v>514</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" hidden="1">
+      <c r="B14" s="32" t="s">
+        <v>514</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" s="34"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+    </row>
+    <row r="15" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+    </row>
+    <row r="16" spans="1:9" ht="17.25" hidden="1">
+      <c r="B16" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+    </row>
+    <row r="17" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B17" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="F17" s="36"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="24" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="17.25" hidden="1">
+      <c r="B18" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="17.25" hidden="1">
+      <c r="B19" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+    </row>
+    <row r="20" spans="2:9" ht="17.25" hidden="1">
+      <c r="B20" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+    </row>
+    <row r="21" spans="2:9" s="39" customFormat="1" ht="21" hidden="1">
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+    </row>
+    <row r="22" spans="2:9" ht="17.25" hidden="1">
+      <c r="B22" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B23" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>309</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="F23" s="36"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="24" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B24" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="F24" s="36"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+    </row>
+    <row r="25" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B25" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+    </row>
+    <row r="26" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B26" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>318</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="F26" s="36"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+    </row>
+    <row r="27" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B27" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>322</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="F27" s="36"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+    </row>
+    <row r="28" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B28" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="F28" s="36"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+    </row>
+    <row r="29" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B29" s="35" t="s">
+        <v>518</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="F29" s="36"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+    </row>
+    <row r="30" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B30" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="D30" s="36" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" thickBot="1">
-      <c r="A8" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" thickBot="1">
-      <c r="A9" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="18" thickBot="1">
-      <c r="A10" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="18" thickBot="1">
-      <c r="A11" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="18" thickBot="1">
-      <c r="A12" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="18" thickBot="1">
-      <c r="A13" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" thickBot="1">
-      <c r="A14" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B15" s="34" t="s">
+      <c r="E30" s="36" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" thickBot="1">
-      <c r="A16" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" thickBot="1">
-      <c r="A17" s="18" t="s">
+      <c r="F30" s="36"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+    </row>
+    <row r="31" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B31" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C31" s="36" t="s">
         <v>333</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="D31" s="36" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="E31" s="36" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" thickBot="1">
-      <c r="A18" s="18" t="s">
+      <c r="F31" s="36"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+    </row>
+    <row r="32" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B32" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C32" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="D32" s="36" t="s">
         <v>337</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="E32" s="36" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" thickBot="1">
-      <c r="A19" s="18" t="s">
+      <c r="F32" s="36"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+    </row>
+    <row r="33" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B33" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C33" s="36" t="s">
         <v>339</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="D33" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="E33" s="36" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" thickBot="1">
-      <c r="A20" s="18" t="s">
+      <c r="F33" s="36"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+    </row>
+    <row r="34" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B34" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C34" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="D34" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="E34" s="36" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B21" s="34" t="s">
+      <c r="F34" s="36"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+    </row>
+    <row r="35" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B35" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C35" s="36" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" thickBot="1">
-      <c r="A22" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" thickBot="1">
-      <c r="A23" s="18" t="s">
+      <c r="D35" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="E35" s="36" t="s">
         <v>347</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="F35" s="36"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+    </row>
+    <row r="36" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B36" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C36" s="36" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="18" thickBot="1">
-      <c r="A24" s="18" t="s">
+      <c r="D36" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="E36" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="F36" s="36"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+    </row>
+    <row r="37" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B37" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C37" s="36" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" thickBot="1">
-      <c r="A25" s="18" t="s">
+      <c r="D37" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="E37" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="F37" s="36"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+    </row>
+    <row r="38" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B38" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="C38" s="36" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="18" thickBot="1">
-      <c r="A26" s="18" t="s">
+      <c r="D38" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="E38" s="36" t="s">
         <v>356</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="F38" s="36"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+    </row>
+    <row r="39" spans="2:8" s="24" customFormat="1" ht="34.5" hidden="1">
+      <c r="B39" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="C39" s="36" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="18" thickBot="1">
-      <c r="A27" s="18" t="s">
+      <c r="D39" s="36" t="s">
         <v>358</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="E39" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="F39" s="36"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+    </row>
+    <row r="40" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B40" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="C40" s="36" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="18" thickBot="1">
-      <c r="A28" s="18" t="s">
+      <c r="D40" s="36" t="s">
         <v>361</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="E40" s="36" t="s">
         <v>362</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="F40" s="36"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+    </row>
+    <row r="41" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B41" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="C41" s="36" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="18" thickBot="1">
-      <c r="A29" s="18" t="s">
+      <c r="D41" s="36" t="s">
         <v>364</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="E41" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="F41" s="36"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+    </row>
+    <row r="42" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B42" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="C42" s="36" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="18" thickBot="1">
-      <c r="A30" s="18" t="s">
+      <c r="D42" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="E42" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="F42" s="36"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+    </row>
+    <row r="43" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B43" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="C43" s="36" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="18" thickBot="1">
-      <c r="A31" s="18" t="s">
+      <c r="D43" s="36" t="s">
         <v>370</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="E43" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="F43" s="36"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+    </row>
+    <row r="44" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B44" s="35" t="s">
+        <v>522</v>
+      </c>
+      <c r="C44" s="36" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="18" thickBot="1">
-      <c r="A32" s="18" t="s">
+      <c r="D44" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="E44" s="36" t="s">
         <v>374</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="F44" s="36"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+    </row>
+    <row r="45" spans="2:8" s="39" customFormat="1" ht="21" hidden="1">
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="38" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="18" thickBot="1">
-      <c r="A33" s="18" t="s">
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+    </row>
+    <row r="46" spans="2:8" ht="17.25" hidden="1">
+      <c r="B46" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F46" s="33"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+    </row>
+    <row r="47" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B47" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="C47" s="36" t="s">
         <v>376</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="D47" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="E47" s="36" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="18" thickBot="1">
-      <c r="A34" s="18" t="s">
+      <c r="F47" s="36"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+    </row>
+    <row r="48" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B48" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="C48" s="36" t="s">
         <v>379</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="D48" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="E48" s="36" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="18" thickBot="1">
-      <c r="A35" s="18" t="s">
+      <c r="F48" s="36"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+    </row>
+    <row r="49" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B49" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="C49" s="36" t="s">
         <v>382</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="D49" s="36" t="s">
         <v>383</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="E49" s="36" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="18" thickBot="1">
-      <c r="A36" s="18" t="s">
+      <c r="F49" s="36"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="35"/>
+    </row>
+    <row r="50" spans="1:9" s="49" customFormat="1" ht="17.25">
+      <c r="A50" s="49" t="s">
+        <v>558</v>
+      </c>
+      <c r="B50" s="47" t="s">
+        <v>523</v>
+      </c>
+      <c r="C50" s="48" t="s">
         <v>385</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="D50" s="48" t="s">
         <v>386</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="E50" s="48" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="18" thickBot="1">
-      <c r="A37" s="18" t="s">
+      <c r="F50" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="G50" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="H50" s="47"/>
+      <c r="I50" s="49" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="17.25" hidden="1">
+      <c r="B51" s="32" t="s">
+        <v>524</v>
+      </c>
+      <c r="C51" s="34" t="s">
         <v>388</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="D51" s="34" t="s">
         <v>389</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="E51" s="34" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="18" thickBot="1">
-      <c r="A38" s="18" t="s">
+      <c r="F51" s="34"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+    </row>
+    <row r="52" spans="1:9" ht="17.25" hidden="1">
+      <c r="B52" s="32" t="s">
+        <v>524</v>
+      </c>
+      <c r="C52" s="34" t="s">
         <v>391</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="D52" s="34" t="s">
         <v>392</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="E52" s="34" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A39" s="18" t="s">
+      <c r="F52" s="34"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+    </row>
+    <row r="53" spans="1:9" s="46" customFormat="1" ht="34.5">
+      <c r="A53" s="46" t="s">
+        <v>558</v>
+      </c>
+      <c r="B53" s="44" t="s">
+        <v>525</v>
+      </c>
+      <c r="C53" s="45" t="s">
         <v>394</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="D53" s="45" t="s">
         <v>395</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="E53" s="45" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="18" thickBot="1">
-      <c r="A40" s="18" t="s">
+      <c r="F53" s="45"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="46" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="17.25" hidden="1">
+      <c r="B54" s="32" t="s">
+        <v>525</v>
+      </c>
+      <c r="C54" s="34" t="s">
         <v>397</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="D54" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="E54" s="34" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="18" thickBot="1">
-      <c r="A41" s="18" t="s">
+      <c r="F54" s="34"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+    </row>
+    <row r="55" spans="1:9" ht="17.25" hidden="1">
+      <c r="B55" s="32" t="s">
+        <v>525</v>
+      </c>
+      <c r="C55" s="34" t="s">
         <v>400</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="D55" s="34" t="s">
         <v>401</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="E55" s="34" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="18" thickBot="1">
-      <c r="A42" s="18" t="s">
+      <c r="F55" s="34"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+    </row>
+    <row r="56" spans="1:9" ht="17.25" hidden="1">
+      <c r="B56" s="32" t="s">
+        <v>526</v>
+      </c>
+      <c r="C56" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="D56" s="34" t="s">
         <v>404</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="E56" s="34" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="18" thickBot="1">
-      <c r="A43" s="18" t="s">
+      <c r="F56" s="34"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+    </row>
+    <row r="57" spans="1:9" ht="17.25" hidden="1">
+      <c r="B57" s="32" t="s">
+        <v>526</v>
+      </c>
+      <c r="C57" s="34" t="s">
         <v>406</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="D57" s="34" t="s">
         <v>407</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="E57" s="34" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="18" thickBot="1">
-      <c r="A44" s="18" t="s">
+      <c r="F57" s="34"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+    </row>
+    <row r="58" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="38" t="s">
         <v>409</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+    </row>
+    <row r="59" spans="1:9" ht="17.25" hidden="1">
+      <c r="B59" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E59" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F59" s="33"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+    </row>
+    <row r="60" spans="1:9" s="46" customFormat="1" ht="34.5">
+      <c r="A60" s="46" t="s">
+        <v>559</v>
+      </c>
+      <c r="B60" s="44" t="s">
+        <v>527</v>
+      </c>
+      <c r="C60" s="45" t="s">
         <v>410</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="D60" s="45" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B45" s="34" t="s">
+      <c r="E60" s="45" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="18" thickBot="1">
-      <c r="A46" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="18" thickBot="1">
-      <c r="A47" s="18" t="s">
+      <c r="F60" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H60" s="44"/>
+      <c r="I60" s="46" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="17.25" hidden="1">
+      <c r="B61" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="C61" s="34" t="s">
         <v>413</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="D61" s="34" t="s">
         <v>414</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="E61" s="34" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="18" thickBot="1">
-      <c r="A48" s="18" t="s">
+      <c r="F61" s="34"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+    </row>
+    <row r="62" spans="1:9" ht="34.5" hidden="1">
+      <c r="B62" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="C62" s="34" t="s">
         <v>416</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="D62" s="34" t="s">
         <v>417</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="E62" s="34" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="18" thickBot="1">
-      <c r="A49" s="18" t="s">
+      <c r="F62" s="34"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+    </row>
+    <row r="63" spans="1:9" s="49" customFormat="1" ht="17.25">
+      <c r="A63" s="49" t="s">
+        <v>559</v>
+      </c>
+      <c r="B63" s="47" t="s">
+        <v>528</v>
+      </c>
+      <c r="C63" s="48" t="s">
         <v>419</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="D63" s="48" t="s">
         <v>420</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="E63" s="48" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="18" thickBot="1">
-      <c r="A50" s="18" t="s">
+      <c r="F63" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="G63" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="H63" s="47"/>
+      <c r="I63" s="49" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="17.25" hidden="1">
+      <c r="B64" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C64" s="34" t="s">
         <v>422</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="D64" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="E64" s="34" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="18" thickBot="1">
-      <c r="A51" s="18" t="s">
+      <c r="F64" s="34"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+    </row>
+    <row r="65" spans="1:9" ht="17.25" hidden="1">
+      <c r="B65" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C65" s="34" t="s">
         <v>425</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="D65" s="34" t="s">
         <v>426</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="E65" s="34" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="18" thickBot="1">
-      <c r="A52" s="18" t="s">
+      <c r="F65" s="34"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+    </row>
+    <row r="66" spans="1:9" ht="17.25" hidden="1">
+      <c r="B66" s="32" t="s">
+        <v>529</v>
+      </c>
+      <c r="C66" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="B52" s="18" t="s">
+      <c r="D66" s="34" t="s">
         <v>429</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="E66" s="34" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A53" s="18" t="s">
+      <c r="F66" s="34"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+    </row>
+    <row r="67" spans="1:9" ht="17.25" hidden="1">
+      <c r="B67" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="C67" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="D67" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="E67" s="34" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="18" thickBot="1">
-      <c r="A54" s="18" t="s">
+      <c r="F67" s="34"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+    </row>
+    <row r="68" spans="1:9" ht="17.25" hidden="1">
+      <c r="B68" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="C68" s="34" t="s">
         <v>434</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="D68" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="E68" s="34" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="18" thickBot="1">
-      <c r="A55" s="18" t="s">
+      <c r="F68" s="34"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="1:9" ht="17.25" hidden="1">
+      <c r="B69" s="32" t="s">
+        <v>531</v>
+      </c>
+      <c r="C69" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="D69" s="34" t="s">
         <v>438</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="E69" s="34" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="18" thickBot="1">
-      <c r="A56" s="18" t="s">
+      <c r="F69" s="34"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+    </row>
+    <row r="70" spans="1:9" ht="17.25" hidden="1">
+      <c r="B70" s="32" t="s">
+        <v>531</v>
+      </c>
+      <c r="C70" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="D70" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="E70" s="34" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="18" thickBot="1">
-      <c r="A57" s="18" t="s">
+      <c r="F70" s="34"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+    </row>
+    <row r="71" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+      <c r="B71" s="37"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="38" t="s">
         <v>443</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37"/>
+    </row>
+    <row r="72" spans="1:9" ht="17.25" hidden="1">
+      <c r="B72" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C72" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E72" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F72" s="33"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+    </row>
+    <row r="73" spans="1:9" s="49" customFormat="1" ht="17.25">
+      <c r="A73" s="49" t="s">
+        <v>560</v>
+      </c>
+      <c r="B73" s="47" t="s">
+        <v>532</v>
+      </c>
+      <c r="C73" s="48" t="s">
         <v>444</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="D73" s="48" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B58" s="34" t="s">
+      <c r="E73" s="48" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="18" thickBot="1">
-      <c r="A59" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A60" s="18" t="s">
+      <c r="F73" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="G73" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="H73" s="47"/>
+      <c r="I73" s="49" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="17.25" hidden="1">
+      <c r="B74" s="32" t="s">
+        <v>532</v>
+      </c>
+      <c r="C74" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="D74" s="34" t="s">
         <v>448</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="E74" s="34" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" ht="18" thickBot="1">
-      <c r="A61" s="18" t="s">
+      <c r="F74" s="34"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+    </row>
+    <row r="75" spans="1:9" s="46" customFormat="1" ht="17.25">
+      <c r="A75" s="46" t="s">
+        <v>560</v>
+      </c>
+      <c r="B75" s="44" t="s">
+        <v>533</v>
+      </c>
+      <c r="C75" s="45" t="s">
         <v>450</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="D75" s="45" t="s">
         <v>451</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="E75" s="45" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A62" s="18" t="s">
+      <c r="F75" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="G75" s="44" t="s">
+        <v>555</v>
+      </c>
+      <c r="H75" s="44"/>
+      <c r="I75" s="46" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="17.25" hidden="1">
+      <c r="B76" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C76" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="D76" s="34" t="s">
         <v>454</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="E76" s="34" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="18" thickBot="1">
-      <c r="A63" s="18" t="s">
+      <c r="F76" s="34"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+    </row>
+    <row r="77" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B77" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="C77" s="36" t="s">
         <v>456</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="D77" s="36" t="s">
         <v>457</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="E77" s="36" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" ht="18" thickBot="1">
-      <c r="A64" s="18" t="s">
+      <c r="F77" s="36"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+    </row>
+    <row r="78" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B78" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="C78" s="36" t="s">
         <v>459</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="D78" s="36" t="s">
         <v>460</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="E78" s="36" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="18" thickBot="1">
-      <c r="A65" s="18" t="s">
+      <c r="F78" s="36"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="35"/>
+    </row>
+    <row r="79" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B79" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="C79" s="36" t="s">
         <v>462</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="D79" s="36" t="s">
         <v>463</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="E79" s="36" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" ht="18" thickBot="1">
-      <c r="A66" s="18" t="s">
+      <c r="F79" s="36"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="35"/>
+    </row>
+    <row r="80" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B80" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="C80" s="36" t="s">
         <v>465</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="D80" s="36" t="s">
         <v>466</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="E80" s="36" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" ht="18" thickBot="1">
-      <c r="A67" s="18" t="s">
+      <c r="F80" s="36"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="35"/>
+    </row>
+    <row r="81" spans="1:9" ht="17.25" hidden="1">
+      <c r="B81" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C81" s="34" t="s">
         <v>468</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="D81" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="E81" s="34" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="18" thickBot="1">
-      <c r="A68" s="18" t="s">
+      <c r="F81" s="34"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+    </row>
+    <row r="82" spans="1:9" ht="17.25" hidden="1">
+      <c r="B82" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C82" s="34" t="s">
         <v>471</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="D82" s="34" t="s">
         <v>472</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="E82" s="34" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="18" thickBot="1">
-      <c r="A69" s="18" t="s">
-        <v>547</v>
-      </c>
-      <c r="B69" s="18" t="s">
+      <c r="F82" s="34"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+    </row>
+    <row r="83" spans="1:9" ht="17.25" hidden="1">
+      <c r="B83" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="C83" s="34" t="s">
         <v>474</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="D83" s="34" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="18" thickBot="1">
-      <c r="A70" s="18" t="s">
+      <c r="E83" s="34" t="s">
         <v>476</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="F83" s="34"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+    </row>
+    <row r="84" spans="1:9" ht="34.5" hidden="1">
+      <c r="B84" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="C84" s="34" t="s">
         <v>477</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="D84" s="34" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B71" s="34" t="s">
+      <c r="E84" s="34" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="18" thickBot="1">
-      <c r="A72" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="18" thickBot="1">
-      <c r="A73" s="18" t="s">
+      <c r="F84" s="34"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+    </row>
+    <row r="85" spans="1:9" ht="17.25" hidden="1">
+      <c r="B85" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="C85" s="34" t="s">
         <v>480</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="D85" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="E85" s="34" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="18" thickBot="1">
-      <c r="A74" s="18" t="s">
+      <c r="F85" s="34"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+    </row>
+    <row r="86" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+      <c r="B86" s="37"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="38" t="s">
         <v>483</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="E86" s="37"/>
+      <c r="F86" s="37"/>
+      <c r="G86" s="37"/>
+      <c r="H86" s="37"/>
+    </row>
+    <row r="87" spans="1:9" ht="17.25" hidden="1">
+      <c r="B87" s="32" t="s">
+        <v>511</v>
+      </c>
+      <c r="C87" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="E87" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="F87" s="33"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+    </row>
+    <row r="88" spans="1:9" s="49" customFormat="1" ht="34.5">
+      <c r="A88" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="B88" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="C88" s="48" t="s">
         <v>484</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="D88" s="48" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="18" thickBot="1">
-      <c r="A75" s="18" t="s">
+      <c r="E88" s="48" t="s">
         <v>486</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="F88" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="G88" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="H88" s="47"/>
+      <c r="I88" s="49" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="49" customFormat="1" ht="34.5">
+      <c r="A89" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="B89" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="C89" s="48" t="s">
         <v>487</v>
       </c>
-      <c r="C75" s="18" t="s">
+      <c r="D89" s="48" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="18" thickBot="1">
-      <c r="A76" s="18" t="s">
+      <c r="E89" s="48" t="s">
         <v>489</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="F89" s="48" t="s">
+        <v>555</v>
+      </c>
+      <c r="G89" s="47" t="s">
+        <v>555</v>
+      </c>
+      <c r="H89" s="47"/>
+      <c r="I89" s="49" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B90" s="35" t="s">
+        <v>537</v>
+      </c>
+      <c r="C90" s="36" t="s">
         <v>490</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="D90" s="36" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="18" thickBot="1">
-      <c r="A77" s="18" t="s">
+      <c r="E90" s="36" t="s">
         <v>492</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="F90" s="36"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="35"/>
+    </row>
+    <row r="91" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B91" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="C91" s="36" t="s">
         <v>493</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="D91" s="36" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" ht="18" thickBot="1">
-      <c r="A78" s="18" t="s">
+      <c r="E91" s="36" t="s">
         <v>495</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="F91" s="36"/>
+      <c r="G91" s="35"/>
+      <c r="H91" s="35"/>
+    </row>
+    <row r="92" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B92" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="C92" s="36" t="s">
         <v>496</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="D92" s="36" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="18" thickBot="1">
-      <c r="A79" s="18" t="s">
+      <c r="E92" s="36" t="s">
         <v>498</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="F92" s="36"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="35"/>
+    </row>
+    <row r="93" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B93" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="C93" s="36" t="s">
         <v>499</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="D93" s="36" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" ht="18" thickBot="1">
-      <c r="A80" s="18" t="s">
+      <c r="E93" s="36" t="s">
         <v>501</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="F93" s="36"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="35"/>
+    </row>
+    <row r="94" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B94" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="C94" s="36" t="s">
         <v>502</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="D94" s="36" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="18" thickBot="1">
-      <c r="A81" s="18" t="s">
+      <c r="E94" s="36" t="s">
         <v>504</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="F94" s="36"/>
+      <c r="G94" s="35"/>
+      <c r="H94" s="35"/>
+    </row>
+    <row r="95" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+      <c r="B95" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="C95" s="36" t="s">
         <v>505</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="D95" s="36" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="18" thickBot="1">
-      <c r="A82" s="18" t="s">
+      <c r="E95" s="36" t="s">
         <v>507</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="F95" s="36"/>
+      <c r="G95" s="35"/>
+      <c r="H95" s="35"/>
+    </row>
+    <row r="96" spans="1:9" s="24" customFormat="1" ht="34.5" hidden="1">
+      <c r="B96" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="C96" s="36" t="s">
         <v>508</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="D96" s="36" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="18" thickBot="1">
-      <c r="A83" s="18" t="s">
+      <c r="E96" s="36" t="s">
         <v>510</v>
       </c>
-      <c r="B83" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A84" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="B84" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="18" thickBot="1">
-      <c r="A85" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="B85" s="18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="21.75" thickBot="1">
-      <c r="B86" s="34" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="18" thickBot="1">
-      <c r="A87" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="C87" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A88" s="18" t="s">
-        <v>520</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>521</v>
-      </c>
-      <c r="C88" s="18" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A89" s="18" t="s">
-        <v>523</v>
-      </c>
-      <c r="B89" s="18" t="s">
-        <v>524</v>
-      </c>
-      <c r="C89" s="18" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="18" thickBot="1">
-      <c r="A90" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="B90" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="C90" s="18" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="18" thickBot="1">
-      <c r="A91" s="18" t="s">
-        <v>529</v>
-      </c>
-      <c r="B91" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="C91" s="18" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="18" thickBot="1">
-      <c r="A92" s="18" t="s">
-        <v>532</v>
-      </c>
-      <c r="B92" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="C92" s="18" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="18" thickBot="1">
-      <c r="A93" s="18" t="s">
-        <v>535</v>
-      </c>
-      <c r="B93" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="C93" s="18" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="18" thickBot="1">
-      <c r="A94" s="18" t="s">
-        <v>538</v>
-      </c>
-      <c r="B94" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="C94" s="18" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="18" thickBot="1">
-      <c r="A95" s="18" t="s">
-        <v>541</v>
-      </c>
-      <c r="B95" s="18" t="s">
-        <v>542</v>
-      </c>
-      <c r="C95" s="18" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="35.25" thickBot="1">
-      <c r="A96" s="18" t="s">
-        <v>544</v>
-      </c>
-      <c r="B96" s="18" t="s">
-        <v>545</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>546</v>
-      </c>
+      <c r="F96" s="36"/>
+      <c r="G96" s="35"/>
+      <c r="H96" s="35"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:J96" xr:uid="{57942659-D9CB-45B1-9A8D-84CB397A0EAA}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="S">
+      <formula>NOT(ISERROR(SEARCH("S",C1)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="G">
-      <formula>NOT(ISERROR(SEARCH("G",A1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="S">
-      <formula>NOT(ISERROR(SEARCH("S",A1)))</formula>
+      <formula>NOT(ISERROR(SEARCH("G",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{DC55A607-D788-43DD-B6E0-8B9BFF0D89E9}">
-            <xm:f>NOT(ISERROR(SEARCH(-G,A1)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(-G,C1)))</xm:f>
             <xm:f>-G</xm:f>
             <x14:dxf>
               <font>
@@ -7906,7 +8641,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A1:A1048576</xm:sqref>
+          <xm:sqref>C1:C1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9978906F-4E91-4AD1-9EF2-946CCB5CA628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709BB47A-D2D1-4501-B6BD-F7A7C8A085BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
@@ -437,7 +437,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="594">
   <si>
     <t>QA-01</t>
   </si>
@@ -3883,127 +3883,104 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>설명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(720p, RGB24 기준, AI 추론 구간 제외) 카메라 영상 입력부터 Host Application전달 완료까지 평균 시간 ms</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>KPI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OO</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>다중 시나리오가 운용중 일때 사용되는 메모리의 사이즈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>낮을 수록 좋음 (상대 평가)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>결함 주입 시험 테스트 통과율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>도메인간 전달되는 기밀 데이터 항목 수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>요구사항 추가시 수정되지 않는 모듈 수의 최대화</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>시나리오 추가시에 재사용되는 모듈 수의 최대화</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOC 변경에 따라 변경되는 모듈 수의 최소화</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OS update에 따라 변경되는 모듈 수의 최소화</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하드웨어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>환경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적응성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Hardware environmental adaptability)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>도메인간 전달시 손상이 방지된 데이터의 항목수</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>품질 속성</t>
+  </si>
+  <si>
+    <t>중요도</t>
+  </si>
+  <si>
+    <t>난이도</t>
   </si>
   <si>
     <t>우선순위</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 영상 입력부터 Host Application 전달 완료까지의 평균 시간(ms)이 목표 시간을 만족해야 한다.</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>다중 시나리오가 운용 중일 때 사용되는 메모리 사용량을 가능한 낮게 유지해야 한다.</t>
+  </si>
+  <si>
+    <t>결함 테스트에서 시스템에서 Critical 고장이 발생되면 안된다.</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>도메인 간 전달되는 데이터는 시스템에 의해서 접근 통제되어야 한다.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>신규 시나리오 추가 시 전체 자산의 100%가 재사용 가능하도록 설계/구축되어야 한다.</t>
+  </si>
+  <si>
+    <t>SoC 변경에 따라 변경되는 모듈이 없어야 한다.</t>
+  </si>
+  <si>
+    <t>OS update에 따라 변경되는 모듈 수를 최소화하여야 한다.</t>
+  </si>
+  <si>
+    <t>신규 요구사항 추가시 다른 모듈에 영향을 주지 않는 모듈의 비율이 최대가 되어야 한다.</t>
+  </si>
+  <si>
+    <t>성능 (반환 시간)</t>
+  </si>
+  <si>
+    <t>[X &lt;= B. A: 카메라 영상 입력부터 Host 전달 완료까지의 평균 시간(ms)] KPI: 10ms (720p, RGB24, AI 추론 구간 제외)</t>
+  </si>
+  <si>
+    <t>성능 (메모리 사용량)</t>
+  </si>
+  <si>
+    <t>[X = A. A: 다중 시나리오에 사용되는 총 메모리 크기.] KPI: 낮을수록 좋음 (시나리오에 따라 사용량이 다름으로 상대 평가)</t>
+  </si>
+  <si>
+    <t>신뢰성 (고장 회피)</t>
+  </si>
+  <si>
+    <t>[X = A/B. A: 고장으로 이어지지 않은 테스트 수, B: 전체 테스트 수] KPI: 100%</t>
+  </si>
+  <si>
+    <t>보안성 (접근 통제)</t>
+  </si>
+  <si>
+    <t>[X = A/B. A: 접근 통제된 기밀 데이터 항목 수, B: 접근 통제가 요구되는 기밀 데이터 항목 수] KPI: 100%</t>
+  </si>
+  <si>
+    <t>유지보수성 (모듈 결합도)</t>
+  </si>
+  <si>
+    <t>[X = A/B. A: 영향을 주지 않는 모듈 수, B: 전체 모듈 수] KPI: 높을수록 좋음 (상대 평가)</t>
+  </si>
+  <si>
+    <t>유지보수성 (모듈 재사용)</t>
+  </si>
+  <si>
+    <t>[X = A/B. A: 재사용되는 모듈수, B: 전체 모듈수] KPI: 100%</t>
+  </si>
+  <si>
+    <t>이식성 (SOC 변경)</t>
+  </si>
+  <si>
+    <t>[X = A/B. A: 변경되는 모듈 수, B: 전체 모듈 수] KPI: 0%</t>
+  </si>
+  <si>
+    <t>이식성 (OS update)</t>
+  </si>
+  <si>
+    <t>[X = A/B. A: OS update시 변경이 필요한 모듈 수, B: 전체 모듈수] KPI: 낮을수록 좋음 (상대평가)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4214,14 +4191,6 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -4261,7 +4230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -4375,13 +4344,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD6D6D6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD6D6D6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD6D6D6"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD6D6D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4502,18 +4497,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4532,26 +4515,35 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5082,20 +5074,20 @@
       <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="42"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="48"/>
       <c r="O5" s="22" t="s">
         <v>90</v>
       </c>
@@ -5125,20 +5117,20 @@
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="42"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="48"/>
       <c r="O7" s="23" t="s">
         <v>106</v>
       </c>
@@ -5267,20 +5259,20 @@
       <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="42"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="48"/>
       <c r="O14" s="22" t="s">
         <v>91</v>
       </c>
@@ -5289,20 +5281,20 @@
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="42"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="48"/>
       <c r="O15" s="23" t="s">
         <v>105</v>
       </c>
@@ -6245,346 +6237,442 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="51.25" customWidth="1"/>
-    <col min="5" max="5" width="86.25" customWidth="1"/>
-    <col min="6" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="8" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="27.5" customWidth="1"/>
+    <col min="2" max="2" width="101" customWidth="1"/>
+    <col min="3" max="5" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="39" customFormat="1" ht="17.25">
-      <c r="A1" s="37" t="s">
-        <v>562</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>511</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="D1" s="51" t="s">
+    <row r="1" spans="1:5" s="39" customFormat="1" ht="18" thickBot="1">
+      <c r="A1" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="E1" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="50" t="s">
+      <c r="B1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>565</v>
       </c>
-      <c r="G1" s="51" t="s">
-        <v>540</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>541</v>
-      </c>
-      <c r="I1" s="37" t="s">
+      <c r="E1" s="15" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25">
+      <c r="A2" s="52" t="s">
+        <v>578</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="E2" s="54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18" thickBot="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="51" t="s">
+        <v>579</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+    </row>
+    <row r="4" spans="1:5" ht="17.25">
+      <c r="A4" s="52" t="s">
+        <v>580</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>569</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="E4" s="54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="35.25" thickBot="1">
+      <c r="A5" s="53"/>
+      <c r="B5" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.25">
+      <c r="A6" s="52" t="s">
+        <v>582</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>570</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E6" s="54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" thickBot="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="51" t="s">
+        <v>583</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+    </row>
+    <row r="8" spans="1:5" ht="17.25">
+      <c r="A8" s="52" t="s">
+        <v>584</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E8" s="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18" thickBot="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="51" t="s">
+        <v>585</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+    </row>
+    <row r="10" spans="1:5" ht="17.25">
+      <c r="A10" s="52" t="s">
+        <v>586</v>
+      </c>
+      <c r="B10" s="50" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="17.25">
-      <c r="A2" s="44" t="s">
-        <v>557</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>512</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D2" s="44" t="s">
+      <c r="C10" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" thickBot="1">
+      <c r="A11" s="53"/>
+      <c r="B11" s="51" t="s">
+        <v>587</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.25">
+      <c r="A12" s="52" t="s">
+        <v>588</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>574</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E12" s="54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" thickBot="1">
+      <c r="A13" s="53"/>
+      <c r="B13" s="51" t="s">
+        <v>589</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.25">
+      <c r="A14" s="52" t="s">
+        <v>590</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>575</v>
+      </c>
+      <c r="C14" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18" thickBot="1">
+      <c r="A15" s="53"/>
+      <c r="B15" s="51" t="s">
+        <v>591</v>
+      </c>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+    </row>
+    <row r="16" spans="1:5" ht="17.25">
+      <c r="A16" s="52" t="s">
+        <v>592</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>576</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" thickBot="1">
+      <c r="A17" s="53"/>
+      <c r="B17" s="51" t="s">
+        <v>593</v>
+      </c>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1"/>
+    <row r="22" spans="1:5" ht="18" thickBot="1">
+      <c r="A22" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="E2" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="F2" s="45" t="s">
+      <c r="D22" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="I2" s="32">
+    </row>
+    <row r="23" spans="1:5" ht="17.25">
+      <c r="A23" s="52" t="s">
+        <v>578</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="E23" s="54">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="51.75">
-      <c r="A3" s="44" t="s">
-        <v>557</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>513</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" s="52" t="s">
+    <row r="24" spans="1:5" ht="18" thickBot="1">
+      <c r="A24" s="53"/>
+      <c r="B24" s="51" t="s">
+        <v>579</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+    </row>
+    <row r="25" spans="1:5" ht="17.25">
+      <c r="A25" s="52" t="s">
+        <v>580</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>569</v>
+      </c>
+      <c r="C25" s="54" t="s">
         <v>568</v>
       </c>
-      <c r="G3" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H3" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" s="32">
+      <c r="D25" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="E25" s="54">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.5">
-      <c r="A4" s="44" t="s">
-        <v>558</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>525</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>395</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>569</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>396</v>
-      </c>
-      <c r="F4" s="54">
-        <v>1</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="44" t="s">
-        <v>555</v>
-      </c>
-      <c r="I4" s="32">
+    <row r="26" spans="1:5" ht="35.25" thickBot="1">
+      <c r="A26" s="53"/>
+      <c r="B26" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+    </row>
+    <row r="27" spans="1:5" ht="17.25">
+      <c r="A27" s="52" t="s">
+        <v>584</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E27" s="54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="18" thickBot="1">
+      <c r="A28" s="53"/>
+      <c r="B28" s="51" t="s">
+        <v>585</v>
+      </c>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+    </row>
+    <row r="29" spans="1:5" ht="17.25">
+      <c r="A29" s="52" t="s">
+        <v>588</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>574</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E29" s="54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="18" thickBot="1">
+      <c r="A30" s="53"/>
+      <c r="B30" s="51" t="s">
+        <v>589</v>
+      </c>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+    </row>
+    <row r="31" spans="1:5" ht="17.25">
+      <c r="A31" s="52" t="s">
+        <v>582</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>570</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>571</v>
+      </c>
+      <c r="E31" s="54">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="34.5">
-      <c r="A5" s="44" t="s">
-        <v>559</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>527</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>570</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>412</v>
-      </c>
-      <c r="F5" s="54">
-        <v>1</v>
-      </c>
-      <c r="G5" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="44" t="s">
-        <v>555</v>
-      </c>
-      <c r="I5" s="32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="17.25">
-      <c r="A6" s="47" t="s">
-        <v>559</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>528</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>420</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>576</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>421</v>
-      </c>
-      <c r="F6" s="53">
-        <v>1</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="I6" s="32"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.5">
-      <c r="A7" s="47" t="s">
-        <v>560</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>532</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>445</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>571</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>446</v>
-      </c>
-      <c r="F7" s="53">
-        <v>1</v>
-      </c>
-      <c r="G7" s="48" t="s">
-        <v>555</v>
-      </c>
-      <c r="H7" s="47" t="s">
-        <v>555</v>
-      </c>
-      <c r="I7" s="32"/>
-    </row>
-    <row r="8" spans="1:9" ht="17.25">
-      <c r="A8" s="44" t="s">
-        <v>560</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>533</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>451</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>572</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>452</v>
-      </c>
-      <c r="F8" s="54">
-        <v>1</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>555</v>
-      </c>
-      <c r="I8" s="32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="51.75">
-      <c r="A9" s="47" t="s">
-        <v>561</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>537</v>
-      </c>
-      <c r="C9" s="56" t="s">
-        <v>575</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>573</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>486</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>568</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>555</v>
-      </c>
-      <c r="H9" s="47" t="s">
-        <v>555</v>
-      </c>
-      <c r="I9" s="32"/>
-    </row>
-    <row r="10" spans="1:9" ht="51.75">
-      <c r="A10" s="47" t="s">
-        <v>561</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>537</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>488</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>574</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>489</v>
-      </c>
-      <c r="F10" s="55" t="s">
-        <v>568</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>555</v>
-      </c>
-      <c r="H10" s="47" t="s">
-        <v>555</v>
-      </c>
-      <c r="I10" s="32"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+    <row r="32" spans="1:5" ht="18" thickBot="1">
+      <c r="A32" s="53"/>
+      <c r="B32" s="51" t="s">
+        <v>583</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
     </row>
   </sheetData>
+  <mergeCells count="52">
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6985,30 +7073,30 @@
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
     </row>
-    <row r="6" spans="1:9" s="46" customFormat="1" ht="17.25">
-      <c r="A6" s="46" t="s">
+    <row r="6" spans="1:9" s="42" customFormat="1" ht="17.25">
+      <c r="A6" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="40" t="s">
         <v>512</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="46" t="s">
+      <c r="H6" s="40"/>
+      <c r="I6" s="42" t="s">
         <v>547</v>
       </c>
     </row>
@@ -7046,30 +7134,30 @@
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
     </row>
-    <row r="9" spans="1:9" s="46" customFormat="1" ht="17.25">
-      <c r="A9" s="46" t="s">
+    <row r="9" spans="1:9" s="42" customFormat="1" ht="17.25">
+      <c r="A9" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="40" t="s">
         <v>513</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="44" t="s">
+      <c r="G9" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="H9" s="44"/>
-      <c r="I9" s="46" t="s">
+      <c r="H9" s="40"/>
+      <c r="I9" s="42" t="s">
         <v>546</v>
       </c>
     </row>
@@ -7747,30 +7835,30 @@
       <c r="G49" s="35"/>
       <c r="H49" s="35"/>
     </row>
-    <row r="50" spans="1:9" s="49" customFormat="1" ht="17.25">
-      <c r="A50" s="49" t="s">
+    <row r="50" spans="1:9" s="45" customFormat="1" ht="17.25">
+      <c r="A50" s="45" t="s">
         <v>558</v>
       </c>
-      <c r="B50" s="47" t="s">
+      <c r="B50" s="43" t="s">
         <v>523</v>
       </c>
-      <c r="C50" s="48" t="s">
+      <c r="C50" s="44" t="s">
         <v>385</v>
       </c>
-      <c r="D50" s="48" t="s">
+      <c r="D50" s="44" t="s">
         <v>386</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="44" t="s">
         <v>387</v>
       </c>
-      <c r="F50" s="48" t="s">
+      <c r="F50" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="G50" s="47" t="s">
+      <c r="G50" s="43" t="s">
         <v>555</v>
       </c>
-      <c r="H50" s="47"/>
-      <c r="I50" s="49" t="s">
+      <c r="H50" s="43"/>
+      <c r="I50" s="45" t="s">
         <v>551</v>
       </c>
     </row>
@@ -7808,26 +7896,26 @@
       <c r="G52" s="32"/>
       <c r="H52" s="32"/>
     </row>
-    <row r="53" spans="1:9" s="46" customFormat="1" ht="34.5">
-      <c r="A53" s="46" t="s">
+    <row r="53" spans="1:9" s="42" customFormat="1" ht="34.5">
+      <c r="A53" s="42" t="s">
         <v>558</v>
       </c>
-      <c r="B53" s="44" t="s">
+      <c r="B53" s="40" t="s">
         <v>525</v>
       </c>
-      <c r="C53" s="45" t="s">
+      <c r="C53" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="D53" s="45" t="s">
+      <c r="D53" s="41" t="s">
         <v>395</v>
       </c>
-      <c r="E53" s="45" t="s">
+      <c r="E53" s="41" t="s">
         <v>396</v>
       </c>
-      <c r="F53" s="45"/>
-      <c r="G53" s="44"/>
-      <c r="H53" s="44"/>
-      <c r="I53" s="46" t="s">
+      <c r="F53" s="41"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="42" t="s">
         <v>545</v>
       </c>
     </row>
@@ -7927,30 +8015,30 @@
       <c r="G59" s="32"/>
       <c r="H59" s="32"/>
     </row>
-    <row r="60" spans="1:9" s="46" customFormat="1" ht="34.5">
-      <c r="A60" s="46" t="s">
+    <row r="60" spans="1:9" s="42" customFormat="1" ht="34.5">
+      <c r="A60" s="42" t="s">
         <v>559</v>
       </c>
-      <c r="B60" s="44" t="s">
+      <c r="B60" s="40" t="s">
         <v>527</v>
       </c>
-      <c r="C60" s="45" t="s">
+      <c r="C60" s="41" t="s">
         <v>410</v>
       </c>
-      <c r="D60" s="45" t="s">
+      <c r="D60" s="41" t="s">
         <v>411</v>
       </c>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="41" t="s">
         <v>412</v>
       </c>
-      <c r="F60" s="45" t="s">
+      <c r="F60" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="G60" s="44" t="s">
+      <c r="G60" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="H60" s="44"/>
-      <c r="I60" s="46" t="s">
+      <c r="H60" s="40"/>
+      <c r="I60" s="42" t="s">
         <v>543</v>
       </c>
     </row>
@@ -7988,30 +8076,30 @@
       <c r="G62" s="32"/>
       <c r="H62" s="32"/>
     </row>
-    <row r="63" spans="1:9" s="49" customFormat="1" ht="17.25">
-      <c r="A63" s="49" t="s">
+    <row r="63" spans="1:9" s="45" customFormat="1" ht="17.25">
+      <c r="A63" s="45" t="s">
         <v>559</v>
       </c>
-      <c r="B63" s="47" t="s">
+      <c r="B63" s="43" t="s">
         <v>528</v>
       </c>
-      <c r="C63" s="48" t="s">
+      <c r="C63" s="44" t="s">
         <v>419</v>
       </c>
-      <c r="D63" s="48" t="s">
+      <c r="D63" s="44" t="s">
         <v>420</v>
       </c>
-      <c r="E63" s="48" t="s">
+      <c r="E63" s="44" t="s">
         <v>421</v>
       </c>
-      <c r="F63" s="48" t="s">
+      <c r="F63" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="G63" s="47" t="s">
+      <c r="G63" s="43" t="s">
         <v>556</v>
       </c>
-      <c r="H63" s="47"/>
-      <c r="I63" s="49" t="s">
+      <c r="H63" s="43"/>
+      <c r="I63" s="45" t="s">
         <v>543</v>
       </c>
     </row>
@@ -8162,30 +8250,30 @@
       <c r="G72" s="32"/>
       <c r="H72" s="32"/>
     </row>
-    <row r="73" spans="1:9" s="49" customFormat="1" ht="17.25">
-      <c r="A73" s="49" t="s">
+    <row r="73" spans="1:9" s="45" customFormat="1" ht="17.25">
+      <c r="A73" s="45" t="s">
         <v>560</v>
       </c>
-      <c r="B73" s="47" t="s">
+      <c r="B73" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C73" s="48" t="s">
+      <c r="C73" s="44" t="s">
         <v>444</v>
       </c>
-      <c r="D73" s="48" t="s">
+      <c r="D73" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="E73" s="48" t="s">
+      <c r="E73" s="44" t="s">
         <v>446</v>
       </c>
-      <c r="F73" s="48" t="s">
+      <c r="F73" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="G73" s="47" t="s">
+      <c r="G73" s="43" t="s">
         <v>555</v>
       </c>
-      <c r="H73" s="47"/>
-      <c r="I73" s="49" t="s">
+      <c r="H73" s="43"/>
+      <c r="I73" s="45" t="s">
         <v>553</v>
       </c>
     </row>
@@ -8206,30 +8294,30 @@
       <c r="G74" s="32"/>
       <c r="H74" s="32"/>
     </row>
-    <row r="75" spans="1:9" s="46" customFormat="1" ht="17.25">
-      <c r="A75" s="46" t="s">
+    <row r="75" spans="1:9" s="42" customFormat="1" ht="17.25">
+      <c r="A75" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="B75" s="44" t="s">
+      <c r="B75" s="40" t="s">
         <v>533</v>
       </c>
-      <c r="C75" s="45" t="s">
+      <c r="C75" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="D75" s="45" t="s">
+      <c r="D75" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="E75" s="45" t="s">
+      <c r="E75" s="41" t="s">
         <v>452</v>
       </c>
-      <c r="F75" s="45" t="s">
+      <c r="F75" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="G75" s="44" t="s">
+      <c r="G75" s="40" t="s">
         <v>555</v>
       </c>
-      <c r="H75" s="44"/>
-      <c r="I75" s="46" t="s">
+      <c r="H75" s="40"/>
+      <c r="I75" s="42" t="s">
         <v>544</v>
       </c>
     </row>
@@ -8431,57 +8519,57 @@
       <c r="G87" s="32"/>
       <c r="H87" s="32"/>
     </row>
-    <row r="88" spans="1:9" s="49" customFormat="1" ht="34.5">
-      <c r="A88" s="49" t="s">
+    <row r="88" spans="1:9" s="45" customFormat="1" ht="34.5">
+      <c r="A88" s="45" t="s">
         <v>561</v>
       </c>
-      <c r="B88" s="47" t="s">
+      <c r="B88" s="43" t="s">
         <v>537</v>
       </c>
-      <c r="C88" s="48" t="s">
+      <c r="C88" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="D88" s="48" t="s">
+      <c r="D88" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="E88" s="48" t="s">
+      <c r="E88" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="F88" s="48" t="s">
+      <c r="F88" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="G88" s="47" t="s">
+      <c r="G88" s="43" t="s">
         <v>555</v>
       </c>
-      <c r="H88" s="47"/>
-      <c r="I88" s="49" t="s">
+      <c r="H88" s="43"/>
+      <c r="I88" s="45" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="49" customFormat="1" ht="34.5">
-      <c r="A89" s="49" t="s">
+    <row r="89" spans="1:9" s="45" customFormat="1" ht="34.5">
+      <c r="A89" s="45" t="s">
         <v>561</v>
       </c>
-      <c r="B89" s="47" t="s">
+      <c r="B89" s="43" t="s">
         <v>537</v>
       </c>
-      <c r="C89" s="48" t="s">
+      <c r="C89" s="44" t="s">
         <v>487</v>
       </c>
-      <c r="D89" s="48" t="s">
+      <c r="D89" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="E89" s="48" t="s">
+      <c r="E89" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="F89" s="48" t="s">
+      <c r="F89" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="G89" s="47" t="s">
+      <c r="G89" s="43" t="s">
         <v>555</v>
       </c>
-      <c r="H89" s="47"/>
-      <c r="I89" s="49" t="s">
+      <c r="H89" s="43"/>
+      <c r="I89" s="45" t="s">
         <v>552</v>
       </c>
     </row>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\arch\test-p\ppt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\architect\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709BB47A-D2D1-4501-B6BD-F7A7C8A085BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5D4154-160C-4391-BBD7-0E2EF842A601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="6" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="7" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -20,15 +20,16 @@
     <sheet name="FR" sheetId="4" r:id="rId5"/>
     <sheet name="CONST" sheetId="5" r:id="rId6"/>
     <sheet name="QA" sheetId="6" r:id="rId7"/>
-    <sheet name="ISO 25010" sheetId="14" r:id="rId8"/>
-    <sheet name="ISO 25023" sheetId="15" r:id="rId9"/>
-    <sheet name="Matrix" sheetId="8" r:id="rId10"/>
-    <sheet name="pKVM interfacer" sheetId="10" r:id="rId11"/>
-    <sheet name="ContextView" sheetId="12" r:id="rId12"/>
-    <sheet name="DP" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId8"/>
+    <sheet name="ISO 25010" sheetId="14" r:id="rId9"/>
+    <sheet name="ISO 25023" sheetId="15" r:id="rId10"/>
+    <sheet name="Matrix" sheetId="8" r:id="rId11"/>
+    <sheet name="pKVM interfacer" sheetId="10" r:id="rId12"/>
+    <sheet name="ContextView" sheetId="12" r:id="rId13"/>
+    <sheet name="DP" sheetId="13" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ISO 25023'!$A$2:$J$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'ISO 25023'!$A$2:$J$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -437,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="605">
   <si>
     <t>QA-01</t>
   </si>
@@ -3974,6 +3975,53 @@
   </si>
   <si>
     <t>[X = A/B. A: OS update시 변경이 필요한 모듈 수, B: 전체 모듈수] KPI: 낮을수록 좋음 (상대평가)</t>
+  </si>
+  <si>
+    <t>1080p RGB24</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 시간</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1080p NV12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>720p RGB24</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>720p NV12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레임 사이즈 (MB)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>암(복)호화 시간(ms)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전송시간(ms)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>44.48
+(ms)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5
+(km/h)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.22
+(cm)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4376,7 +4424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4515,18 +4563,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4544,6 +4580,21 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4958,2021 +5009,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
-  <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
-    <col min="2" max="13" width="6.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="48"/>
-      <c r="O5" s="22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="48"/>
-      <c r="O7" s="23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="48"/>
-      <c r="O14" s="22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="48"/>
-      <c r="O15" s="23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B7:M7"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B15:M15"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="64.125" customWidth="1"/>
-    <col min="3" max="3" width="40.875" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="17.25">
-      <c r="A1" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
-    <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29.25" thickBot="1">
-      <c r="A4" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="43.5" thickBot="1">
-      <c r="A5" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="43.5" thickBot="1">
-      <c r="A6" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" thickBot="1">
-      <c r="A7" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="45" thickBot="1">
-      <c r="A8" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="28.5">
-      <c r="A9" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>126</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
-  <cols>
-    <col min="2" max="2" width="74.625" customWidth="1"/>
-    <col min="3" max="3" width="57.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="15"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="16"/>
-    </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3" ht="18" thickBot="1">
-      <c r="A8" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9" spans="1:3" ht="18" thickBot="1">
-      <c r="A9" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="16"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="3" max="3" width="69" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="27.5" customWidth="1"/>
-    <col min="2" max="2" width="101" customWidth="1"/>
-    <col min="3" max="5" width="9.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="39" customFormat="1" ht="18" thickBot="1">
-      <c r="A1" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="17.25">
-      <c r="A2" s="52" t="s">
-        <v>578</v>
-      </c>
-      <c r="B2" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D2" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="E2" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="18" thickBot="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="51" t="s">
-        <v>579</v>
-      </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-    </row>
-    <row r="4" spans="1:5" ht="17.25">
-      <c r="A4" s="52" t="s">
-        <v>580</v>
-      </c>
-      <c r="B4" s="50" t="s">
-        <v>569</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="E4" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="35.25" thickBot="1">
-      <c r="A5" s="53"/>
-      <c r="B5" s="51" t="s">
-        <v>581</v>
-      </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-    </row>
-    <row r="6" spans="1:5" ht="17.25">
-      <c r="A6" s="52" t="s">
-        <v>582</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>570</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E6" s="54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" thickBot="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="51" t="s">
-        <v>583</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-    </row>
-    <row r="8" spans="1:5" ht="17.25">
-      <c r="A8" s="52" t="s">
-        <v>584</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D8" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E8" s="54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="18" thickBot="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="51" t="s">
-        <v>585</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-    </row>
-    <row r="10" spans="1:5" ht="17.25">
-      <c r="A10" s="52" t="s">
-        <v>586</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>577</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="D10" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" thickBot="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="51" t="s">
-        <v>587</v>
-      </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-    </row>
-    <row r="12" spans="1:5" ht="17.25">
-      <c r="A12" s="52" t="s">
-        <v>588</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>574</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E12" s="54">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="18" thickBot="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="51" t="s">
-        <v>589</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-    </row>
-    <row r="14" spans="1:5" ht="17.25">
-      <c r="A14" s="52" t="s">
-        <v>590</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>575</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="D14" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E14" s="54" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18" thickBot="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="51" t="s">
-        <v>591</v>
-      </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-    </row>
-    <row r="16" spans="1:5" ht="17.25">
-      <c r="A16" s="52" t="s">
-        <v>592</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>576</v>
-      </c>
-      <c r="C16" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="D16" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="18" thickBot="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="51" t="s">
-        <v>593</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-    </row>
-    <row r="21" spans="1:5" ht="17.25" thickBot="1"/>
-    <row r="22" spans="1:5" ht="18" thickBot="1">
-      <c r="A22" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="17.25">
-      <c r="A23" s="52" t="s">
-        <v>578</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="C23" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D23" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="E23" s="54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18" thickBot="1">
-      <c r="A24" s="53"/>
-      <c r="B24" s="51" t="s">
-        <v>579</v>
-      </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-    </row>
-    <row r="25" spans="1:5" ht="17.25">
-      <c r="A25" s="52" t="s">
-        <v>580</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>569</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D25" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="E25" s="54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="35.25" thickBot="1">
-      <c r="A26" s="53"/>
-      <c r="B26" s="51" t="s">
-        <v>581</v>
-      </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-    </row>
-    <row r="27" spans="1:5" ht="17.25">
-      <c r="A27" s="52" t="s">
-        <v>584</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D27" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E27" s="54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="18" thickBot="1">
-      <c r="A28" s="53"/>
-      <c r="B28" s="51" t="s">
-        <v>585</v>
-      </c>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-    </row>
-    <row r="29" spans="1:5" ht="17.25">
-      <c r="A29" s="52" t="s">
-        <v>588</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>574</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D29" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E29" s="54">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="18" thickBot="1">
-      <c r="A30" s="53"/>
-      <c r="B30" s="51" t="s">
-        <v>589</v>
-      </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-    </row>
-    <row r="31" spans="1:5" ht="17.25">
-      <c r="A31" s="52" t="s">
-        <v>582</v>
-      </c>
-      <c r="B31" s="50" t="s">
-        <v>570</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="D31" s="54" t="s">
-        <v>571</v>
-      </c>
-      <c r="E31" s="54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="18" thickBot="1">
-      <c r="A32" s="53"/>
-      <c r="B32" s="51" t="s">
-        <v>583</v>
-      </c>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-    </row>
-  </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12054B3A-2648-4FB0-BBA9-9ACDCE3B68E0}">
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="39.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="105" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A5" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A7" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A8" s="30"/>
-      <c r="B8" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A10" s="30"/>
-      <c r="B10" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A11" s="30"/>
-      <c r="B11" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A13" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" thickBot="1">
-      <c r="A17" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" thickBot="1">
-      <c r="A22" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A23" s="25"/>
-      <c r="B23" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A24" s="30"/>
-      <c r="B24" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A25" s="25"/>
-      <c r="B25" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A27" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A28" s="30"/>
-      <c r="B28" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A29" s="30"/>
-      <c r="B29" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.25">
-      <c r="B30" s="31" t="s">
-        <v>255</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57942659-D9CB-45B1-9A8D-84CB397A0EAA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I96"/>
@@ -8735,4 +6771,2205 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="7.375" customWidth="1"/>
+    <col min="2" max="13" width="6.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
+      <c r="O5" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="54"/>
+      <c r="O7" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="54"/>
+      <c r="O14" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="54"/>
+      <c r="O15" s="23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B7:M7"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B15:M15"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="25.75" customWidth="1"/>
+    <col min="2" max="2" width="64.125" customWidth="1"/>
+    <col min="3" max="3" width="40.875" customWidth="1"/>
+    <col min="4" max="4" width="25.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17.25">
+      <c r="A1" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
+    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29.25" thickBot="1">
+      <c r="A4" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="43.5" thickBot="1">
+      <c r="A5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="43.5" thickBot="1">
+      <c r="A6" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" thickBot="1">
+      <c r="A7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="45" thickBot="1">
+      <c r="A8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.5">
+      <c r="A9" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="74.625" customWidth="1"/>
+    <col min="3" max="3" width="57.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="15"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="16"/>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="18" thickBot="1">
+      <c r="A8" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" ht="18" thickBot="1">
+      <c r="A9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" thickBot="1">
+      <c r="A5" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" thickBot="1">
+      <c r="A7" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="69" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="27.5" customWidth="1"/>
+    <col min="2" max="2" width="101" customWidth="1"/>
+    <col min="3" max="5" width="9.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="39" customFormat="1" ht="18" thickBot="1">
+      <c r="A1" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25">
+      <c r="A2" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>567</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="E2" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18" thickBot="1">
+      <c r="A3" s="49"/>
+      <c r="B3" s="47" t="s">
+        <v>579</v>
+      </c>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+    </row>
+    <row r="4" spans="1:5" ht="17.25">
+      <c r="A4" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>569</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="E4" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="35.25" thickBot="1">
+      <c r="A5" s="49"/>
+      <c r="B5" s="47" t="s">
+        <v>581</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.25">
+      <c r="A6" s="48" t="s">
+        <v>582</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>570</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E6" s="50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" thickBot="1">
+      <c r="A7" s="49"/>
+      <c r="B7" s="47" t="s">
+        <v>583</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+    </row>
+    <row r="8" spans="1:5" ht="17.25">
+      <c r="A8" s="48" t="s">
+        <v>584</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>572</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E8" s="50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18" thickBot="1">
+      <c r="A9" s="49"/>
+      <c r="B9" s="47" t="s">
+        <v>585</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+    </row>
+    <row r="10" spans="1:5" ht="17.25">
+      <c r="A10" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>577</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" thickBot="1">
+      <c r="A11" s="49"/>
+      <c r="B11" s="47" t="s">
+        <v>587</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.25">
+      <c r="A12" s="48" t="s">
+        <v>588</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>574</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E12" s="50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="18" thickBot="1">
+      <c r="A13" s="49"/>
+      <c r="B13" s="47" t="s">
+        <v>589</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.25">
+      <c r="A14" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>575</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="18" thickBot="1">
+      <c r="A15" s="49"/>
+      <c r="B15" s="47" t="s">
+        <v>591</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+    </row>
+    <row r="16" spans="1:5" ht="17.25">
+      <c r="A16" s="48" t="s">
+        <v>592</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>576</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="18" thickBot="1">
+      <c r="A17" s="49"/>
+      <c r="B17" s="47" t="s">
+        <v>593</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1"/>
+    <row r="22" spans="1:5" ht="18" thickBot="1">
+      <c r="A22" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17.25">
+      <c r="A23" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>567</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="E23" s="50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18" thickBot="1">
+      <c r="A24" s="49"/>
+      <c r="B24" s="47" t="s">
+        <v>579</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+    </row>
+    <row r="25" spans="1:5" ht="17.25">
+      <c r="A25" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>569</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="E25" s="50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="35.25" thickBot="1">
+      <c r="A26" s="49"/>
+      <c r="B26" s="47" t="s">
+        <v>581</v>
+      </c>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+    </row>
+    <row r="27" spans="1:5" ht="17.25">
+      <c r="A27" s="48" t="s">
+        <v>584</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>572</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E27" s="50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="18" thickBot="1">
+      <c r="A28" s="49"/>
+      <c r="B28" s="47" t="s">
+        <v>585</v>
+      </c>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+    </row>
+    <row r="29" spans="1:5" ht="17.25">
+      <c r="A29" s="48" t="s">
+        <v>588</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>574</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E29" s="50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="18" thickBot="1">
+      <c r="A30" s="49"/>
+      <c r="B30" s="47" t="s">
+        <v>589</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+    </row>
+    <row r="31" spans="1:5" ht="17.25">
+      <c r="A31" s="48" t="s">
+        <v>582</v>
+      </c>
+      <c r="B31" s="46" t="s">
+        <v>570</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>571</v>
+      </c>
+      <c r="E31" s="50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18" thickBot="1">
+      <c r="A32" s="49"/>
+      <c r="B32" s="47" t="s">
+        <v>583</v>
+      </c>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+    </row>
+  </sheetData>
+  <mergeCells count="52">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7D28BF-FC95-411D-BBBF-B7CDE652B6A5}">
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6">
+      <c r="C2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C3">
+        <v>5.93</v>
+      </c>
+      <c r="D3">
+        <v>7.41</v>
+      </c>
+      <c r="E3">
+        <v>14.83</v>
+      </c>
+      <c r="F3">
+        <f>(D3+E3) * 2</f>
+        <v>44.480000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C4">
+        <v>2.96</v>
+      </c>
+      <c r="D4">
+        <v>3.7</v>
+      </c>
+      <c r="E4">
+        <v>7.4</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F6" si="0">(D4+E4) * 2</f>
+        <v>22.200000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" t="s">
+        <v>597</v>
+      </c>
+      <c r="C5">
+        <v>2.63</v>
+      </c>
+      <c r="D5">
+        <v>3.29</v>
+      </c>
+      <c r="E5">
+        <v>6.58</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>19.740000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C6">
+        <v>1.31</v>
+      </c>
+      <c r="D6">
+        <v>1.64</v>
+      </c>
+      <c r="E6">
+        <v>3.28</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="33">
+      <c r="C10" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="33">
+      <c r="B11" s="56" t="s">
+        <v>602</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>604</v>
+      </c>
+      <c r="D11">
+        <v>24.71</v>
+      </c>
+      <c r="E11">
+        <v>37.07</v>
+      </c>
+      <c r="F11">
+        <v>49.43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12">
+        <v>22.200000000000003</v>
+      </c>
+      <c r="C12">
+        <v>6.17</v>
+      </c>
+      <c r="D12">
+        <v>12.33</v>
+      </c>
+      <c r="E12">
+        <v>18.5</v>
+      </c>
+      <c r="F12">
+        <v>24.67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13">
+        <v>19.740000000000002</v>
+      </c>
+      <c r="C13">
+        <v>5.48</v>
+      </c>
+      <c r="D13">
+        <v>10.97</v>
+      </c>
+      <c r="E13">
+        <v>16.45</v>
+      </c>
+      <c r="F13">
+        <v>21.93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14">
+        <v>9.84</v>
+      </c>
+      <c r="C14">
+        <v>2.73</v>
+      </c>
+      <c r="D14">
+        <v>5.47</v>
+      </c>
+      <c r="E14">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F14">
+        <v>10.93</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12054B3A-2648-4FB0-BBA9-9ACDCE3B68E0}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="39.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="105" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" thickBot="1">
+      <c r="A2" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
+      <c r="A3" s="25"/>
+      <c r="B3" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" thickBot="1">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A5" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" thickBot="1">
+      <c r="A6" s="25"/>
+      <c r="B6" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A7" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A9" s="30"/>
+      <c r="B9" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A10" s="30"/>
+      <c r="B10" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A11" s="30"/>
+      <c r="B11" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A12" s="30"/>
+      <c r="B12" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A13" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A14" s="25"/>
+      <c r="B14" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A15" s="25"/>
+      <c r="B15" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" thickBot="1">
+      <c r="A16" s="25"/>
+      <c r="B16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" thickBot="1">
+      <c r="A17" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A18" s="25"/>
+      <c r="B18" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A19" s="25"/>
+      <c r="B19" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A20" s="25"/>
+      <c r="B20" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A21" s="25"/>
+      <c r="B21" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" thickBot="1">
+      <c r="A22" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A23" s="25"/>
+      <c r="B23" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A24" s="30"/>
+      <c r="B24" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A25" s="25"/>
+      <c r="B25" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
+      <c r="A27" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A28" s="30"/>
+      <c r="B28" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A29" s="30"/>
+      <c r="B29" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="17.25">
+      <c r="B30" s="31" t="s">
+        <v>255</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\architect\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5D4154-160C-4391-BBD7-0E2EF842A601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E568DC2-7F7D-4D0F-8531-0546D1D266C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="7" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="603">
   <si>
     <t>QA-01</t>
   </si>
@@ -3977,23 +3977,7 @@
     <t>[X = A/B. A: OS update시 변경이 필요한 모듈 수, B: 전체 모듈수] KPI: 낮을수록 좋음 (상대평가)</t>
   </si>
   <si>
-    <t>1080p RGB24</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>전체 시간</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1080p NV12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>720p RGB24</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>720p NV12</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -4021,6 +4005,14 @@
   <si>
     <t>12.22
 (cm)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1024x512</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1280x720</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4569,6 +4561,9 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4592,9 +4587,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6890,20 +6882,20 @@
       <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="55"/>
       <c r="O5" s="22" t="s">
         <v>90</v>
       </c>
@@ -6933,20 +6925,20 @@
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="55"/>
       <c r="O7" s="23" t="s">
         <v>106</v>
       </c>
@@ -7075,20 +7067,20 @@
       <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="55"/>
       <c r="O14" s="22" t="s">
         <v>91</v>
       </c>
@@ -7097,20 +7089,20 @@
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>188</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="55"/>
       <c r="O15" s="23" t="s">
         <v>105</v>
       </c>
@@ -8079,212 +8071,212 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>578</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="51">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" thickBot="1">
-      <c r="A3" s="49"/>
+      <c r="A3" s="50"/>
       <c r="B3" s="47" t="s">
         <v>579</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
     </row>
     <row r="4" spans="1:5" ht="17.25">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="49" t="s">
         <v>580</v>
       </c>
       <c r="B4" s="46" t="s">
         <v>569</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="51">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="35.25" thickBot="1">
-      <c r="A5" s="49"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="47" t="s">
         <v>581</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
     </row>
     <row r="6" spans="1:5" ht="17.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="49" t="s">
         <v>582</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>570</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="51">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" thickBot="1">
-      <c r="A7" s="49"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="47" t="s">
         <v>583</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
     </row>
     <row r="8" spans="1:5" ht="17.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="49" t="s">
         <v>584</v>
       </c>
       <c r="B8" s="46" t="s">
         <v>572</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="51">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" thickBot="1">
-      <c r="A9" s="49"/>
+      <c r="A9" s="50"/>
       <c r="B9" s="47" t="s">
         <v>585</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
     </row>
     <row r="10" spans="1:5" ht="17.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="49" t="s">
         <v>586</v>
       </c>
       <c r="B10" s="46" t="s">
         <v>577</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="51" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" thickBot="1">
-      <c r="A11" s="49"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="47" t="s">
         <v>587</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
     </row>
     <row r="12" spans="1:5" ht="17.25">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="49" t="s">
         <v>588</v>
       </c>
       <c r="B12" s="46" t="s">
         <v>574</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="51">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" thickBot="1">
-      <c r="A13" s="49"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="47" t="s">
         <v>589</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
     </row>
     <row r="14" spans="1:5" ht="17.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="49" t="s">
         <v>590</v>
       </c>
       <c r="B14" s="46" t="s">
         <v>575</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="51" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" thickBot="1">
-      <c r="A15" s="49"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="47" t="s">
         <v>591</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
     </row>
     <row r="16" spans="1:5" ht="17.25">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="49" t="s">
         <v>592</v>
       </c>
       <c r="B16" s="46" t="s">
         <v>576</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="51" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" thickBot="1">
-      <c r="A17" s="49"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="47" t="s">
         <v>593</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
     </row>
     <row r="21" spans="1:5" ht="17.25" thickBot="1"/>
     <row r="22" spans="1:5" ht="18" thickBot="1">
@@ -8305,169 +8297,145 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="17.25">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="49" t="s">
         <v>578</v>
       </c>
       <c r="B23" s="46" t="s">
         <v>567</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="51">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" thickBot="1">
-      <c r="A24" s="49"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="47" t="s">
         <v>579</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
     </row>
     <row r="25" spans="1:5" ht="17.25">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="49" t="s">
         <v>580</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>569</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="51">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="35.25" thickBot="1">
-      <c r="A26" s="49"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="47" t="s">
         <v>581</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
     </row>
     <row r="27" spans="1:5" ht="17.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="49" t="s">
         <v>584</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>572</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="51">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" thickBot="1">
-      <c r="A28" s="49"/>
+      <c r="A28" s="50"/>
       <c r="B28" s="47" t="s">
         <v>585</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
     </row>
     <row r="29" spans="1:5" ht="17.25">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="49" t="s">
         <v>588</v>
       </c>
       <c r="B29" s="46" t="s">
         <v>574</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D29" s="50" t="s">
+      <c r="D29" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="51">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" thickBot="1">
-      <c r="A30" s="49"/>
+      <c r="A30" s="50"/>
       <c r="B30" s="47" t="s">
         <v>589</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
     </row>
     <row r="31" spans="1:5" ht="17.25">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="49" t="s">
         <v>582</v>
       </c>
       <c r="B31" s="46" t="s">
         <v>570</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="D31" s="50" t="s">
+      <c r="D31" s="51" t="s">
         <v>571</v>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="51">
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" thickBot="1">
-      <c r="A32" s="49"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="47" t="s">
         <v>583</v>
       </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D27:D28"/>
@@ -8480,14 +8448,38 @@
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8496,7 +8488,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7D28BF-FC95-411D-BBBF-B7CDE652B6A5}">
-  <dimension ref="B2:F14"/>
+  <dimension ref="B2:F12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
@@ -8508,24 +8500,25 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="C2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="E2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="F2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="C3">
-        <v>5.93</v>
+        <f>1024*512*3/1024/1024</f>
+        <v>1.5</v>
       </c>
       <c r="D3">
         <v>7.41</v>
@@ -8540,137 +8533,101 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C4">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="D4">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="E4">
-        <v>7.4</v>
+        <v>6.58</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F6" si="0">(D4+E4) * 2</f>
+        <f t="shared" ref="F4" si="0">(D4+E4) * 2</f>
+        <v>19.740000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="33">
+      <c r="C8" s="48" t="s">
+        <v>599</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="33">
+      <c r="B9" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>600</v>
+      </c>
+      <c r="D9">
+        <v>24.71</v>
+      </c>
+      <c r="E9">
+        <v>37.07</v>
+      </c>
+      <c r="F9">
+        <v>49.43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10">
         <v>22.200000000000003</v>
       </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" t="s">
-        <v>597</v>
-      </c>
-      <c r="C5">
-        <v>2.63</v>
-      </c>
-      <c r="D5">
-        <v>3.29</v>
-      </c>
-      <c r="E5">
-        <v>6.58</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
+      <c r="C10">
+        <v>6.17</v>
+      </c>
+      <c r="D10">
+        <v>12.33</v>
+      </c>
+      <c r="E10">
+        <v>18.5</v>
+      </c>
+      <c r="F10">
+        <v>24.67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11">
         <v>19.740000000000002</v>
       </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" t="s">
-        <v>598</v>
-      </c>
-      <c r="C6">
-        <v>1.31</v>
-      </c>
-      <c r="D6">
-        <v>1.64</v>
-      </c>
-      <c r="E6">
-        <v>3.28</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>9.84</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="33">
-      <c r="C10" s="56" t="s">
-        <v>603</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="33">
-      <c r="B11" s="56" t="s">
-        <v>602</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>604</v>
+      <c r="C11">
+        <v>5.48</v>
       </c>
       <c r="D11">
-        <v>24.71</v>
+        <v>10.97</v>
       </c>
       <c r="E11">
-        <v>37.07</v>
+        <v>16.45</v>
       </c>
       <c r="F11">
-        <v>49.43</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12">
-        <v>22.200000000000003</v>
+        <v>9.84</v>
       </c>
       <c r="C12">
-        <v>6.17</v>
+        <v>2.73</v>
       </c>
       <c r="D12">
-        <v>12.33</v>
+        <v>5.47</v>
       </c>
       <c r="E12">
-        <v>18.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F12">
-        <v>24.67</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13">
-        <v>19.740000000000002</v>
-      </c>
-      <c r="C13">
-        <v>5.48</v>
-      </c>
-      <c r="D13">
-        <v>10.97</v>
-      </c>
-      <c r="E13">
-        <v>16.45</v>
-      </c>
-      <c r="F13">
-        <v>21.93</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14">
-        <v>9.84</v>
-      </c>
-      <c r="C14">
-        <v>2.73</v>
-      </c>
-      <c r="D14">
-        <v>5.47</v>
-      </c>
-      <c r="E14">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F14">
         <v>10.93</v>
       </c>
     </row>

--- a/ppt/tables.xlsx
+++ b/ppt/tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\boram1288\orange\architect\test-p\ppt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\boram1288\orange\arch\test-p\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E568DC2-7F7D-4D0F-8531-0546D1D266C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2F1186-DAF9-4506-85F7-08B0A3EF4C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="915" activeTab="7" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="915" activeTab="8" xr2:uid="{566D5FF2-664D-49E6-8694-5714426ADE65}"/>
   </bookViews>
   <sheets>
     <sheet name="침해 사고" sheetId="9" r:id="rId1"/>
@@ -21,15 +21,16 @@
     <sheet name="CONST" sheetId="5" r:id="rId6"/>
     <sheet name="QA" sheetId="6" r:id="rId7"/>
     <sheet name="Sheet1" sheetId="16" r:id="rId8"/>
-    <sheet name="ISO 25010" sheetId="14" r:id="rId9"/>
-    <sheet name="ISO 25023" sheetId="15" r:id="rId10"/>
-    <sheet name="Matrix" sheetId="8" r:id="rId11"/>
-    <sheet name="pKVM interfacer" sheetId="10" r:id="rId12"/>
-    <sheet name="ContextView" sheetId="12" r:id="rId13"/>
-    <sheet name="DP" sheetId="13" r:id="rId14"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId9"/>
+    <sheet name="ISO 25010" sheetId="14" r:id="rId10"/>
+    <sheet name="ISO 25023" sheetId="15" r:id="rId11"/>
+    <sheet name="Matrix" sheetId="8" r:id="rId12"/>
+    <sheet name="pKVM interfacer" sheetId="10" r:id="rId13"/>
+    <sheet name="ContextView" sheetId="12" r:id="rId14"/>
+    <sheet name="DP" sheetId="13" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'ISO 25023'!$A$2:$J$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'ISO 25023'!$A$2:$J$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -438,7 +439,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="629">
   <si>
     <t>QA-01</t>
   </si>
@@ -4015,12 +4016,90 @@
     <t>1280x720</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>노출 정보</t>
+  </si>
+  <si>
+    <t>추론 가능한 정보</t>
+  </si>
+  <si>
+    <t>CAPTURE/START/STOP</t>
+  </si>
+  <si>
+    <t>카메라가 언제 사용되는지</t>
+  </si>
+  <si>
+    <t>sensor_id</t>
+  </si>
+  <si>
+    <t>front/rear/robot arm camera 등 어떤 카메라인지</t>
+  </si>
+  <si>
+    <t>width/height</t>
+  </si>
+  <si>
+    <t>영상 해상도</t>
+  </si>
+  <si>
+    <t>fps</t>
+  </si>
+  <si>
+    <t>sensing 방식</t>
+  </si>
+  <si>
+    <t>pixel format</t>
+  </si>
+  <si>
+    <t>RGB/YUV/depth 등</t>
+  </si>
+  <si>
+    <t>exposure/gain</t>
+  </si>
+  <si>
+    <t>주변 밝기</t>
+  </si>
+  <si>
+    <t>focus/lens position</t>
+  </si>
+  <si>
+    <t>대상 거리 변화</t>
+  </si>
+  <si>
+    <t>frame count</t>
+  </si>
+  <si>
+    <t>촬영량</t>
+  </si>
+  <si>
+    <t>IOVA/GPA</t>
+  </si>
+  <si>
+    <t>memory 사용 패턴</t>
+  </si>
+  <si>
+    <t>buffer size/stride</t>
+  </si>
+  <si>
+    <t>영상 포맷 추정</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>작업 발생 시점</t>
+  </si>
+  <si>
+    <t>secure/nonsecure flag</t>
+  </si>
+  <si>
+    <t>보안 작업 수행 여부</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4231,6 +4310,22 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -4416,7 +4511,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4587,6 +4682,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4934,9 +5035,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAA4CBF-2B00-47DE-B890-6C9CADE53CC2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="3" width="22.625" customWidth="1"/>
+    <col min="2" max="3" width="22.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5001,19 +5102,313 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12054B3A-2648-4FB0-BBA9-9ACDCE3B68E0}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="39.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="105" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A1" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A2" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A3" s="25"/>
+      <c r="B3" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A5" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A6" s="25"/>
+      <c r="B6" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A7" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A9" s="30"/>
+      <c r="B9" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A10" s="30"/>
+      <c r="B10" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A11" s="30"/>
+      <c r="B11" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A12" s="30"/>
+      <c r="B12" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A13" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A14" s="25"/>
+      <c r="B14" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A15" s="25"/>
+      <c r="B15" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A16" s="25"/>
+      <c r="B16" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A17" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A18" s="25"/>
+      <c r="B18" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A19" s="25"/>
+      <c r="B19" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A20" s="25"/>
+      <c r="B20" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A21" s="25"/>
+      <c r="B21" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A22" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A23" s="25"/>
+      <c r="B23" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A24" s="30"/>
+      <c r="B24" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
+      <c r="A25" s="25"/>
+      <c r="B25" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="24" customFormat="1" ht="19.8" thickBot="1">
+      <c r="A27" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A28" s="30"/>
+      <c r="B28" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A29" s="30"/>
+      <c r="B29" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="19.2">
+      <c r="B30" s="31" t="s">
+        <v>255</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57942659-D9CB-45B1-9A8D-84CB397A0EAA}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I96"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" customWidth="1"/>
     <col min="4" max="4" width="62" customWidth="1"/>
-    <col min="5" max="5" width="97.625" customWidth="1"/>
-    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="97.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="39" customFormat="1" ht="21">
+    <row r="1" spans="1:9" s="39" customFormat="1" ht="20.399999999999999">
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="38" t="s">
@@ -5030,7 +5425,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25">
+    <row r="2" spans="1:9" ht="19.2">
       <c r="A2" s="39" t="s">
         <v>562</v>
       </c>
@@ -5050,7 +5445,7 @@
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
     </row>
-    <row r="3" spans="1:9" ht="17.25" hidden="1">
+    <row r="3" spans="1:9" ht="19.2" hidden="1">
       <c r="B3" s="32" t="s">
         <v>512</v>
       </c>
@@ -5067,7 +5462,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
     </row>
-    <row r="4" spans="1:9" ht="17.25" hidden="1">
+    <row r="4" spans="1:9" ht="19.2" hidden="1">
       <c r="B4" s="32" t="s">
         <v>512</v>
       </c>
@@ -5084,7 +5479,7 @@
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
     </row>
-    <row r="5" spans="1:9" ht="17.25" hidden="1">
+    <row r="5" spans="1:9" ht="19.2" hidden="1">
       <c r="B5" s="32" t="s">
         <v>512</v>
       </c>
@@ -5101,7 +5496,7 @@
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
     </row>
-    <row r="6" spans="1:9" s="42" customFormat="1" ht="17.25">
+    <row r="6" spans="1:9" s="42" customFormat="1" ht="19.2">
       <c r="A6" s="42" t="s">
         <v>557</v>
       </c>
@@ -5128,7 +5523,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" hidden="1">
+    <row r="7" spans="1:9" ht="19.2" hidden="1">
       <c r="B7" s="32" t="s">
         <v>512</v>
       </c>
@@ -5145,7 +5540,7 @@
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
     </row>
-    <row r="8" spans="1:9" ht="17.25" hidden="1">
+    <row r="8" spans="1:9" ht="19.2" hidden="1">
       <c r="B8" s="32" t="s">
         <v>513</v>
       </c>
@@ -5162,7 +5557,7 @@
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
     </row>
-    <row r="9" spans="1:9" s="42" customFormat="1" ht="17.25">
+    <row r="9" spans="1:9" s="42" customFormat="1" ht="19.2">
       <c r="A9" s="42" t="s">
         <v>557</v>
       </c>
@@ -5189,7 +5584,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" hidden="1">
+    <row r="10" spans="1:9" ht="19.2" hidden="1">
       <c r="B10" s="32" t="s">
         <v>513</v>
       </c>
@@ -5206,7 +5601,7 @@
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
     </row>
-    <row r="11" spans="1:9" ht="17.25" hidden="1">
+    <row r="11" spans="1:9" ht="19.2" hidden="1">
       <c r="B11" s="32" t="s">
         <v>513</v>
       </c>
@@ -5223,7 +5618,7 @@
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:9" ht="17.25" hidden="1">
+    <row r="12" spans="1:9" ht="19.2" hidden="1">
       <c r="B12" s="32" t="s">
         <v>514</v>
       </c>
@@ -5243,7 +5638,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.25" hidden="1">
+    <row r="13" spans="1:9" ht="19.2" hidden="1">
       <c r="B13" s="32" t="s">
         <v>514</v>
       </c>
@@ -5260,7 +5655,7 @@
       <c r="G13" s="32"/>
       <c r="H13" s="32"/>
     </row>
-    <row r="14" spans="1:9" ht="17.25" hidden="1">
+    <row r="14" spans="1:9" ht="19.2" hidden="1">
       <c r="B14" s="32" t="s">
         <v>514</v>
       </c>
@@ -5277,7 +5672,7 @@
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
     </row>
-    <row r="15" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+    <row r="15" spans="1:9" s="39" customFormat="1" ht="20.399999999999999" hidden="1">
       <c r="B15" s="37"/>
       <c r="C15" s="37"/>
       <c r="D15" s="38" t="s">
@@ -5288,7 +5683,7 @@
       <c r="G15" s="37"/>
       <c r="H15" s="37"/>
     </row>
-    <row r="16" spans="1:9" ht="17.25" hidden="1">
+    <row r="16" spans="1:9" ht="19.2" hidden="1">
       <c r="B16" s="32" t="s">
         <v>511</v>
       </c>
@@ -5305,7 +5700,7 @@
       <c r="G16" s="32"/>
       <c r="H16" s="32"/>
     </row>
-    <row r="17" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="17" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B17" s="35" t="s">
         <v>515</v>
       </c>
@@ -5325,7 +5720,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="17.25" hidden="1">
+    <row r="18" spans="2:9" ht="19.2" hidden="1">
       <c r="B18" s="32" t="s">
         <v>516</v>
       </c>
@@ -5345,7 +5740,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="17.25" hidden="1">
+    <row r="19" spans="2:9" ht="19.2" hidden="1">
       <c r="B19" s="32" t="s">
         <v>516</v>
       </c>
@@ -5362,7 +5757,7 @@
       <c r="G19" s="32"/>
       <c r="H19" s="32"/>
     </row>
-    <row r="20" spans="2:9" ht="17.25" hidden="1">
+    <row r="20" spans="2:9" ht="19.2" hidden="1">
       <c r="B20" s="32" t="s">
         <v>516</v>
       </c>
@@ -5379,7 +5774,7 @@
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
     </row>
-    <row r="21" spans="2:9" s="39" customFormat="1" ht="21" hidden="1">
+    <row r="21" spans="2:9" s="39" customFormat="1" ht="20.399999999999999" hidden="1">
       <c r="B21" s="37"/>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
@@ -5390,7 +5785,7 @@
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
     </row>
-    <row r="22" spans="2:9" ht="17.25" hidden="1">
+    <row r="22" spans="2:9" ht="19.2" hidden="1">
       <c r="B22" s="32" t="s">
         <v>511</v>
       </c>
@@ -5407,7 +5802,7 @@
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
     </row>
-    <row r="23" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="23" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B23" s="35" t="s">
         <v>517</v>
       </c>
@@ -5427,7 +5822,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="24" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B24" s="35" t="s">
         <v>517</v>
       </c>
@@ -5444,7 +5839,7 @@
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
     </row>
-    <row r="25" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="25" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B25" s="35" t="s">
         <v>517</v>
       </c>
@@ -5461,7 +5856,7 @@
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
     </row>
-    <row r="26" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="26" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B26" s="35" t="s">
         <v>518</v>
       </c>
@@ -5478,7 +5873,7 @@
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
     </row>
-    <row r="27" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="27" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B27" s="35" t="s">
         <v>518</v>
       </c>
@@ -5495,7 +5890,7 @@
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
     </row>
-    <row r="28" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="28" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B28" s="35" t="s">
         <v>518</v>
       </c>
@@ -5512,7 +5907,7 @@
       <c r="G28" s="35"/>
       <c r="H28" s="35"/>
     </row>
-    <row r="29" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="29" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B29" s="35" t="s">
         <v>518</v>
       </c>
@@ -5529,7 +5924,7 @@
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
     </row>
-    <row r="30" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="30" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B30" s="35" t="s">
         <v>519</v>
       </c>
@@ -5546,7 +5941,7 @@
       <c r="G30" s="35"/>
       <c r="H30" s="35"/>
     </row>
-    <row r="31" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="31" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B31" s="35" t="s">
         <v>519</v>
       </c>
@@ -5563,7 +5958,7 @@
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
     </row>
-    <row r="32" spans="2:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="32" spans="2:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B32" s="35" t="s">
         <v>519</v>
       </c>
@@ -5580,7 +5975,7 @@
       <c r="G32" s="35"/>
       <c r="H32" s="35"/>
     </row>
-    <row r="33" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="33" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B33" s="35" t="s">
         <v>519</v>
       </c>
@@ -5597,7 +5992,7 @@
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
     </row>
-    <row r="34" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="34" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B34" s="35" t="s">
         <v>519</v>
       </c>
@@ -5614,7 +6009,7 @@
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
     </row>
-    <row r="35" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="35" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B35" s="35" t="s">
         <v>519</v>
       </c>
@@ -5631,7 +6026,7 @@
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
     </row>
-    <row r="36" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="36" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B36" s="35" t="s">
         <v>519</v>
       </c>
@@ -5648,7 +6043,7 @@
       <c r="G36" s="35"/>
       <c r="H36" s="35"/>
     </row>
-    <row r="37" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="37" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B37" s="35" t="s">
         <v>519</v>
       </c>
@@ -5665,7 +6060,7 @@
       <c r="G37" s="35"/>
       <c r="H37" s="35"/>
     </row>
-    <row r="38" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="38" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B38" s="35" t="s">
         <v>519</v>
       </c>
@@ -5682,7 +6077,7 @@
       <c r="G38" s="35"/>
       <c r="H38" s="35"/>
     </row>
-    <row r="39" spans="2:8" s="24" customFormat="1" ht="34.5" hidden="1">
+    <row r="39" spans="2:8" s="24" customFormat="1" ht="38.4" hidden="1">
       <c r="B39" s="35" t="s">
         <v>520</v>
       </c>
@@ -5699,7 +6094,7 @@
       <c r="G39" s="35"/>
       <c r="H39" s="35"/>
     </row>
-    <row r="40" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="40" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B40" s="35" t="s">
         <v>520</v>
       </c>
@@ -5716,7 +6111,7 @@
       <c r="G40" s="35"/>
       <c r="H40" s="35"/>
     </row>
-    <row r="41" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="41" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B41" s="35" t="s">
         <v>520</v>
       </c>
@@ -5733,7 +6128,7 @@
       <c r="G41" s="35"/>
       <c r="H41" s="35"/>
     </row>
-    <row r="42" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="42" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B42" s="35" t="s">
         <v>521</v>
       </c>
@@ -5750,7 +6145,7 @@
       <c r="G42" s="35"/>
       <c r="H42" s="35"/>
     </row>
-    <row r="43" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="43" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B43" s="35" t="s">
         <v>522</v>
       </c>
@@ -5767,7 +6162,7 @@
       <c r="G43" s="35"/>
       <c r="H43" s="35"/>
     </row>
-    <row r="44" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="44" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B44" s="35" t="s">
         <v>522</v>
       </c>
@@ -5784,7 +6179,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" s="39" customFormat="1" ht="21" hidden="1">
+    <row r="45" spans="2:8" s="39" customFormat="1" ht="20.399999999999999" hidden="1">
       <c r="B45" s="37"/>
       <c r="C45" s="37"/>
       <c r="D45" s="38" t="s">
@@ -5795,7 +6190,7 @@
       <c r="G45" s="37"/>
       <c r="H45" s="37"/>
     </row>
-    <row r="46" spans="2:8" ht="17.25" hidden="1">
+    <row r="46" spans="2:8" ht="19.2" hidden="1">
       <c r="B46" s="32" t="s">
         <v>511</v>
       </c>
@@ -5812,7 +6207,7 @@
       <c r="G46" s="32"/>
       <c r="H46" s="32"/>
     </row>
-    <row r="47" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="47" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B47" s="35" t="s">
         <v>523</v>
       </c>
@@ -5829,7 +6224,7 @@
       <c r="G47" s="35"/>
       <c r="H47" s="35"/>
     </row>
-    <row r="48" spans="2:8" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="48" spans="2:8" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B48" s="35" t="s">
         <v>523</v>
       </c>
@@ -5846,7 +6241,7 @@
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
     </row>
-    <row r="49" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="49" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B49" s="35" t="s">
         <v>523</v>
       </c>
@@ -5863,7 +6258,7 @@
       <c r="G49" s="35"/>
       <c r="H49" s="35"/>
     </row>
-    <row r="50" spans="1:9" s="45" customFormat="1" ht="17.25">
+    <row r="50" spans="1:9" s="45" customFormat="1" ht="19.2">
       <c r="A50" s="45" t="s">
         <v>558</v>
       </c>
@@ -5890,7 +6285,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="17.25" hidden="1">
+    <row r="51" spans="1:9" ht="19.2" hidden="1">
       <c r="B51" s="32" t="s">
         <v>524</v>
       </c>
@@ -5907,7 +6302,7 @@
       <c r="G51" s="32"/>
       <c r="H51" s="32"/>
     </row>
-    <row r="52" spans="1:9" ht="17.25" hidden="1">
+    <row r="52" spans="1:9" ht="19.2" hidden="1">
       <c r="B52" s="32" t="s">
         <v>524</v>
       </c>
@@ -5924,7 +6319,7 @@
       <c r="G52" s="32"/>
       <c r="H52" s="32"/>
     </row>
-    <row r="53" spans="1:9" s="42" customFormat="1" ht="34.5">
+    <row r="53" spans="1:9" s="42" customFormat="1" ht="38.4">
       <c r="A53" s="42" t="s">
         <v>558</v>
       </c>
@@ -5947,7 +6342,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="17.25" hidden="1">
+    <row r="54" spans="1:9" ht="19.2" hidden="1">
       <c r="B54" s="32" t="s">
         <v>525</v>
       </c>
@@ -5964,7 +6359,7 @@
       <c r="G54" s="32"/>
       <c r="H54" s="32"/>
     </row>
-    <row r="55" spans="1:9" ht="17.25" hidden="1">
+    <row r="55" spans="1:9" ht="19.2" hidden="1">
       <c r="B55" s="32" t="s">
         <v>525</v>
       </c>
@@ -5981,7 +6376,7 @@
       <c r="G55" s="32"/>
       <c r="H55" s="32"/>
     </row>
-    <row r="56" spans="1:9" ht="17.25" hidden="1">
+    <row r="56" spans="1:9" ht="19.2" hidden="1">
       <c r="B56" s="32" t="s">
         <v>526</v>
       </c>
@@ -5998,7 +6393,7 @@
       <c r="G56" s="32"/>
       <c r="H56" s="32"/>
     </row>
-    <row r="57" spans="1:9" ht="17.25" hidden="1">
+    <row r="57" spans="1:9" ht="19.2" hidden="1">
       <c r="B57" s="32" t="s">
         <v>526</v>
       </c>
@@ -6015,7 +6410,7 @@
       <c r="G57" s="32"/>
       <c r="H57" s="32"/>
     </row>
-    <row r="58" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+    <row r="58" spans="1:9" s="39" customFormat="1" ht="20.399999999999999" hidden="1">
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
       <c r="D58" s="38" t="s">
@@ -6026,7 +6421,7 @@
       <c r="G58" s="37"/>
       <c r="H58" s="37"/>
     </row>
-    <row r="59" spans="1:9" ht="17.25" hidden="1">
+    <row r="59" spans="1:9" ht="19.2" hidden="1">
       <c r="B59" s="32" t="s">
         <v>511</v>
       </c>
@@ -6043,7 +6438,7 @@
       <c r="G59" s="32"/>
       <c r="H59" s="32"/>
     </row>
-    <row r="60" spans="1:9" s="42" customFormat="1" ht="34.5">
+    <row r="60" spans="1:9" s="42" customFormat="1" ht="38.4">
       <c r="A60" s="42" t="s">
         <v>559</v>
       </c>
@@ -6070,7 +6465,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="17.25" hidden="1">
+    <row r="61" spans="1:9" ht="19.2" hidden="1">
       <c r="B61" s="32" t="s">
         <v>527</v>
       </c>
@@ -6087,7 +6482,7 @@
       <c r="G61" s="32"/>
       <c r="H61" s="32"/>
     </row>
-    <row r="62" spans="1:9" ht="34.5" hidden="1">
+    <row r="62" spans="1:9" ht="38.4" hidden="1">
       <c r="B62" s="32" t="s">
         <v>527</v>
       </c>
@@ -6104,7 +6499,7 @@
       <c r="G62" s="32"/>
       <c r="H62" s="32"/>
     </row>
-    <row r="63" spans="1:9" s="45" customFormat="1" ht="17.25">
+    <row r="63" spans="1:9" s="45" customFormat="1" ht="19.2">
       <c r="A63" s="45" t="s">
         <v>559</v>
       </c>
@@ -6131,7 +6526,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="17.25" hidden="1">
+    <row r="64" spans="1:9" ht="19.2" hidden="1">
       <c r="B64" s="32" t="s">
         <v>528</v>
       </c>
@@ -6148,7 +6543,7 @@
       <c r="G64" s="32"/>
       <c r="H64" s="32"/>
     </row>
-    <row r="65" spans="1:9" ht="17.25" hidden="1">
+    <row r="65" spans="1:9" ht="19.2" hidden="1">
       <c r="B65" s="32" t="s">
         <v>528</v>
       </c>
@@ -6165,7 +6560,7 @@
       <c r="G65" s="32"/>
       <c r="H65" s="32"/>
     </row>
-    <row r="66" spans="1:9" ht="17.25" hidden="1">
+    <row r="66" spans="1:9" ht="19.2" hidden="1">
       <c r="B66" s="32" t="s">
         <v>529</v>
       </c>
@@ -6182,7 +6577,7 @@
       <c r="G66" s="32"/>
       <c r="H66" s="32"/>
     </row>
-    <row r="67" spans="1:9" ht="17.25" hidden="1">
+    <row r="67" spans="1:9" ht="19.2" hidden="1">
       <c r="B67" s="32" t="s">
         <v>530</v>
       </c>
@@ -6199,7 +6594,7 @@
       <c r="G67" s="32"/>
       <c r="H67" s="32"/>
     </row>
-    <row r="68" spans="1:9" ht="17.25" hidden="1">
+    <row r="68" spans="1:9" ht="19.2" hidden="1">
       <c r="B68" s="32" t="s">
         <v>530</v>
       </c>
@@ -6216,7 +6611,7 @@
       <c r="G68" s="32"/>
       <c r="H68" s="32"/>
     </row>
-    <row r="69" spans="1:9" ht="17.25" hidden="1">
+    <row r="69" spans="1:9" ht="19.2" hidden="1">
       <c r="B69" s="32" t="s">
         <v>531</v>
       </c>
@@ -6233,7 +6628,7 @@
       <c r="G69" s="32"/>
       <c r="H69" s="32"/>
     </row>
-    <row r="70" spans="1:9" ht="17.25" hidden="1">
+    <row r="70" spans="1:9" ht="19.2" hidden="1">
       <c r="B70" s="32" t="s">
         <v>531</v>
       </c>
@@ -6250,7 +6645,7 @@
       <c r="G70" s="32"/>
       <c r="H70" s="32"/>
     </row>
-    <row r="71" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+    <row r="71" spans="1:9" s="39" customFormat="1" ht="20.399999999999999" hidden="1">
       <c r="B71" s="37"/>
       <c r="C71" s="37"/>
       <c r="D71" s="38" t="s">
@@ -6261,7 +6656,7 @@
       <c r="G71" s="37"/>
       <c r="H71" s="37"/>
     </row>
-    <row r="72" spans="1:9" ht="17.25" hidden="1">
+    <row r="72" spans="1:9" ht="19.2" hidden="1">
       <c r="B72" s="32" t="s">
         <v>511</v>
       </c>
@@ -6278,7 +6673,7 @@
       <c r="G72" s="32"/>
       <c r="H72" s="32"/>
     </row>
-    <row r="73" spans="1:9" s="45" customFormat="1" ht="17.25">
+    <row r="73" spans="1:9" s="45" customFormat="1" ht="19.2">
       <c r="A73" s="45" t="s">
         <v>560</v>
       </c>
@@ -6305,7 +6700,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="17.25" hidden="1">
+    <row r="74" spans="1:9" ht="19.2" hidden="1">
       <c r="B74" s="32" t="s">
         <v>532</v>
       </c>
@@ -6322,7 +6717,7 @@
       <c r="G74" s="32"/>
       <c r="H74" s="32"/>
     </row>
-    <row r="75" spans="1:9" s="42" customFormat="1" ht="17.25">
+    <row r="75" spans="1:9" s="42" customFormat="1" ht="19.2">
       <c r="A75" s="42" t="s">
         <v>560</v>
       </c>
@@ -6349,7 +6744,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="17.25" hidden="1">
+    <row r="76" spans="1:9" ht="19.2" hidden="1">
       <c r="B76" s="32" t="s">
         <v>533</v>
       </c>
@@ -6366,7 +6761,7 @@
       <c r="G76" s="32"/>
       <c r="H76" s="32"/>
     </row>
-    <row r="77" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="77" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B77" s="35" t="s">
         <v>534</v>
       </c>
@@ -6383,7 +6778,7 @@
       <c r="G77" s="35"/>
       <c r="H77" s="35"/>
     </row>
-    <row r="78" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="78" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B78" s="35" t="s">
         <v>534</v>
       </c>
@@ -6400,7 +6795,7 @@
       <c r="G78" s="35"/>
       <c r="H78" s="35"/>
     </row>
-    <row r="79" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="79" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B79" s="35" t="s">
         <v>534</v>
       </c>
@@ -6417,7 +6812,7 @@
       <c r="G79" s="35"/>
       <c r="H79" s="35"/>
     </row>
-    <row r="80" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="80" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B80" s="35" t="s">
         <v>535</v>
       </c>
@@ -6434,7 +6829,7 @@
       <c r="G80" s="35"/>
       <c r="H80" s="35"/>
     </row>
-    <row r="81" spans="1:9" ht="17.25" hidden="1">
+    <row r="81" spans="1:9" ht="19.2" hidden="1">
       <c r="B81" s="32" t="s">
         <v>535</v>
       </c>
@@ -6451,7 +6846,7 @@
       <c r="G81" s="32"/>
       <c r="H81" s="32"/>
     </row>
-    <row r="82" spans="1:9" ht="17.25" hidden="1">
+    <row r="82" spans="1:9" ht="19.2" hidden="1">
       <c r="B82" s="32" t="s">
         <v>535</v>
       </c>
@@ -6468,7 +6863,7 @@
       <c r="G82" s="32"/>
       <c r="H82" s="32"/>
     </row>
-    <row r="83" spans="1:9" ht="17.25" hidden="1">
+    <row r="83" spans="1:9" ht="19.2" hidden="1">
       <c r="B83" s="32" t="s">
         <v>536</v>
       </c>
@@ -6485,7 +6880,7 @@
       <c r="G83" s="32"/>
       <c r="H83" s="32"/>
     </row>
-    <row r="84" spans="1:9" ht="34.5" hidden="1">
+    <row r="84" spans="1:9" ht="38.4" hidden="1">
       <c r="B84" s="32" t="s">
         <v>536</v>
       </c>
@@ -6502,7 +6897,7 @@
       <c r="G84" s="32"/>
       <c r="H84" s="32"/>
     </row>
-    <row r="85" spans="1:9" ht="17.25" hidden="1">
+    <row r="85" spans="1:9" ht="19.2" hidden="1">
       <c r="B85" s="32" t="s">
         <v>536</v>
       </c>
@@ -6519,7 +6914,7 @@
       <c r="G85" s="32"/>
       <c r="H85" s="32"/>
     </row>
-    <row r="86" spans="1:9" s="39" customFormat="1" ht="21" hidden="1">
+    <row r="86" spans="1:9" s="39" customFormat="1" ht="20.399999999999999" hidden="1">
       <c r="B86" s="37"/>
       <c r="C86" s="37"/>
       <c r="D86" s="38" t="s">
@@ -6530,7 +6925,7 @@
       <c r="G86" s="37"/>
       <c r="H86" s="37"/>
     </row>
-    <row r="87" spans="1:9" ht="17.25" hidden="1">
+    <row r="87" spans="1:9" ht="19.2" hidden="1">
       <c r="B87" s="32" t="s">
         <v>511</v>
       </c>
@@ -6547,7 +6942,7 @@
       <c r="G87" s="32"/>
       <c r="H87" s="32"/>
     </row>
-    <row r="88" spans="1:9" s="45" customFormat="1" ht="34.5">
+    <row r="88" spans="1:9" s="45" customFormat="1" ht="38.4">
       <c r="A88" s="45" t="s">
         <v>561</v>
       </c>
@@ -6574,7 +6969,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="89" spans="1:9" s="45" customFormat="1" ht="34.5">
+    <row r="89" spans="1:9" s="45" customFormat="1" ht="38.4">
       <c r="A89" s="45" t="s">
         <v>561</v>
       </c>
@@ -6601,7 +6996,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="90" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="90" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B90" s="35" t="s">
         <v>537</v>
       </c>
@@ -6618,7 +7013,7 @@
       <c r="G90" s="35"/>
       <c r="H90" s="35"/>
     </row>
-    <row r="91" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="91" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B91" s="35" t="s">
         <v>538</v>
       </c>
@@ -6635,7 +7030,7 @@
       <c r="G91" s="35"/>
       <c r="H91" s="35"/>
     </row>
-    <row r="92" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="92" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B92" s="35" t="s">
         <v>538</v>
       </c>
@@ -6652,7 +7047,7 @@
       <c r="G92" s="35"/>
       <c r="H92" s="35"/>
     </row>
-    <row r="93" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="93" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B93" s="35" t="s">
         <v>539</v>
       </c>
@@ -6669,7 +7064,7 @@
       <c r="G93" s="35"/>
       <c r="H93" s="35"/>
     </row>
-    <row r="94" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="94" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B94" s="35" t="s">
         <v>539</v>
       </c>
@@ -6686,7 +7081,7 @@
       <c r="G94" s="35"/>
       <c r="H94" s="35"/>
     </row>
-    <row r="95" spans="1:9" s="24" customFormat="1" ht="17.25" hidden="1">
+    <row r="95" spans="1:9" s="24" customFormat="1" ht="19.2" hidden="1">
       <c r="B95" s="35" t="s">
         <v>539</v>
       </c>
@@ -6703,7 +7098,7 @@
       <c r="G95" s="35"/>
       <c r="H95" s="35"/>
     </row>
-    <row r="96" spans="1:9" s="24" customFormat="1" ht="34.5" hidden="1">
+    <row r="96" spans="1:9" s="24" customFormat="1" ht="38.4" hidden="1">
       <c r="B96" s="35" t="s">
         <v>539</v>
       </c>
@@ -6765,12 +7160,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A7022E-1906-487A-90E9-2BB33B9DC038}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="13" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7157,24 +7552,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0DB3F-D8A6-4BD0-B1F7-B5D84B7939AB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="25.75" customWidth="1"/>
-    <col min="2" max="2" width="64.125" customWidth="1"/>
-    <col min="3" max="3" width="40.875" customWidth="1"/>
-    <col min="4" max="4" width="25.75" customWidth="1"/>
+    <col min="1" max="1" width="25.69921875" customWidth="1"/>
+    <col min="2" max="2" width="64.09765625" customWidth="1"/>
+    <col min="3" max="3" width="40.8984375" customWidth="1"/>
+    <col min="4" max="4" width="25.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1"/>
-    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+    <row r="2" spans="1:3" ht="18" thickBot="1"/>
+    <row r="3" spans="1:3" ht="18" thickBot="1">
       <c r="A3" s="9" t="s">
         <v>109</v>
       </c>
@@ -7185,7 +7580,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="29.25" thickBot="1">
+    <row r="4" spans="1:3" ht="28.2" thickBot="1">
       <c r="A4" s="10" t="s">
         <v>112</v>
       </c>
@@ -7196,7 +7591,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43.5" thickBot="1">
+    <row r="5" spans="1:3" ht="42" thickBot="1">
       <c r="A5" s="10" t="s">
         <v>115</v>
       </c>
@@ -7207,7 +7602,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" thickBot="1">
+    <row r="6" spans="1:3" ht="42" thickBot="1">
       <c r="A6" s="10" t="s">
         <v>118</v>
       </c>
@@ -7218,7 +7613,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" thickBot="1">
+    <row r="7" spans="1:3" ht="42" thickBot="1">
       <c r="A7" s="10" t="s">
         <v>121</v>
       </c>
@@ -7229,7 +7624,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" thickBot="1">
+    <row r="8" spans="1:3" ht="42" thickBot="1">
       <c r="A8" s="13" t="s">
         <v>129</v>
       </c>
@@ -7240,7 +7635,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.5">
+    <row r="9" spans="1:3" ht="27.6">
       <c r="A9" s="13" t="s">
         <v>128</v>
       </c>
@@ -7250,102 +7645,6 @@
       <c r="C9" s="14" t="s">
         <v>126</v>
       </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="29.125" defaultRowHeight="16.5"/>
-  <cols>
-    <col min="2" max="2" width="74.625" customWidth="1"/>
-    <col min="3" max="3" width="57.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="15"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="16"/>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="16"/>
-    </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
-      <c r="A5" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
-      <c r="A7" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3" ht="18" thickBot="1">
-      <c r="A8" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9" spans="1:3" ht="18" thickBot="1">
-      <c r="A9" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -7354,16 +7653,112 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C28460-B628-4EDE-BDBD-E1106E6E8025}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="29.09765625" defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="2" max="2" width="74.59765625" customWidth="1"/>
+    <col min="3" max="3" width="57.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A1" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="15"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A2" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="16"/>
+    </row>
+    <row r="3" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A3" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A4" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A5" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A6" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A7" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A8" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" ht="19.8" thickBot="1">
+      <c r="A9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E403F8-499C-4609-BBF1-C98C4D7CB1B3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.25" customWidth="1"/>
+    <col min="2" max="2" width="63.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
+    <row r="1" spans="1:3" ht="19.8" thickBot="1">
       <c r="A1" s="15" t="s">
         <v>161</v>
       </c>
@@ -7374,7 +7769,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
+    <row r="2" spans="1:3" ht="19.8" thickBot="1">
       <c r="A2" s="20" t="s">
         <v>148</v>
       </c>
@@ -7385,7 +7780,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
+    <row r="3" spans="1:3" ht="19.8" thickBot="1">
       <c r="A3" s="20" t="s">
         <v>150</v>
       </c>
@@ -7396,7 +7791,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
+    <row r="4" spans="1:3" ht="19.8" thickBot="1">
       <c r="A4" s="20" t="s">
         <v>152</v>
       </c>
@@ -7407,7 +7802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" thickBot="1">
+    <row r="5" spans="1:3" ht="19.8" thickBot="1">
       <c r="A5" s="20" t="s">
         <v>154</v>
       </c>
@@ -7418,7 +7813,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
+    <row r="6" spans="1:3" ht="19.8" thickBot="1">
       <c r="A6" s="20" t="s">
         <v>156</v>
       </c>
@@ -7429,7 +7824,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" thickBot="1">
+    <row r="7" spans="1:3" ht="19.8" thickBot="1">
       <c r="A7" s="20" t="s">
         <v>158</v>
       </c>
@@ -7449,11 +7844,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC930AF-9269-4D83-9B82-D3D07D029F13}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7564,10 +7959,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89DFAC-72A6-4108-9E56-15AF596EC46D}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.25" customWidth="1"/>
+    <col min="3" max="3" width="57.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7766,9 +8161,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE187A4-FDD5-45A6-8352-744BFCAE912E}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
     <col min="3" max="3" width="69" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7903,10 +8298,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A541DB4C-3518-4E9E-B674-29F56CE3873D}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7995,9 +8390,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B28AE17-5A65-4395-BC12-CB2558163A43}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" customWidth="1"/>
     <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8046,14 +8441,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291A8966-D248-40C5-810D-CDD92F7EB876}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="2" width="101" customWidth="1"/>
-    <col min="3" max="5" width="9.25" customWidth="1"/>
+    <col min="3" max="5" width="9.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="39" customFormat="1" ht="18" thickBot="1">
+    <row r="1" spans="1:5" s="39" customFormat="1" ht="19.8" thickBot="1">
       <c r="A1" s="15" t="s">
         <v>563</v>
       </c>
@@ -8070,7 +8465,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.25">
+    <row r="2" spans="1:5" ht="19.2">
       <c r="A2" s="49" t="s">
         <v>578</v>
       </c>
@@ -8087,7 +8482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" thickBot="1">
+    <row r="3" spans="1:5" ht="19.8" thickBot="1">
       <c r="A3" s="50"/>
       <c r="B3" s="47" t="s">
         <v>579</v>
@@ -8096,7 +8491,7 @@
       <c r="D3" s="52"/>
       <c r="E3" s="52"/>
     </row>
-    <row r="4" spans="1:5" ht="17.25">
+    <row r="4" spans="1:5" ht="19.2">
       <c r="A4" s="49" t="s">
         <v>580</v>
       </c>
@@ -8113,7 +8508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="35.25" thickBot="1">
+    <row r="5" spans="1:5" ht="39" thickBot="1">
       <c r="A5" s="50"/>
       <c r="B5" s="47" t="s">
         <v>581</v>
@@ -8122,7 +8517,7 @@
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
     </row>
-    <row r="6" spans="1:5" ht="17.25">
+    <row r="6" spans="1:5" ht="19.2">
       <c r="A6" s="49" t="s">
         <v>582</v>
       </c>
@@ -8139,7 +8534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" thickBot="1">
+    <row r="7" spans="1:5" ht="19.8" thickBot="1">
       <c r="A7" s="50"/>
       <c r="B7" s="47" t="s">
         <v>583</v>
@@ -8148,7 +8543,7 @@
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
     </row>
-    <row r="8" spans="1:5" ht="17.25">
+    <row r="8" spans="1:5" ht="19.2">
       <c r="A8" s="49" t="s">
         <v>584</v>
       </c>
@@ -8165,7 +8560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" thickBot="1">
+    <row r="9" spans="1:5" ht="19.8" thickBot="1">
       <c r="A9" s="50"/>
       <c r="B9" s="47" t="s">
         <v>585</v>
@@ -8174,7 +8569,7 @@
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" spans="1:5" ht="17.25">
+    <row r="10" spans="1:5" ht="19.2">
       <c r="A10" s="49" t="s">
         <v>586</v>
       </c>
@@ -8191,7 +8586,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" thickBot="1">
+    <row r="11" spans="1:5" ht="19.8" thickBot="1">
       <c r="A11" s="50"/>
       <c r="B11" s="47" t="s">
         <v>587</v>
@@ -8200,7 +8595,7 @@
       <c r="D11" s="52"/>
       <c r="E11" s="52"/>
     </row>
-    <row r="12" spans="1:5" ht="17.25">
+    <row r="12" spans="1:5" ht="19.2">
       <c r="A12" s="49" t="s">
         <v>588</v>
       </c>
@@ -8217,7 +8612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" thickBot="1">
+    <row r="13" spans="1:5" ht="19.8" thickBot="1">
       <c r="A13" s="50"/>
       <c r="B13" s="47" t="s">
         <v>589</v>
@@ -8226,7 +8621,7 @@
       <c r="D13" s="52"/>
       <c r="E13" s="52"/>
     </row>
-    <row r="14" spans="1:5" ht="17.25">
+    <row r="14" spans="1:5" ht="19.2">
       <c r="A14" s="49" t="s">
         <v>590</v>
       </c>
@@ -8243,7 +8638,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" thickBot="1">
+    <row r="15" spans="1:5" ht="19.8" thickBot="1">
       <c r="A15" s="50"/>
       <c r="B15" s="47" t="s">
         <v>591</v>
@@ -8252,7 +8647,7 @@
       <c r="D15" s="52"/>
       <c r="E15" s="52"/>
     </row>
-    <row r="16" spans="1:5" ht="17.25">
+    <row r="16" spans="1:5" ht="19.2">
       <c r="A16" s="49" t="s">
         <v>592</v>
       </c>
@@ -8269,7 +8664,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" thickBot="1">
+    <row r="17" spans="1:5" ht="19.8" thickBot="1">
       <c r="A17" s="50"/>
       <c r="B17" s="47" t="s">
         <v>593</v>
@@ -8278,8 +8673,8 @@
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
     </row>
-    <row r="21" spans="1:5" ht="17.25" thickBot="1"/>
-    <row r="22" spans="1:5" ht="18" thickBot="1">
+    <row r="21" spans="1:5" ht="18" thickBot="1"/>
+    <row r="22" spans="1:5" ht="19.8" thickBot="1">
       <c r="A22" s="15" t="s">
         <v>563</v>
       </c>
@@ -8296,7 +8691,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17.25">
+    <row r="23" spans="1:5" ht="19.2">
       <c r="A23" s="49" t="s">
         <v>578</v>
       </c>
@@ -8313,7 +8708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18" thickBot="1">
+    <row r="24" spans="1:5" ht="19.8" thickBot="1">
       <c r="A24" s="50"/>
       <c r="B24" s="47" t="s">
         <v>579</v>
@@ -8322,7 +8717,7 @@
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
     </row>
-    <row r="25" spans="1:5" ht="17.25">
+    <row r="25" spans="1:5" ht="19.2">
       <c r="A25" s="49" t="s">
         <v>580</v>
       </c>
@@ -8339,7 +8734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="35.25" thickBot="1">
+    <row r="26" spans="1:5" ht="39" thickBot="1">
       <c r="A26" s="50"/>
       <c r="B26" s="47" t="s">
         <v>581</v>
@@ -8348,7 +8743,7 @@
       <c r="D26" s="52"/>
       <c r="E26" s="52"/>
     </row>
-    <row r="27" spans="1:5" ht="17.25">
+    <row r="27" spans="1:5" ht="19.2">
       <c r="A27" s="49" t="s">
         <v>584</v>
       </c>
@@ -8365,7 +8760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="18" thickBot="1">
+    <row r="28" spans="1:5" ht="19.8" thickBot="1">
       <c r="A28" s="50"/>
       <c r="B28" s="47" t="s">
         <v>585</v>
@@ -8374,7 +8769,7 @@
       <c r="D28" s="52"/>
       <c r="E28" s="52"/>
     </row>
-    <row r="29" spans="1:5" ht="17.25">
+    <row r="29" spans="1:5" ht="19.2">
       <c r="A29" s="49" t="s">
         <v>588</v>
       </c>
@@ -8391,7 +8786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="18" thickBot="1">
+    <row r="30" spans="1:5" ht="19.8" thickBot="1">
       <c r="A30" s="50"/>
       <c r="B30" s="47" t="s">
         <v>589</v>
@@ -8400,7 +8795,7 @@
       <c r="D30" s="52"/>
       <c r="E30" s="52"/>
     </row>
-    <row r="31" spans="1:5" ht="17.25">
+    <row r="31" spans="1:5" ht="19.2">
       <c r="A31" s="49" t="s">
         <v>582</v>
       </c>
@@ -8417,7 +8812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="18" thickBot="1">
+    <row r="32" spans="1:5" ht="19.8" thickBot="1">
       <c r="A32" s="50"/>
       <c r="B32" s="47" t="s">
         <v>583</v>
@@ -8428,14 +8823,38 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D27:D28"/>
@@ -8448,38 +8867,14 @@
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8489,13 +8884,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7D28BF-FC95-411D-BBBF-B7CDE652B6A5}">
   <dimension ref="B2:F12"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" customWidth="1"/>
-    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.09765625" customWidth="1"/>
+    <col min="4" max="4" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" customWidth="1"/>
+    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -8549,7 +8944,7 @@
         <v>19.740000000000002</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="33">
+    <row r="8" spans="2:6" ht="34.799999999999997">
       <c r="C8" s="48" t="s">
         <v>599</v>
       </c>
@@ -8563,7 +8958,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="33">
+    <row r="9" spans="2:6" ht="34.799999999999997">
       <c r="B9" s="48" t="s">
         <v>598</v>
       </c>
@@ -8638,291 +9033,116 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12054B3A-2648-4FB0-BBA9-9ACDCE3B68E0}">
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE51B4F-EDEB-44A3-84FD-FBE00642B6DC}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="39.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="105" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" customWidth="1"/>
+    <col min="2" max="2" width="43.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1">
-      <c r="A1" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-    </row>
-    <row r="2" spans="1:3" ht="18" thickBot="1">
-      <c r="A2" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" thickBot="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A5" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" thickBot="1">
-      <c r="A6" s="25"/>
-      <c r="B6" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A7" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A8" s="30"/>
-      <c r="B8" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A10" s="30"/>
-      <c r="B10" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A11" s="30"/>
-      <c r="B11" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A13" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="18" thickBot="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="18" thickBot="1">
-      <c r="A17" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A19" s="25"/>
-      <c r="B19" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A21" s="25"/>
-      <c r="B21" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="18" thickBot="1">
-      <c r="A22" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A23" s="25"/>
-      <c r="B23" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A24" s="30"/>
-      <c r="B24" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" thickBot="1">
-      <c r="A25" s="25"/>
-      <c r="B25" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="24" customFormat="1" ht="18" thickBot="1">
-      <c r="A27" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A28" s="30"/>
-      <c r="B28" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="24" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A29" s="30"/>
-      <c r="B29" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="17.25">
-      <c r="B30" s="31" t="s">
-        <v>255</v>
+    <row r="1" spans="1:2">
+      <c r="A1" s="57" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="58" t="s">
+        <v>605</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="58" t="s">
+        <v>607</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="48" t="s">
+        <v>609</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="48" t="s">
+        <v>611</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="48" t="s">
+        <v>613</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="48" t="s">
+        <v>615</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="48" t="s">
+        <v>617</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="48" t="s">
+        <v>619</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="48" t="s">
+        <v>621</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="48" t="s">
+        <v>623</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="48" t="s">
+        <v>625</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="48" t="s">
+        <v>627</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>628</v>
       </c>
     </row>
   </sheetData>
